--- a/datos/excursiones.xlsx
+++ b/datos/excursiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josel\Documents\elaios_mapa\proyecto_mapa_excursiones\mapa_elaios\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0512FE75-382D-4AFF-A5F5-A5E01C815FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3A55D9-B255-40C2-AEF8-F9273397C8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
   </bookViews>
@@ -2200,7 +2200,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F92D137-B0F7-489C-BBD5-87D14D584D75}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Q209"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2209,7 +2208,7 @@
     <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="135.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="67.33203125" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="39.109375" hidden="1" customWidth="1"/>
@@ -2272,7 +2271,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="str">
         <f t="shared" ref="A2:A37" si="0">CONCATENATE(E2,"_",TEXT(B2,"00"),"_",TEXT(C2,"00"))</f>
         <v>2025_12_21</v>
@@ -2322,7 +2321,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_11_23</v>
@@ -2376,7 +2375,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_11_22</v>
@@ -2430,7 +2429,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_10_19</v>
@@ -2484,7 +2483,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_10_05</v>
@@ -2538,7 +2537,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_10_04</v>
@@ -2592,7 +2591,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_08_31</v>
@@ -2646,7 +2645,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_08_30</v>
@@ -2700,7 +2699,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_07_20</v>
@@ -2754,7 +2753,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_06_25</v>
@@ -2808,7 +2807,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_06_08</v>
@@ -2862,7 +2861,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_05_01</v>
@@ -2918,7 +2917,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_04_06</v>
@@ -2972,7 +2971,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_04_05</v>
@@ -3026,7 +3025,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_03_16</v>
@@ -3080,7 +3079,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_03_15</v>
@@ -3134,7 +3133,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_02_16</v>
@@ -3190,7 +3189,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2025_01_26</v>
@@ -3244,7 +3243,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_12_15</v>
@@ -3300,7 +3299,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_11_10</v>
@@ -3356,7 +3355,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_10_05</v>
@@ -3412,7 +3411,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_10_06</v>
@@ -3466,7 +3465,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_09_07</v>
@@ -3522,7 +3521,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_09_08</v>
@@ -3570,7 +3569,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="str">
         <f>CONCATENATE(E26,"_",TEXT(B26,"00"),"_",TEXT(C26,"00"))</f>
         <v>2024_08_04</v>
@@ -3626,7 +3625,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_07_13</v>
@@ -3682,7 +3681,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_07_14</v>
@@ -3738,7 +3737,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_06_15</v>
@@ -3794,7 +3793,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_06_16</v>
@@ -3848,7 +3847,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_05_17</v>
@@ -3901,7 +3900,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_04_13</v>
@@ -3954,7 +3953,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_04_14</v>
@@ -4005,7 +4004,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_03_17</v>
@@ -4058,7 +4057,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_02_18</v>
@@ -4111,7 +4110,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2024_01_21</v>
@@ -4164,7 +4163,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="str">
         <f t="shared" si="0"/>
         <v>2023_12_17</v>
@@ -4217,7 +4216,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="str">
         <f t="shared" ref="A38:A73" si="7">CONCATENATE(E38,"_",TEXT(B38,"00"),"_",TEXT(C38,"00"))</f>
         <v>2023_11_19</v>
@@ -4270,7 +4269,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_10_10</v>
@@ -4326,7 +4325,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_09_01</v>
@@ -4379,7 +4378,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_07_29</v>
@@ -4432,7 +4431,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_07_08</v>
@@ -4485,7 +4484,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_07_09</v>
@@ -4538,7 +4537,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_06_10</v>
@@ -4591,7 +4590,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_06_11</v>
@@ -4642,7 +4641,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_05_27</v>
@@ -4695,7 +4694,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_05_28</v>
@@ -4746,7 +4745,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_04_29</v>
@@ -4799,7 +4798,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_04_30</v>
@@ -4850,7 +4849,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_03_11</v>
@@ -4906,7 +4905,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_03_12</v>
@@ -4960,7 +4959,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2023_02_12</v>
@@ -5505,7 +5504,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_12_01</v>
@@ -5546,7 +5545,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_11_01</v>
@@ -5587,7 +5586,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_10_01</v>
@@ -5628,7 +5627,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_10_01</v>
@@ -5669,7 +5668,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_09_01</v>
@@ -5710,7 +5709,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_07_01</v>
@@ -5751,7 +5750,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_06_01</v>
@@ -5792,7 +5791,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2021_05_01</v>
@@ -5833,7 +5832,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="7" t="str">
         <f t="shared" si="7"/>
         <v>2020_12_01</v>
@@ -5874,7 +5873,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="str">
         <f t="shared" ref="A74:A105" si="18">CONCATENATE(E74,"_",TEXT(B74,"00"),"_",TEXT(C74,"00"))</f>
         <v>2020_06_01</v>
@@ -5915,7 +5914,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2020_02_01</v>
@@ -5956,7 +5955,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2020_01_01</v>
@@ -5997,7 +5996,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_12_01</v>
@@ -6038,7 +6037,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_11_01</v>
@@ -6079,7 +6078,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_10_01</v>
@@ -6120,7 +6119,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_09_01</v>
@@ -6161,7 +6160,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_08_01</v>
@@ -6202,7 +6201,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_07_01</v>
@@ -6243,7 +6242,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_06_01</v>
@@ -6284,7 +6283,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_05_01</v>
@@ -6325,7 +6324,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_04_01</v>
@@ -6366,7 +6365,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_03_01</v>
@@ -6407,7 +6406,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_02_01</v>
@@ -6448,7 +6447,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_02_01</v>
@@ -6489,7 +6488,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2019_01_01</v>
@@ -6530,7 +6529,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_12_01</v>
@@ -6571,7 +6570,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_11_01</v>
@@ -6612,7 +6611,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_10_01</v>
@@ -6653,7 +6652,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_09_01</v>
@@ -6694,7 +6693,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_08_01</v>
@@ -6735,7 +6734,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_07_01</v>
@@ -6776,7 +6775,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_06_01</v>
@@ -6817,7 +6816,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_05_01</v>
@@ -6858,7 +6857,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_05_01</v>
@@ -6899,7 +6898,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_04_01</v>
@@ -6940,7 +6939,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_03_01</v>
@@ -6981,7 +6980,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_02_01</v>
@@ -7022,7 +7021,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2018_01_01</v>
@@ -7063,7 +7062,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2017_12_01</v>
@@ -7104,7 +7103,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2017_11_01</v>
@@ -7145,7 +7144,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="str">
         <f t="shared" si="18"/>
         <v>2017_10_01</v>
@@ -7186,7 +7185,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="str">
         <f t="shared" ref="A106:A137" si="21">CONCATENATE(E106,"_",TEXT(B106,"00"),"_",TEXT(C106,"00"))</f>
         <v>2017_09_01</v>
@@ -7227,7 +7226,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_07_01</v>
@@ -7268,7 +7267,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_06_01</v>
@@ -7309,7 +7308,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_05_01</v>
@@ -7350,7 +7349,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_05_01</v>
@@ -7391,7 +7390,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_04_01</v>
@@ -7432,7 +7431,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_03_01</v>
@@ -7473,7 +7472,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_02_01</v>
@@ -7514,7 +7513,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2017_01_01</v>
@@ -7555,7 +7554,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_12_01</v>
@@ -7596,7 +7595,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_11_01</v>
@@ -7637,7 +7636,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_10_01</v>
@@ -7678,7 +7677,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_09_01</v>
@@ -7719,7 +7718,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_06_01</v>
@@ -7760,7 +7759,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_05_01</v>
@@ -7801,7 +7800,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_04_01</v>
@@ -7842,7 +7841,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_02_01</v>
@@ -7883,7 +7882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2016_01_01</v>
@@ -7924,7 +7923,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_12_01</v>
@@ -7965,7 +7964,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_11_01</v>
@@ -8006,7 +8005,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_10_01</v>
@@ -8047,7 +8046,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_09_01</v>
@@ -8088,7 +8087,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_07_01</v>
@@ -8129,7 +8128,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_06_01</v>
@@ -8170,7 +8169,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_05_01</v>
@@ -8211,7 +8210,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_04_01</v>
@@ -8252,7 +8251,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_03_01</v>
@@ -8293,7 +8292,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_02_01</v>
@@ -8334,7 +8333,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_02_01</v>
@@ -8375,7 +8374,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2015_01_01</v>
@@ -8416,7 +8415,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2014_12_01</v>
@@ -8457,7 +8456,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="str">
         <f t="shared" si="21"/>
         <v>2014_11_01</v>
@@ -8498,7 +8497,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="7" t="str">
         <f t="shared" ref="A138:A169" si="24">CONCATENATE(E138,"_",TEXT(B138,"00"),"_",TEXT(C138,"00"))</f>
         <v>2014_10_01</v>
@@ -8539,7 +8538,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_09_01</v>
@@ -8580,7 +8579,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_07_01</v>
@@ -8621,7 +8620,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_06_01</v>
@@ -8662,7 +8661,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_05_01</v>
@@ -8703,7 +8702,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_05_01</v>
@@ -8744,7 +8743,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_04_01</v>
@@ -8785,7 +8784,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_03_01</v>
@@ -8826,7 +8825,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_02_01</v>
@@ -8867,7 +8866,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2014_01_01</v>
@@ -8908,7 +8907,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_12_01</v>
@@ -8949,7 +8948,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_11_01</v>
@@ -8990,7 +8989,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_10_01</v>
@@ -9031,7 +9030,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_09_01</v>
@@ -9072,7 +9071,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_07_01</v>
@@ -9113,7 +9112,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_06_01</v>
@@ -9154,7 +9153,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_05_01</v>
@@ -9195,7 +9194,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_04_01</v>
@@ -9236,7 +9235,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_03_01</v>
@@ -9277,7 +9276,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_02_01</v>
@@ -9318,7 +9317,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2013_01_01</v>
@@ -9359,7 +9358,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_12_01</v>
@@ -9400,7 +9399,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_11_01</v>
@@ -9441,7 +9440,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_10_01</v>
@@ -9482,7 +9481,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_09_01</v>
@@ -9523,7 +9522,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_07_01</v>
@@ -9564,7 +9563,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_06_01</v>
@@ -9605,7 +9604,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_05_01</v>
@@ -9646,7 +9645,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_04_01</v>
@@ -9687,7 +9686,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_03_01</v>
@@ -9728,7 +9727,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_02_01</v>
@@ -9769,7 +9768,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="7" t="str">
         <f t="shared" si="24"/>
         <v>2012_01_01</v>
@@ -9810,7 +9809,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="7" t="str">
         <f t="shared" ref="A170:A201" si="27">CONCATENATE(E170,"_",TEXT(B170,"00"),"_",TEXT(C170,"00"))</f>
         <v>2011_12_01</v>
@@ -9851,7 +9850,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_11_01</v>
@@ -9892,7 +9891,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_10_01</v>
@@ -9933,7 +9932,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_09_01</v>
@@ -9974,7 +9973,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_07_01</v>
@@ -10015,7 +10014,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_07_01</v>
@@ -10056,7 +10055,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_06_01</v>
@@ -10097,7 +10096,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_05_01</v>
@@ -10138,7 +10137,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_04_01</v>
@@ -10179,7 +10178,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_03_01</v>
@@ -10220,7 +10219,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_02_01</v>
@@ -10261,7 +10260,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2011_01_01</v>
@@ -10302,7 +10301,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_12_01</v>
@@ -10343,7 +10342,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_11_01</v>
@@ -10384,7 +10383,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_10_01</v>
@@ -10425,7 +10424,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_09_01</v>
@@ -10466,7 +10465,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_06_01</v>
@@ -10507,7 +10506,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_05_01</v>
@@ -10548,7 +10547,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_04_01</v>
@@ -10589,7 +10588,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_03_01</v>
@@ -10630,7 +10629,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_02_01</v>
@@ -10671,7 +10670,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2010_01_01</v>
@@ -10712,7 +10711,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_12_01</v>
@@ -10753,7 +10752,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_10_01</v>
@@ -10794,7 +10793,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_07_01</v>
@@ -10835,7 +10834,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_06_01</v>
@@ -10876,7 +10875,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_05_01</v>
@@ -10917,7 +10916,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_04_01</v>
@@ -10958,7 +10957,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_03_01</v>
@@ -10999,7 +10998,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_02_01</v>
@@ -11040,7 +11039,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2009_01_01</v>
@@ -11081,7 +11080,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="7" t="str">
         <f t="shared" si="27"/>
         <v>2008_11_01</v>
@@ -11122,7 +11121,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="str">
         <f t="shared" ref="A202:A209" si="30">CONCATENATE(E202,"_",TEXT(B202,"00"),"_",TEXT(C202,"00"))</f>
         <v>2008_10_01</v>
@@ -11163,7 +11162,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="str">
         <f t="shared" si="30"/>
         <v>2008_07_01</v>
@@ -11204,7 +11203,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="7" t="str">
         <f t="shared" si="30"/>
         <v>2008_06_01</v>
@@ -11245,7 +11244,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="str">
         <f t="shared" si="30"/>
         <v>2008_05_01</v>
@@ -11286,7 +11285,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="str">
         <f t="shared" si="30"/>
         <v>2008_04_01</v>
@@ -11327,7 +11326,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="str">
         <f t="shared" si="30"/>
         <v>2008_03_01</v>
@@ -11368,7 +11367,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="7" t="str">
         <f t="shared" si="30"/>
         <v>2008_02_01</v>
@@ -11409,7 +11408,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="7" t="str">
         <f t="shared" si="30"/>
         <v>2008_01_01</v>
@@ -11452,11 +11451,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:Q209" xr:uid="{0F92D137-B0F7-489C-BBD5-87D14D584D75}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="2022"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q209">
       <sortCondition descending="1" ref="A1"/>
     </sortState>

--- a/datos/excursiones.xlsx
+++ b/datos/excursiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josel\Documents\elaios_mapa\proyecto_mapa_excursiones\mapa_elaios\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3A55D9-B255-40C2-AEF8-F9273397C8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DC4098-9B3B-4757-8D84-0FB49381A2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="548">
   <si>
     <t>mes_numerico</t>
   </si>
@@ -1668,18 +1668,6 @@
   </si>
   <si>
     <t>https://www.google.es/maps/place/22120+Si%C3%A9tamo,+Huesca/@42.1262349,-0.288962,16z/data=!3m1!4b1!4m6!3m5!1s0xd5869c86e724c7b:0x47ccb08933c3746a!8m2!3d42.1303701!4d-0.2813739!16s%2Fg%2F11bc6nwk_0?entry=ttu&amp;g_ep=EgoyMDI2MDcxNS4wIKXMDSoASAFQAw%3D%3D</t>
-  </si>
-  <si>
-    <t>Suma</t>
-  </si>
-  <si>
-    <t>Promedio</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Recuento</t>
   </si>
   <si>
     <t>GR-92 Camino de ronda desde L´Ametlla de Mar a L´Ampolla</t>
@@ -2200,7 +2188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F92D137-B0F7-489C-BBD5-87D14D584D75}">
-  <dimension ref="A1:Q209"/>
+  <dimension ref="A1:Q211"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -4763,10 +4751,10 @@
         <v>2023</v>
       </c>
       <c r="F48" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G48" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H48" s="7" t="str">
         <f t="shared" si="8"/>
@@ -4777,7 +4765,7 @@
         <v>0.91357820000000001</v>
       </c>
       <c r="J48" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="K48" t="s">
         <v>100</v>
@@ -4816,10 +4804,10 @@
         <v>2023</v>
       </c>
       <c r="F49" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G49" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H49" s="7" t="str">
         <f t="shared" ref="H49" si="14">MID(J49,FIND("@",J49)+1,FIND(",",J49,FIND("@",J49))-FIND("@",J49)-1)</f>
@@ -4830,7 +4818,7 @@
         <v>0.91357820000000001</v>
       </c>
       <c r="J49" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="K49" t="s">
         <v>100</v>
@@ -4867,10 +4855,10 @@
         <v>2023</v>
       </c>
       <c r="F50" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="G50" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H50" s="7" t="str">
         <f t="shared" si="8"/>
@@ -4881,13 +4869,13 @@
         <v>-2.356951</v>
       </c>
       <c r="J50" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="K50" t="s">
         <v>100</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>414</v>
@@ -4902,7 +4890,7 @@
         <v>458</v>
       </c>
       <c r="Q50" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
@@ -4917,16 +4905,16 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E51">
         <v>2023</v>
       </c>
       <c r="F51" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="G51" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="H51" s="7" t="str">
         <f t="shared" ref="H51" si="16">MID(J51,FIND("@",J51)+1,FIND(",",J51,FIND("@",J51))-FIND("@",J51)-1)</f>
@@ -4937,13 +4925,13 @@
         <v>-2.356951</v>
       </c>
       <c r="J51" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="K51" t="s">
         <v>100</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" t="s">
@@ -4956,7 +4944,7 @@
         <v>458</v>
       </c>
       <c r="Q51" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
@@ -4977,7 +4965,7 @@
         <v>2023</v>
       </c>
       <c r="F52" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G52" t="s">
         <v>351</v>
@@ -4991,7 +4979,7 @@
         <v>-0.53164290000000003</v>
       </c>
       <c r="J52" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="K52" t="s">
         <v>100</v>
@@ -11123,7 +11111,7 @@
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="7" t="str">
-        <f t="shared" ref="A202:A209" si="30">CONCATENATE(E202,"_",TEXT(B202,"00"),"_",TEXT(C202,"00"))</f>
+        <f t="shared" ref="A202:A211" si="30">CONCATENATE(E202,"_",TEXT(B202,"00"),"_",TEXT(C202,"00"))</f>
         <v>2008_10_01</v>
       </c>
       <c r="B202">
@@ -11447,6 +11435,36 @@
       </c>
       <c r="O209" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A210" s="7" t="str">
+        <f t="shared" si="30"/>
+        <v>2007_01_01</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="E210">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A211" s="7" t="str">
+        <f t="shared" si="30"/>
+        <v>2006_01_01</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="E211">
+        <v>2006</v>
       </c>
     </row>
   </sheetData>

--- a/datos/excursiones.xlsx
+++ b/datos/excursiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josel\Documents\elaios_mapa\proyecto_mapa_excursiones\mapa_elaios\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DC4098-9B3B-4757-8D84-0FB49381A2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C36920-313C-4A53-8116-6694E69B348C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="548">
   <si>
     <t>mes_numerico</t>
   </si>
@@ -11448,8 +11448,14 @@
       <c r="C210">
         <v>1</v>
       </c>
+      <c r="D210" t="s">
+        <v>10</v>
+      </c>
       <c r="E210">
         <v>2007</v>
+      </c>
+      <c r="F210" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.3">
@@ -11463,8 +11469,14 @@
       <c r="C211">
         <v>1</v>
       </c>
+      <c r="D211" t="s">
+        <v>15</v>
+      </c>
       <c r="E211">
         <v>2006</v>
+      </c>
+      <c r="F211" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/datos/excursiones.xlsx
+++ b/datos/excursiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josel\Documents\elaios_mapa\proyecto_mapa_excursiones\mapa_elaios\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8918285-60B7-42AC-BACF-53924249F3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{0AAA0AB3-4D1B-4FA2-AAE1-96F3CD5FC277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
   </bookViews>

--- a/datos/excursiones.xlsx
+++ b/datos/excursiones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josel\Documents\elaios_mapa\proyecto_mapa_excursiones\mapa_elaios\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AE7836-3529-46C3-9C22-FADC82A4762D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6325DBF7-DC96-42B8-AE96-A9FF2DC3D528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="1039">
   <si>
     <t>mes_numerico</t>
   </si>
@@ -3070,9 +3070,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>elaios;panteres_grogues</t>
   </si>
   <si>
     <t>https://www.wikiloc.com/walking-trails/escocia-paseo-por-edinburgh-y-subida-a-arthurs-seat-220692329</t>
@@ -4299,7 +4296,7 @@
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P8" t="s">
         <v>80</v>
@@ -4466,7 +4463,7 @@
         <v>99</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>99</v>
@@ -5216,7 +5213,7 @@
         <v>301</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" t="s">
@@ -5332,7 +5329,7 @@
         <v>99</v>
       </c>
       <c r="M26" s="18" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>272</v>
@@ -5684,7 +5681,7 @@
         <v>99</v>
       </c>
       <c r="M32" s="20" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" t="s">
@@ -5741,7 +5738,7 @@
         <v>99</v>
       </c>
       <c r="M33" s="20" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>264</v>
@@ -5800,7 +5797,7 @@
         <v>99</v>
       </c>
       <c r="M34" s="20" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>263</v>
@@ -5859,7 +5856,7 @@
         <v>99</v>
       </c>
       <c r="M35" s="20" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>261</v>
@@ -5918,7 +5915,7 @@
         <v>99</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>259</v>
@@ -5977,7 +5974,7 @@
         <v>99</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>257</v>
@@ -6036,7 +6033,7 @@
         <v>99</v>
       </c>
       <c r="M38" s="21" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>255</v>
@@ -6154,7 +6151,7 @@
         <v>99</v>
       </c>
       <c r="M40" s="20" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>251</v>
@@ -6213,7 +6210,7 @@
         <v>99</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>249</v>
@@ -6272,7 +6269,7 @@
         <v>99</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>247</v>
@@ -6331,7 +6328,7 @@
         <v>99</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>246</v>
@@ -6447,7 +6444,7 @@
         <v>99</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>245</v>
@@ -6506,7 +6503,7 @@
         <v>99</v>
       </c>
       <c r="M46" s="20" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" t="s">
@@ -6622,7 +6619,7 @@
         <v>99</v>
       </c>
       <c r="M48" s="20" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" t="s">
@@ -6679,7 +6676,7 @@
         <v>99</v>
       </c>
       <c r="M49" s="20" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>243</v>
@@ -6848,13 +6845,13 @@
         <v>-0.8052433</v>
       </c>
       <c r="K52" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="L52" t="s">
         <v>99</v>
       </c>
       <c r="M52" s="20" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>241</v>
@@ -7631,7 +7628,7 @@
     </row>
     <row r="66" spans="1:18">
       <c r="A66" s="7" t="str">
-        <f t="shared" ref="A66:A97" si="4">CONCATENATE(E66,"_",TEXT(B66,"00"),"_",TEXT(C66,"00"))</f>
+        <f t="shared" ref="A66:A77" si="4">CONCATENATE(E66,"_",TEXT(B66,"00"),"_",TEXT(C66,"00"))</f>
         <v>2022_04_24</v>
       </c>
       <c r="B66">
@@ -7742,7 +7739,7 @@
         <v>81</v>
       </c>
       <c r="R67" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -8381,7 +8378,7 @@
         <v>80</v>
       </c>
       <c r="Q78" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R78" s="19" t="s">
         <v>82</v>
@@ -8437,7 +8434,7 @@
         <v>80</v>
       </c>
       <c r="Q79" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R79" s="19" t="s">
         <v>85</v>
@@ -8493,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="Q80" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R80" s="19" t="s">
         <v>85</v>
@@ -8549,7 +8546,7 @@
         <v>80</v>
       </c>
       <c r="Q81" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R81" s="19" t="s">
         <v>85</v>
@@ -8605,7 +8602,7 @@
         <v>993</v>
       </c>
       <c r="Q82" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R82" s="19" t="s">
         <v>82</v>
@@ -8661,7 +8658,7 @@
         <v>80</v>
       </c>
       <c r="Q83" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R83" s="19" t="s">
         <v>82</v>
@@ -8717,7 +8714,7 @@
         <v>80</v>
       </c>
       <c r="Q84" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R84" s="19" t="s">
         <v>82</v>
@@ -8773,7 +8770,7 @@
         <v>80</v>
       </c>
       <c r="Q85" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R85" s="19" t="s">
         <v>82</v>
@@ -8829,7 +8826,7 @@
         <v>80</v>
       </c>
       <c r="Q86" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R86" s="19" t="s">
         <v>82</v>
@@ -8885,7 +8882,7 @@
         <v>80</v>
       </c>
       <c r="Q87" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R87" s="19" t="s">
         <v>292</v>
@@ -8941,7 +8938,7 @@
         <v>80</v>
       </c>
       <c r="Q88" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R88" s="19" t="s">
         <v>82</v>
@@ -8997,10 +8994,10 @@
         <v>80</v>
       </c>
       <c r="Q89" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R89" s="19" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -9053,7 +9050,7 @@
         <v>302</v>
       </c>
       <c r="Q90" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R90" s="19" t="s">
         <v>82</v>
@@ -9109,7 +9106,7 @@
         <v>302</v>
       </c>
       <c r="Q91" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R91" s="19" t="s">
         <v>315</v>
@@ -9165,7 +9162,7 @@
         <v>80</v>
       </c>
       <c r="Q92" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R92" s="19" t="s">
         <v>82</v>
@@ -9221,7 +9218,7 @@
         <v>80</v>
       </c>
       <c r="Q93" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R93" s="19" t="s">
         <v>82</v>
@@ -9277,7 +9274,7 @@
         <v>80</v>
       </c>
       <c r="Q94" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R94" s="19" t="s">
         <v>82</v>
@@ -9333,7 +9330,7 @@
         <v>80</v>
       </c>
       <c r="Q95" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R95" s="19" t="s">
         <v>85</v>
@@ -9389,7 +9386,7 @@
         <v>80</v>
       </c>
       <c r="Q96" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R96" s="19" t="s">
         <v>285</v>
@@ -9445,10 +9442,10 @@
         <v>80</v>
       </c>
       <c r="Q97" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R97" s="19" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -9501,7 +9498,7 @@
         <v>993</v>
       </c>
       <c r="Q98" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R98" s="19" t="s">
         <v>82</v>
@@ -9557,7 +9554,7 @@
         <v>80</v>
       </c>
       <c r="Q99" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R99" s="19" t="s">
         <v>82</v>
@@ -9613,7 +9610,7 @@
         <v>80</v>
       </c>
       <c r="Q100" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R100" s="19" t="s">
         <v>85</v>
@@ -9669,10 +9666,10 @@
         <v>80</v>
       </c>
       <c r="Q101" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R101" s="19" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -9725,10 +9722,10 @@
         <v>80</v>
       </c>
       <c r="Q102" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R102" s="19" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -9781,7 +9778,7 @@
         <v>80</v>
       </c>
       <c r="Q103" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R103" s="19" t="s">
         <v>82</v>
@@ -9837,7 +9834,7 @@
         <v>80</v>
       </c>
       <c r="Q104" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R104" s="19" t="s">
         <v>315</v>
@@ -9893,10 +9890,10 @@
         <v>80</v>
       </c>
       <c r="Q105" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R105" s="19" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -9949,7 +9946,7 @@
         <v>80</v>
       </c>
       <c r="Q106" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R106" s="19" t="s">
         <v>82</v>
@@ -10005,7 +10002,7 @@
         <v>80</v>
       </c>
       <c r="Q107" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R107" s="19" t="s">
         <v>86</v>
@@ -10061,7 +10058,7 @@
         <v>80</v>
       </c>
       <c r="Q108" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R108" s="19" t="s">
         <v>82</v>
@@ -10117,7 +10114,7 @@
         <v>80</v>
       </c>
       <c r="Q109" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R109" s="19" t="s">
         <v>82</v>
@@ -10173,7 +10170,7 @@
         <v>80</v>
       </c>
       <c r="Q110" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R110" s="19" t="s">
         <v>82</v>
@@ -10229,7 +10226,7 @@
         <v>80</v>
       </c>
       <c r="Q111" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R111" s="19" t="s">
         <v>82</v>
@@ -10285,7 +10282,7 @@
         <v>80</v>
       </c>
       <c r="Q112" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R112" s="19" t="s">
         <v>82</v>
@@ -10341,7 +10338,7 @@
         <v>80</v>
       </c>
       <c r="Q113" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R113" s="19" t="s">
         <v>82</v>
@@ -10397,7 +10394,7 @@
         <v>80</v>
       </c>
       <c r="Q114" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R114" s="19" t="s">
         <v>285</v>
@@ -10453,7 +10450,7 @@
         <v>80</v>
       </c>
       <c r="Q115" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R115" s="19" t="s">
         <v>82</v>
@@ -10503,13 +10500,13 @@
       </c>
       <c r="N116" s="3"/>
       <c r="O116" t="s">
-        <v>88</v>
+        <v>280</v>
       </c>
       <c r="P116" t="s">
         <v>80</v>
       </c>
       <c r="Q116" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R116" s="19" t="s">
         <v>285</v>
@@ -10565,7 +10562,7 @@
         <v>80</v>
       </c>
       <c r="Q117" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R117" s="19" t="s">
         <v>82</v>
@@ -10621,7 +10618,7 @@
         <v>80</v>
       </c>
       <c r="Q118" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R118" s="19" t="s">
         <v>82</v>
@@ -10677,7 +10674,7 @@
         <v>80</v>
       </c>
       <c r="Q119" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R119" s="19" t="s">
         <v>82</v>
@@ -10727,13 +10724,13 @@
       </c>
       <c r="N120" s="3"/>
       <c r="O120" t="s">
-        <v>88</v>
+        <v>279</v>
       </c>
       <c r="P120" t="s">
         <v>80</v>
       </c>
       <c r="Q120" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R120" s="19" t="s">
         <v>82</v>
@@ -10789,10 +10786,10 @@
         <v>80</v>
       </c>
       <c r="Q121" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R121" s="19" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -10845,7 +10842,7 @@
         <v>80</v>
       </c>
       <c r="Q122" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R122" s="19" t="s">
         <v>82</v>
@@ -10901,7 +10898,7 @@
         <v>80</v>
       </c>
       <c r="Q123" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R123" s="19" t="s">
         <v>82</v>
@@ -10957,7 +10954,7 @@
         <v>80</v>
       </c>
       <c r="Q124" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R124" s="19" t="s">
         <v>82</v>
@@ -11013,7 +11010,7 @@
         <v>80</v>
       </c>
       <c r="Q125" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R125" s="19" t="s">
         <v>82</v>
@@ -11069,7 +11066,7 @@
         <v>993</v>
       </c>
       <c r="Q126" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R126" s="19" t="s">
         <v>82</v>
@@ -11125,7 +11122,7 @@
         <v>80</v>
       </c>
       <c r="Q127" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R127" s="19" t="s">
         <v>82</v>
@@ -11181,7 +11178,7 @@
         <v>80</v>
       </c>
       <c r="Q128" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R128" s="19" t="s">
         <v>82</v>
@@ -11237,10 +11234,10 @@
         <v>80</v>
       </c>
       <c r="Q129" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R129" s="19" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -11293,7 +11290,7 @@
         <v>80</v>
       </c>
       <c r="Q130" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R130" s="19" t="s">
         <v>82</v>
@@ -11349,7 +11346,7 @@
         <v>80</v>
       </c>
       <c r="Q131" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R131" s="19" t="s">
         <v>82</v>
@@ -11405,7 +11402,7 @@
         <v>80</v>
       </c>
       <c r="Q132" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R132" s="19" t="s">
         <v>82</v>
@@ -11461,7 +11458,7 @@
         <v>80</v>
       </c>
       <c r="Q133" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R133" s="19" t="s">
         <v>86</v>
@@ -11517,7 +11514,7 @@
         <v>80</v>
       </c>
       <c r="Q134" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R134" s="19" t="s">
         <v>285</v>
@@ -11573,7 +11570,7 @@
         <v>80</v>
       </c>
       <c r="Q135" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R135" s="19" t="s">
         <v>83</v>
@@ -11629,7 +11626,7 @@
         <v>80</v>
       </c>
       <c r="Q136" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R136" s="19" t="s">
         <v>82</v>
@@ -11685,7 +11682,7 @@
         <v>993</v>
       </c>
       <c r="Q137" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R137" s="19" t="s">
         <v>82</v>
@@ -11741,7 +11738,7 @@
         <v>80</v>
       </c>
       <c r="Q138" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R138" s="19" t="s">
         <v>285</v>
@@ -11797,7 +11794,7 @@
         <v>80</v>
       </c>
       <c r="Q139" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R139" s="19" t="s">
         <v>285</v>
@@ -11853,7 +11850,7 @@
         <v>80</v>
       </c>
       <c r="Q140" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R140" s="19" t="s">
         <v>82</v>
@@ -11909,7 +11906,7 @@
         <v>80</v>
       </c>
       <c r="Q141" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R141" s="19" t="s">
         <v>82</v>
@@ -11965,7 +11962,7 @@
         <v>80</v>
       </c>
       <c r="Q142" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R142" s="19" t="s">
         <v>82</v>
@@ -12021,7 +12018,7 @@
         <v>80</v>
       </c>
       <c r="Q143" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R143" s="19" t="s">
         <v>82</v>
@@ -12077,7 +12074,7 @@
         <v>80</v>
       </c>
       <c r="Q144" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R144" s="19" t="s">
         <v>82</v>
@@ -12133,7 +12130,7 @@
         <v>80</v>
       </c>
       <c r="Q145" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R145" s="19" t="s">
         <v>82</v>
@@ -12189,7 +12186,7 @@
         <v>80</v>
       </c>
       <c r="Q146" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R146" s="19" t="s">
         <v>82</v>
@@ -12245,7 +12242,7 @@
         <v>80</v>
       </c>
       <c r="Q147" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R147" s="19" t="s">
         <v>82</v>
@@ -12301,7 +12298,7 @@
         <v>80</v>
       </c>
       <c r="Q148" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R148" s="19" t="s">
         <v>82</v>
@@ -12357,7 +12354,7 @@
         <v>80</v>
       </c>
       <c r="Q149" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R149" s="19" t="s">
         <v>82</v>
@@ -12413,7 +12410,7 @@
         <v>80</v>
       </c>
       <c r="Q150" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R150" s="19" t="s">
         <v>82</v>
@@ -12469,7 +12466,7 @@
         <v>80</v>
       </c>
       <c r="Q151" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R151" s="19" t="s">
         <v>82</v>
@@ -12525,7 +12522,7 @@
         <v>80</v>
       </c>
       <c r="Q152" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R152" s="19" t="s">
         <v>334</v>
@@ -12581,7 +12578,7 @@
         <v>80</v>
       </c>
       <c r="Q153" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R153" s="19" t="s">
         <v>315</v>
@@ -12631,13 +12628,13 @@
       </c>
       <c r="N154" s="3"/>
       <c r="O154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P154" t="s">
         <v>80</v>
       </c>
       <c r="Q154" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R154" s="19" t="s">
         <v>83</v>
@@ -12693,7 +12690,7 @@
         <v>993</v>
       </c>
       <c r="Q155" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R155" s="19" t="s">
         <v>82</v>
@@ -12749,7 +12746,7 @@
         <v>995</v>
       </c>
       <c r="Q156" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R156" s="19" t="s">
         <v>82</v>
@@ -12805,7 +12802,7 @@
         <v>80</v>
       </c>
       <c r="Q157" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R157" s="19" t="s">
         <v>285</v>
@@ -12861,7 +12858,7 @@
         <v>80</v>
       </c>
       <c r="Q158" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R158" s="19" t="s">
         <v>82</v>
@@ -12917,7 +12914,7 @@
         <v>80</v>
       </c>
       <c r="Q159" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R159" s="19" t="s">
         <v>82</v>
@@ -12973,7 +12970,7 @@
         <v>80</v>
       </c>
       <c r="Q160" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R160" s="19" t="s">
         <v>82</v>
@@ -13029,7 +13026,7 @@
         <v>80</v>
       </c>
       <c r="Q161" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R161" s="19" t="s">
         <v>86</v>
@@ -13085,7 +13082,7 @@
         <v>80</v>
       </c>
       <c r="Q162" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R162" s="19" t="s">
         <v>82</v>
@@ -13141,7 +13138,7 @@
         <v>80</v>
       </c>
       <c r="Q163" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R163" s="19" t="s">
         <v>82</v>
@@ -13197,7 +13194,7 @@
         <v>80</v>
       </c>
       <c r="Q164" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R164" s="19" t="s">
         <v>82</v>
@@ -13253,7 +13250,7 @@
         <v>80</v>
       </c>
       <c r="Q165" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R165" s="19" t="s">
         <v>82</v>
@@ -13309,7 +13306,7 @@
         <v>80</v>
       </c>
       <c r="Q166" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R166" s="19" t="s">
         <v>82</v>
@@ -13365,7 +13362,7 @@
         <v>80</v>
       </c>
       <c r="Q167" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R167" s="19" t="s">
         <v>85</v>
@@ -13421,7 +13418,7 @@
         <v>80</v>
       </c>
       <c r="Q168" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R168" s="19" t="s">
         <v>82</v>
@@ -13477,7 +13474,7 @@
         <v>80</v>
       </c>
       <c r="Q169" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R169" s="19" t="s">
         <v>82</v>
@@ -13533,7 +13530,7 @@
         <v>80</v>
       </c>
       <c r="Q170" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R170" s="19" t="s">
         <v>82</v>
@@ -13589,7 +13586,7 @@
         <v>993</v>
       </c>
       <c r="Q171" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R171" s="19" t="s">
         <v>85</v>
@@ -13645,7 +13642,7 @@
         <v>993</v>
       </c>
       <c r="Q172" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R172" s="19" t="s">
         <v>82</v>
@@ -13701,7 +13698,7 @@
         <v>80</v>
       </c>
       <c r="Q173" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R173" s="19" t="s">
         <v>85</v>
@@ -13757,7 +13754,7 @@
         <v>80</v>
       </c>
       <c r="Q174" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R174" s="19" t="s">
         <v>285</v>
@@ -13813,7 +13810,7 @@
         <v>80</v>
       </c>
       <c r="Q175" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R175" s="19" t="s">
         <v>82</v>
@@ -13869,7 +13866,7 @@
         <v>80</v>
       </c>
       <c r="Q176" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R176" s="19" t="s">
         <v>82</v>
@@ -13925,7 +13922,7 @@
         <v>302</v>
       </c>
       <c r="Q177" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R177" s="19" t="s">
         <v>82</v>
@@ -13981,7 +13978,7 @@
         <v>302</v>
       </c>
       <c r="Q178" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R178" s="19" t="s">
         <v>82</v>
@@ -14037,7 +14034,7 @@
         <v>80</v>
       </c>
       <c r="Q179" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R179" s="19" t="s">
         <v>82</v>
@@ -14093,7 +14090,7 @@
         <v>80</v>
       </c>
       <c r="Q180" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R180" s="19" t="s">
         <v>82</v>
@@ -14149,7 +14146,7 @@
         <v>80</v>
       </c>
       <c r="Q181" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R181" s="19" t="s">
         <v>82</v>
@@ -14205,7 +14202,7 @@
         <v>80</v>
       </c>
       <c r="Q182" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R182" s="19" t="s">
         <v>82</v>
@@ -14261,7 +14258,7 @@
         <v>80</v>
       </c>
       <c r="Q183" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R183" s="19" t="s">
         <v>285</v>
@@ -14317,7 +14314,7 @@
         <v>80</v>
       </c>
       <c r="Q184" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R184" s="19" t="s">
         <v>285</v>
@@ -14373,7 +14370,7 @@
         <v>80</v>
       </c>
       <c r="Q185" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R185" s="19" t="s">
         <v>364</v>
@@ -14429,7 +14426,7 @@
         <v>80</v>
       </c>
       <c r="Q186" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R186" s="19" t="s">
         <v>397</v>
@@ -14485,7 +14482,7 @@
         <v>80</v>
       </c>
       <c r="Q187" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R187" s="19" t="s">
         <v>315</v>
@@ -14541,7 +14538,7 @@
         <v>80</v>
       </c>
       <c r="Q188" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R188" s="19" t="s">
         <v>82</v>
@@ -14597,7 +14594,7 @@
         <v>80</v>
       </c>
       <c r="Q189" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R189" s="19" t="s">
         <v>82</v>
@@ -14653,10 +14650,10 @@
         <v>80</v>
       </c>
       <c r="Q190" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R190" s="19" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="191" spans="1:18">
@@ -14709,10 +14706,10 @@
         <v>80</v>
       </c>
       <c r="Q191" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R191" s="19" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="192" spans="1:18">
@@ -14765,7 +14762,7 @@
         <v>80</v>
       </c>
       <c r="Q192" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R192" s="19" t="s">
         <v>82</v>
@@ -14821,7 +14818,7 @@
         <v>80</v>
       </c>
       <c r="Q193" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R193" s="19" t="s">
         <v>82</v>
@@ -14857,7 +14854,7 @@
         <v>42.7610304</v>
       </c>
       <c r="J194" s="7">
-        <f t="shared" ref="J194:J257" si="10">VALUE(SUBSTITUTE(MID(K194,FIND(",",K194,FIND("@",K194))+1,FIND(",",K194,FIND(",",K194,FIND("@",K194))+1)-FIND(",",K194,FIND("@",K194))-1),".",","))</f>
+        <f t="shared" ref="J194:J250" si="10">VALUE(SUBSTITUTE(MID(K194,FIND(",",K194,FIND("@",K194))+1,FIND(",",K194,FIND(",",K194,FIND("@",K194))+1)-FIND(",",K194,FIND("@",K194))-1),".",","))</f>
         <v>-0.23676420000000001</v>
       </c>
       <c r="K194" t="s">
@@ -14877,7 +14874,7 @@
         <v>80</v>
       </c>
       <c r="Q194" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R194" s="19" t="s">
         <v>82</v>
@@ -14933,7 +14930,7 @@
         <v>80</v>
       </c>
       <c r="Q195" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R195" s="19" t="s">
         <v>82</v>
@@ -14989,7 +14986,7 @@
         <v>80</v>
       </c>
       <c r="Q196" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R196" s="19" t="s">
         <v>82</v>
@@ -15045,7 +15042,7 @@
         <v>80</v>
       </c>
       <c r="Q197" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R197" s="19" t="s">
         <v>285</v>
@@ -15101,7 +15098,7 @@
         <v>80</v>
       </c>
       <c r="Q198" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R198" s="19" t="s">
         <v>82</v>
@@ -15157,7 +15154,7 @@
         <v>80</v>
       </c>
       <c r="Q199" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R199" s="19" t="s">
         <v>82</v>
@@ -15213,7 +15210,7 @@
         <v>80</v>
       </c>
       <c r="Q200" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R200" s="19" t="s">
         <v>82</v>
@@ -15269,7 +15266,7 @@
         <v>80</v>
       </c>
       <c r="Q201" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R201" s="19" t="s">
         <v>285</v>
@@ -15325,7 +15322,7 @@
         <v>80</v>
       </c>
       <c r="Q202" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R202" s="19" t="s">
         <v>85</v>
@@ -15381,7 +15378,7 @@
         <v>80</v>
       </c>
       <c r="Q203" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R203" s="19" t="s">
         <v>85</v>
@@ -15437,7 +15434,7 @@
         <v>80</v>
       </c>
       <c r="Q204" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R204" s="19" t="s">
         <v>82</v>
@@ -15493,7 +15490,7 @@
         <v>80</v>
       </c>
       <c r="Q205" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R205" s="19" t="s">
         <v>82</v>
@@ -15549,7 +15546,7 @@
         <v>80</v>
       </c>
       <c r="Q206" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R206" s="19" t="s">
         <v>315</v>
@@ -15605,7 +15602,7 @@
         <v>80</v>
       </c>
       <c r="Q207" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R207" s="19" t="s">
         <v>315</v>
@@ -15661,7 +15658,7 @@
         <v>302</v>
       </c>
       <c r="Q208" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R208" s="19" t="s">
         <v>82</v>
@@ -15717,7 +15714,7 @@
         <v>302</v>
       </c>
       <c r="Q209" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R209" s="19" t="s">
         <v>82</v>
@@ -15773,7 +15770,7 @@
         <v>302</v>
       </c>
       <c r="Q210" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R210" s="19" t="s">
         <v>82</v>
@@ -15829,7 +15826,7 @@
         <v>302</v>
       </c>
       <c r="Q211" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R211" s="19" t="s">
         <v>82</v>
@@ -15885,7 +15882,7 @@
         <v>80</v>
       </c>
       <c r="Q212" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R212" s="19" t="s">
         <v>82</v>
@@ -15935,13 +15932,13 @@
       </c>
       <c r="N213" s="3"/>
       <c r="O213" t="s">
-        <v>1008</v>
+        <v>89</v>
       </c>
       <c r="P213" t="s">
         <v>80</v>
       </c>
       <c r="Q213" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R213" s="19" t="s">
         <v>83</v>
@@ -15997,7 +15994,7 @@
         <v>80</v>
       </c>
       <c r="Q214" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R214" s="19" t="s">
         <v>83</v>
@@ -16053,7 +16050,7 @@
         <v>80</v>
       </c>
       <c r="Q215" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R215" s="19" t="s">
         <v>82</v>
@@ -16109,7 +16106,7 @@
         <v>80</v>
       </c>
       <c r="Q216" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R216" s="19" t="s">
         <v>82</v>
@@ -16165,7 +16162,7 @@
         <v>80</v>
       </c>
       <c r="Q217" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R217" s="19" t="s">
         <v>82</v>
@@ -16221,7 +16218,7 @@
         <v>80</v>
       </c>
       <c r="Q218" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R218" s="19" t="s">
         <v>85</v>
@@ -16277,7 +16274,7 @@
         <v>80</v>
       </c>
       <c r="Q219" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R219" s="19" t="s">
         <v>85</v>
@@ -16333,7 +16330,7 @@
         <v>80</v>
       </c>
       <c r="Q220" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R220" s="19" t="s">
         <v>85</v>
@@ -16389,7 +16386,7 @@
         <v>80</v>
       </c>
       <c r="Q221" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R221" s="19" t="s">
         <v>82</v>
@@ -16445,7 +16442,7 @@
         <v>80</v>
       </c>
       <c r="Q222" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R222" s="19" t="s">
         <v>82</v>
@@ -16501,7 +16498,7 @@
         <v>80</v>
       </c>
       <c r="Q223" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R223" s="19" t="s">
         <v>82</v>
@@ -16557,7 +16554,7 @@
         <v>80</v>
       </c>
       <c r="Q224" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R224" s="19" t="s">
         <v>82</v>
@@ -16613,7 +16610,7 @@
         <v>80</v>
       </c>
       <c r="Q225" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R225" s="19" t="s">
         <v>285</v>
@@ -16669,7 +16666,7 @@
         <v>80</v>
       </c>
       <c r="Q226" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R226" s="19" t="s">
         <v>82</v>
@@ -16725,7 +16722,7 @@
         <v>80</v>
       </c>
       <c r="Q227" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R227" s="19" t="s">
         <v>82</v>
@@ -16781,7 +16778,7 @@
         <v>80</v>
       </c>
       <c r="Q228" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R228" s="19" t="s">
         <v>85</v>
@@ -16837,7 +16834,7 @@
         <v>80</v>
       </c>
       <c r="Q229" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R229" s="19" t="s">
         <v>82</v>
@@ -16877,7 +16874,7 @@
         <v>-0.67069840000000003</v>
       </c>
       <c r="K230" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="L230" t="s">
         <v>99</v>
@@ -16893,7 +16890,7 @@
         <v>80</v>
       </c>
       <c r="Q230" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R230" s="19" t="s">
         <v>82</v>
@@ -16949,7 +16946,7 @@
         <v>80</v>
       </c>
       <c r="Q231" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R231" s="19" t="s">
         <v>82</v>
@@ -17005,7 +17002,7 @@
         <v>80</v>
       </c>
       <c r="Q232" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R232" s="19" t="s">
         <v>82</v>
@@ -17061,7 +17058,7 @@
         <v>80</v>
       </c>
       <c r="Q233" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R233" s="19" t="s">
         <v>82</v>
@@ -17117,7 +17114,7 @@
         <v>80</v>
       </c>
       <c r="Q234" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R234" s="19" t="s">
         <v>85</v>
@@ -17173,7 +17170,7 @@
         <v>80</v>
       </c>
       <c r="Q235" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R235" s="19" t="s">
         <v>82</v>
@@ -17229,7 +17226,7 @@
         <v>80</v>
       </c>
       <c r="Q236" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R236" s="19" t="s">
         <v>285</v>
@@ -17285,7 +17282,7 @@
         <v>80</v>
       </c>
       <c r="Q237" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R237" s="19" t="s">
         <v>82</v>
@@ -17341,7 +17338,7 @@
         <v>80</v>
       </c>
       <c r="Q238" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R238" s="19" t="s">
         <v>82</v>
@@ -17397,7 +17394,7 @@
         <v>80</v>
       </c>
       <c r="Q239" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R239" s="19" t="s">
         <v>85</v>
@@ -17453,7 +17450,7 @@
         <v>80</v>
       </c>
       <c r="Q240" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R240" s="19" t="s">
         <v>85</v>
@@ -17493,7 +17490,7 @@
         <v>-0.33615020000000001</v>
       </c>
       <c r="K241" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="L241" t="s">
         <v>99</v>
@@ -17509,7 +17506,7 @@
         <v>80</v>
       </c>
       <c r="Q241" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R241" s="19" t="s">
         <v>82</v>
@@ -17565,7 +17562,7 @@
         <v>80</v>
       </c>
       <c r="Q242" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R242" s="19" t="s">
         <v>82</v>
@@ -17621,7 +17618,7 @@
         <v>80</v>
       </c>
       <c r="Q243" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R243" s="19" t="s">
         <v>82</v>
@@ -17677,7 +17674,7 @@
         <v>80</v>
       </c>
       <c r="Q244" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R244" s="19" t="s">
         <v>82</v>
@@ -17733,7 +17730,7 @@
         <v>80</v>
       </c>
       <c r="Q245" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R245" s="19" t="s">
         <v>82</v>
@@ -17789,7 +17786,7 @@
         <v>80</v>
       </c>
       <c r="Q246" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R246" s="19" t="s">
         <v>82</v>
@@ -17845,7 +17842,7 @@
         <v>80</v>
       </c>
       <c r="Q247" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R247" s="19" t="s">
         <v>82</v>
@@ -17901,7 +17898,7 @@
         <v>80</v>
       </c>
       <c r="Q248" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R248" s="19" t="s">
         <v>82</v>
@@ -17956,7 +17953,7 @@
         <v>80</v>
       </c>
       <c r="Q249" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R249" s="19" t="s">
         <v>85</v>
@@ -18011,7 +18008,7 @@
         <v>80</v>
       </c>
       <c r="Q250" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="R250" s="19" t="s">
         <v>85</v>

--- a/datos/excursiones.xlsx
+++ b/datos/excursiones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josel\Documents\elaios_mapa\proyecto_mapa_excursiones\mapa_elaios\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98085444-6A91-492B-812E-ADDE34659AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67259905-77D8-4289-9548-48AB3CD52313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43290" yWindow="240" windowWidth="11340" windowHeight="10890" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2990,10 +2990,6 @@
     <t>https://es.wikiloc.com/rutas-senderismo/pico-pegueras-collada-de-tramasaguas-y-punta-bacibosa-desde-sin-194197281</t>
   </si>
   <si>
-    <t>Circular Piracés
-Jubierre (RGP)</t>
-  </si>
-  <si>
     <t>https://es.wikiloc.com/rutas-senderismo/aragon-circular-piraces-bco-los-olivares-cerro-patrilla-las-escapaduras-ermita-de-las-coronas-y-pen-123532298</t>
   </si>
   <si>
@@ -3178,6 +3174,9 @@
   </si>
   <si>
     <t>https://www.google.com/maps/place/50109+Alpartir,+Zaragoza/@41.4237559,-1.385757,1630m/data=!3m2!1e3!4b1!4m6!3m5!1s0xd5bf01a1d0c845f:0xb7407c698ed18fd5!8m2!3d41.4242518!4d-1.3794838!16s%2Fg%2F11cn5r51g7?entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Circular Piracés (RGP)</t>
   </si>
 </sst>
 </file>
@@ -3889,7 +3888,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -3943,7 +3942,7 @@
         <v>2025</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>93</v>
@@ -3999,10 +3998,10 @@
         <v>2025</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H3" t="s">
         <v>58</v>
@@ -4022,7 +4021,7 @@
         <v>97</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="8" t="s">
@@ -4056,7 +4055,7 @@
         <v>2025</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G4" t="s">
         <v>57</v>
@@ -4113,7 +4112,7 @@
         <v>2025</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G5" t="s">
         <v>53</v>
@@ -4170,7 +4169,7 @@
         <v>2025</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G6" t="s">
         <v>50</v>
@@ -4227,7 +4226,7 @@
         <v>2025</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G7" t="s">
         <v>47</v>
@@ -4284,7 +4283,7 @@
         <v>2025</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G8" t="s">
         <v>44</v>
@@ -4341,7 +4340,7 @@
         <v>2025</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G9" t="s">
         <v>42</v>
@@ -4398,7 +4397,7 @@
         <v>2025</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -4455,7 +4454,7 @@
         <v>2025</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G11" t="s">
         <v>37</v>
@@ -4478,7 +4477,7 @@
         <v>97</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>97</v>
@@ -4514,7 +4513,7 @@
         <v>2025</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G12" t="s">
         <v>33</v>
@@ -4571,7 +4570,7 @@
         <v>2025</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>28</v>
@@ -4630,7 +4629,7 @@
         <v>2025</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -4687,7 +4686,7 @@
         <v>2025</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
@@ -4744,7 +4743,7 @@
         <v>2025</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
@@ -4801,7 +4800,7 @@
         <v>2025</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G17" t="s">
         <v>16</v>
@@ -4858,7 +4857,7 @@
         <v>2025</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>11</v>
@@ -4917,7 +4916,7 @@
         <v>2025</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G19" t="s">
         <v>7</v>
@@ -4974,7 +4973,7 @@
         <v>2024</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G20" t="s">
         <v>273</v>
@@ -5033,7 +5032,7 @@
         <v>2024</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G21" t="s">
         <v>271</v>
@@ -5092,7 +5091,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G22" t="s">
         <v>289</v>
@@ -5149,7 +5148,7 @@
         <v>2024</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G23" t="s">
         <v>284</v>
@@ -5208,7 +5207,7 @@
         <v>2024</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G24" t="s">
         <v>292</v>
@@ -5228,7 +5227,7 @@
         <v>297</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" t="s">
@@ -5262,7 +5261,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G25" t="s">
         <v>291</v>
@@ -5321,7 +5320,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G26" t="s">
         <v>267</v>
@@ -5344,7 +5343,7 @@
         <v>97</v>
       </c>
       <c r="M26" s="18" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>268</v>
@@ -5380,7 +5379,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G27" t="s">
         <v>265</v>
@@ -5439,7 +5438,7 @@
         <v>2024</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G28" t="s">
         <v>301</v>
@@ -5498,7 +5497,7 @@
         <v>2024</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G29" t="s">
         <v>314</v>
@@ -5555,7 +5554,7 @@
         <v>2024</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G30" t="s">
         <v>307</v>
@@ -5614,7 +5613,7 @@
         <v>2024</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G31" t="s">
         <v>261</v>
@@ -5673,7 +5672,7 @@
         <v>2024</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G32" t="s">
         <v>321</v>
@@ -5696,7 +5695,7 @@
         <v>97</v>
       </c>
       <c r="M32" s="20" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" t="s">
@@ -5730,7 +5729,7 @@
         <v>2024</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>319</v>
@@ -5753,7 +5752,7 @@
         <v>97</v>
       </c>
       <c r="M33" s="20" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>260</v>
@@ -5789,7 +5788,7 @@
         <v>2024</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G34" t="s">
         <v>258</v>
@@ -5812,7 +5811,7 @@
         <v>97</v>
       </c>
       <c r="M34" s="20" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>259</v>
@@ -5848,7 +5847,7 @@
         <v>2024</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G35" t="s">
         <v>256</v>
@@ -5871,7 +5870,7 @@
         <v>97</v>
       </c>
       <c r="M35" s="20" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>257</v>
@@ -5907,7 +5906,7 @@
         <v>2024</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G36" t="s">
         <v>254</v>
@@ -5930,7 +5929,7 @@
         <v>97</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>255</v>
@@ -5966,7 +5965,7 @@
         <v>2023</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G37" t="s">
         <v>328</v>
@@ -5989,7 +5988,7 @@
         <v>97</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>253</v>
@@ -6025,7 +6024,7 @@
         <v>2023</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G38" t="s">
         <v>250</v>
@@ -6048,7 +6047,7 @@
         <v>97</v>
       </c>
       <c r="M38" s="21" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>251</v>
@@ -6084,7 +6083,7 @@
         <v>2023</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G39" t="s">
         <v>248</v>
@@ -6143,7 +6142,7 @@
         <v>2023</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G40" t="s">
         <v>246</v>
@@ -6166,7 +6165,7 @@
         <v>97</v>
       </c>
       <c r="M40" s="20" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>247</v>
@@ -6202,7 +6201,7 @@
         <v>2023</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G41" t="s">
         <v>244</v>
@@ -6219,13 +6218,13 @@
         <v>-0.23676420000000001</v>
       </c>
       <c r="K41" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="L41" t="s">
         <v>97</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>245</v>
@@ -6261,7 +6260,7 @@
         <v>2023</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G42" t="s">
         <v>341</v>
@@ -6278,13 +6277,13 @@
         <v>-0.23676420000000001</v>
       </c>
       <c r="K42" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="L42" t="s">
         <v>97</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>243</v>
@@ -6320,7 +6319,7 @@
         <v>2023</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G43" t="s">
         <v>338</v>
@@ -6343,7 +6342,7 @@
         <v>97</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>242</v>
@@ -6379,7 +6378,7 @@
         <v>2023</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G44" t="s">
         <v>344</v>
@@ -6436,7 +6435,7 @@
         <v>2023</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>345</v>
@@ -6459,7 +6458,7 @@
         <v>97</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>241</v>
@@ -6495,13 +6494,13 @@
         <v>2023</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G46" t="s">
         <v>347</v>
       </c>
       <c r="H46" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="I46" s="7" t="str">
         <f t="shared" si="1"/>
@@ -6512,13 +6511,13 @@
         <v>-0.16970170000000001</v>
       </c>
       <c r="K46" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L46" t="s">
         <v>97</v>
       </c>
       <c r="M46" s="20" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" t="s">
@@ -6534,7 +6533,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="28.8">
+    <row r="47" spans="1:18">
       <c r="A47" s="7" t="str">
         <f t="shared" si="3"/>
         <v>2023_05_27</v>
@@ -6552,13 +6551,13 @@
         <v>2023</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>981</v>
+        <v>1043</v>
       </c>
       <c r="H47" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="I47" s="7" t="str">
         <f t="shared" si="1"/>
@@ -6569,13 +6568,13 @@
         <v>-0.32057790000000003</v>
       </c>
       <c r="K47" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="L47" t="s">
         <v>97</v>
       </c>
       <c r="M47" s="20" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>240</v>
@@ -6611,7 +6610,7 @@
         <v>2023</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G48" t="s">
         <v>349</v>
@@ -6634,7 +6633,7 @@
         <v>97</v>
       </c>
       <c r="M48" s="20" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" t="s">
@@ -6668,7 +6667,7 @@
         <v>2023</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G49" t="s">
         <v>348</v>
@@ -6691,7 +6690,7 @@
         <v>97</v>
       </c>
       <c r="M49" s="20" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>239</v>
@@ -6727,7 +6726,7 @@
         <v>2023</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G50" t="s">
         <v>358</v>
@@ -6784,7 +6783,7 @@
         <v>2023</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G51" t="s">
         <v>359</v>
@@ -6843,13 +6842,13 @@
         <v>2023</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G52" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H52" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="I52" s="7" t="str">
         <f t="shared" si="1"/>
@@ -6860,13 +6859,13 @@
         <v>-0.8052433</v>
       </c>
       <c r="K52" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="L52" t="s">
         <v>97</v>
       </c>
       <c r="M52" s="20" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>237</v>
@@ -6902,7 +6901,7 @@
         <v>2022</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G53" t="s">
         <v>235</v>
@@ -6925,7 +6924,7 @@
         <v>97</v>
       </c>
       <c r="M53" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>236</v>
@@ -6961,7 +6960,7 @@
         <v>2022</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G54" t="s">
         <v>233</v>
@@ -7020,7 +7019,7 @@
         <v>2022</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G55" t="s">
         <v>231</v>
@@ -7043,7 +7042,7 @@
         <v>97</v>
       </c>
       <c r="M55" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" t="s">
@@ -7077,7 +7076,7 @@
         <v>2022</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G56" t="s">
         <v>231</v>
@@ -7100,7 +7099,7 @@
         <v>97</v>
       </c>
       <c r="M56" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>232</v>
@@ -7136,7 +7135,7 @@
         <v>2022</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G57" t="s">
         <v>229</v>
@@ -7159,7 +7158,7 @@
         <v>97</v>
       </c>
       <c r="M57" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" t="s">
@@ -7193,7 +7192,7 @@
         <v>2022</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G58" t="s">
         <v>229</v>
@@ -7216,7 +7215,7 @@
         <v>97</v>
       </c>
       <c r="M58" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>230</v>
@@ -7252,7 +7251,7 @@
         <v>2022</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G59" t="s">
         <v>227</v>
@@ -7275,7 +7274,7 @@
         <v>97</v>
       </c>
       <c r="M59" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>228</v>
@@ -7311,7 +7310,7 @@
         <v>2022</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G60" t="s">
         <v>374</v>
@@ -7334,7 +7333,7 @@
         <v>97</v>
       </c>
       <c r="M60" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" t="s">
@@ -7368,7 +7367,7 @@
         <v>2022</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>373</v>
@@ -7391,7 +7390,7 @@
         <v>97</v>
       </c>
       <c r="M61" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>226</v>
@@ -7427,7 +7426,7 @@
         <v>2022</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G62" t="s">
         <v>378</v>
@@ -7450,7 +7449,7 @@
         <v>97</v>
       </c>
       <c r="M62" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" t="s">
@@ -7484,7 +7483,7 @@
         <v>2022</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>377</v>
@@ -7507,7 +7506,7 @@
         <v>97</v>
       </c>
       <c r="M63" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>225</v>
@@ -7543,7 +7542,7 @@
         <v>2022</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G64" t="s">
         <v>223</v>
@@ -7566,7 +7565,7 @@
         <v>97</v>
       </c>
       <c r="M64" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>224</v>
@@ -7602,7 +7601,7 @@
         <v>2022</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G65" t="s">
         <v>383</v>
@@ -7625,7 +7624,7 @@
         <v>97</v>
       </c>
       <c r="M65" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" t="s">
@@ -7659,7 +7658,7 @@
         <v>2022</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G66" t="s">
         <v>221</v>
@@ -7682,7 +7681,7 @@
         <v>97</v>
       </c>
       <c r="M66" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>222</v>
@@ -7718,7 +7717,7 @@
         <v>2022</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G67" t="s">
         <v>391</v>
@@ -7741,7 +7740,7 @@
         <v>97</v>
       </c>
       <c r="M67" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" t="s">
@@ -7754,7 +7753,7 @@
         <v>79</v>
       </c>
       <c r="R67" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -7775,7 +7774,7 @@
         <v>2022</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G68" t="s">
         <v>219</v>
@@ -7798,7 +7797,7 @@
         <v>97</v>
       </c>
       <c r="M68" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>220</v>
@@ -7834,7 +7833,7 @@
         <v>2022</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G69" t="s">
         <v>217</v>
@@ -7857,7 +7856,7 @@
         <v>97</v>
       </c>
       <c r="M69" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>218</v>
@@ -7893,7 +7892,7 @@
         <v>2022</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G70" t="s">
         <v>215</v>
@@ -7916,7 +7915,7 @@
         <v>97</v>
       </c>
       <c r="M70" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>216</v>
@@ -7952,7 +7951,7 @@
         <v>2021</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G71" t="s">
         <v>213</v>
@@ -7975,7 +7974,7 @@
         <v>97</v>
       </c>
       <c r="M71" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>214</v>
@@ -8011,7 +8010,7 @@
         <v>2021</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G72" t="s">
         <v>211</v>
@@ -8034,7 +8033,7 @@
         <v>97</v>
       </c>
       <c r="M72" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>212</v>
@@ -8070,7 +8069,7 @@
         <v>2021</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G73" t="s">
         <v>209</v>
@@ -8093,7 +8092,7 @@
         <v>97</v>
       </c>
       <c r="M73" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>210</v>
@@ -8129,7 +8128,7 @@
         <v>2021</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G74" t="s">
         <v>205</v>
@@ -8152,7 +8151,7 @@
         <v>97</v>
       </c>
       <c r="M74" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>206</v>
@@ -8188,7 +8187,7 @@
         <v>2021</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G75" t="s">
         <v>405</v>
@@ -8211,7 +8210,7 @@
         <v>97</v>
       </c>
       <c r="M75" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" t="s">
@@ -8245,7 +8244,7 @@
         <v>2021</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G76" t="s">
         <v>103</v>
@@ -8268,7 +8267,7 @@
         <v>97</v>
       </c>
       <c r="M76" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" t="s">
@@ -8302,7 +8301,7 @@
         <v>2021</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>404</v>
@@ -8325,7 +8324,7 @@
         <v>97</v>
       </c>
       <c r="M77" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>208</v>
@@ -8360,7 +8359,7 @@
         <v>2021</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G78" s="15" t="s">
         <v>207</v>
@@ -8393,7 +8392,7 @@
         <v>78</v>
       </c>
       <c r="Q78" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R78" s="19" t="s">
         <v>80</v>
@@ -8416,7 +8415,7 @@
         <v>2021</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G79" s="15" t="s">
         <v>205</v>
@@ -8439,7 +8438,7 @@
         <v>97</v>
       </c>
       <c r="M79" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N79" s="3"/>
       <c r="O79" t="s">
@@ -8449,7 +8448,7 @@
         <v>78</v>
       </c>
       <c r="Q79" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R79" s="19" t="s">
         <v>83</v>
@@ -8472,7 +8471,7 @@
         <v>2020</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G80" s="15" t="s">
         <v>204</v>
@@ -8505,7 +8504,7 @@
         <v>78</v>
       </c>
       <c r="Q80" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R80" s="19" t="s">
         <v>83</v>
@@ -8528,7 +8527,7 @@
         <v>2020</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G81" s="15" t="s">
         <v>117</v>
@@ -8551,7 +8550,7 @@
         <v>97</v>
       </c>
       <c r="M81" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N81" s="3"/>
       <c r="O81" t="s">
@@ -8561,7 +8560,7 @@
         <v>78</v>
       </c>
       <c r="Q81" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R81" s="19" t="s">
         <v>83</v>
@@ -8584,7 +8583,7 @@
         <v>2020</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G82" s="15" t="s">
         <v>203</v>
@@ -8607,7 +8606,7 @@
         <v>97</v>
       </c>
       <c r="M82" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N82" s="3"/>
       <c r="O82" t="s">
@@ -8617,7 +8616,7 @@
         <v>974</v>
       </c>
       <c r="Q82" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R82" s="19" t="s">
         <v>80</v>
@@ -8640,7 +8639,7 @@
         <v>2020</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G83" s="15" t="s">
         <v>202</v>
@@ -8673,7 +8672,7 @@
         <v>78</v>
       </c>
       <c r="Q83" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R83" s="19" t="s">
         <v>80</v>
@@ -8696,7 +8695,7 @@
         <v>2019</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G84" s="15" t="s">
         <v>106</v>
@@ -8729,7 +8728,7 @@
         <v>78</v>
       </c>
       <c r="Q84" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R84" s="19" t="s">
         <v>80</v>
@@ -8752,7 +8751,7 @@
         <v>2019</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G85" s="15" t="s">
         <v>425</v>
@@ -8785,7 +8784,7 @@
         <v>78</v>
       </c>
       <c r="Q85" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R85" s="19" t="s">
         <v>80</v>
@@ -8808,7 +8807,7 @@
         <v>2019</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G86" s="15" t="s">
         <v>201</v>
@@ -8841,7 +8840,7 @@
         <v>78</v>
       </c>
       <c r="Q86" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R86" s="19" t="s">
         <v>80</v>
@@ -8864,7 +8863,7 @@
         <v>2019</v>
       </c>
       <c r="F87" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G87" s="15" t="s">
         <v>429</v>
@@ -8897,7 +8896,7 @@
         <v>78</v>
       </c>
       <c r="Q87" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R87" s="19" t="s">
         <v>288</v>
@@ -8920,7 +8919,7 @@
         <v>2019</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G88" s="15" t="s">
         <v>431</v>
@@ -8953,7 +8952,7 @@
         <v>78</v>
       </c>
       <c r="Q88" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R88" s="19" t="s">
         <v>80</v>
@@ -8976,13 +8975,13 @@
         <v>2019</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G89" s="15" t="s">
         <v>200</v>
       </c>
       <c r="H89" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="I89" s="7" t="str">
         <f t="shared" si="5"/>
@@ -8993,7 +8992,7 @@
         <v>-9.1917266000000009</v>
       </c>
       <c r="K89" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="L89" t="s">
         <v>97</v>
@@ -9009,10 +9008,10 @@
         <v>78</v>
       </c>
       <c r="Q89" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R89" s="19" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -9032,7 +9031,7 @@
         <v>2019</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G90" s="15" t="s">
         <v>434</v>
@@ -9065,7 +9064,7 @@
         <v>298</v>
       </c>
       <c r="Q90" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R90" s="19" t="s">
         <v>80</v>
@@ -9088,7 +9087,7 @@
         <v>2019</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G91" s="15" t="s">
         <v>435</v>
@@ -9121,7 +9120,7 @@
         <v>298</v>
       </c>
       <c r="Q91" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R91" s="19" t="s">
         <v>311</v>
@@ -9144,7 +9143,7 @@
         <v>2019</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G92" s="15" t="s">
         <v>199</v>
@@ -9177,7 +9176,7 @@
         <v>78</v>
       </c>
       <c r="Q92" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R92" s="19" t="s">
         <v>80</v>
@@ -9200,13 +9199,13 @@
         <v>2019</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G93" s="15" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H93" t="s">
         <v>1027</v>
-      </c>
-      <c r="H93" t="s">
-        <v>1028</v>
       </c>
       <c r="I93" s="7" t="str">
         <f t="shared" si="5"/>
@@ -9217,13 +9216,13 @@
         <v>0.39274419999999999</v>
       </c>
       <c r="K93" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="L93" t="s">
         <v>97</v>
       </c>
       <c r="M93" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" t="s">
@@ -9233,7 +9232,7 @@
         <v>78</v>
       </c>
       <c r="Q93" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R93" s="19" t="s">
         <v>80</v>
@@ -9256,7 +9255,7 @@
         <v>2019</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G94" s="15" t="s">
         <v>440</v>
@@ -9289,7 +9288,7 @@
         <v>78</v>
       </c>
       <c r="Q94" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R94" s="19" t="s">
         <v>80</v>
@@ -9312,7 +9311,7 @@
         <v>2019</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G95" s="15" t="s">
         <v>198</v>
@@ -9345,7 +9344,7 @@
         <v>78</v>
       </c>
       <c r="Q95" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R95" s="19" t="s">
         <v>83</v>
@@ -9368,7 +9367,7 @@
         <v>2019</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G96" s="15" t="s">
         <v>197</v>
@@ -9401,7 +9400,7 @@
         <v>78</v>
       </c>
       <c r="Q96" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R96" s="19" t="s">
         <v>281</v>
@@ -9424,7 +9423,7 @@
         <v>2019</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G97" s="15" t="s">
         <v>195</v>
@@ -9447,7 +9446,7 @@
         <v>97</v>
       </c>
       <c r="M97" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" t="s">
@@ -9457,10 +9456,10 @@
         <v>78</v>
       </c>
       <c r="Q97" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R97" s="19" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -9480,7 +9479,7 @@
         <v>2019</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G98" s="15" t="s">
         <v>196</v>
@@ -9503,7 +9502,7 @@
         <v>97</v>
       </c>
       <c r="M98" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" t="s">
@@ -9513,7 +9512,7 @@
         <v>974</v>
       </c>
       <c r="Q98" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R98" s="19" t="s">
         <v>80</v>
@@ -9536,7 +9535,7 @@
         <v>2019</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G99" s="15" t="s">
         <v>114</v>
@@ -9569,7 +9568,7 @@
         <v>78</v>
       </c>
       <c r="Q99" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R99" s="19" t="s">
         <v>80</v>
@@ -9592,7 +9591,7 @@
         <v>2018</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G100" s="15" t="s">
         <v>194</v>
@@ -9615,7 +9614,7 @@
         <v>97</v>
       </c>
       <c r="M100" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N100" s="3"/>
       <c r="O100" t="s">
@@ -9625,7 +9624,7 @@
         <v>78</v>
       </c>
       <c r="Q100" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R100" s="19" t="s">
         <v>83</v>
@@ -9648,13 +9647,13 @@
         <v>2018</v>
       </c>
       <c r="F101" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G101" s="15" t="s">
         <v>193</v>
       </c>
       <c r="H101" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="I101" s="7" t="str">
         <f t="shared" si="5"/>
@@ -9665,7 +9664,7 @@
         <v>-3.3156636000000002</v>
       </c>
       <c r="K101" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="L101" t="s">
         <v>97</v>
@@ -9681,10 +9680,10 @@
         <v>78</v>
       </c>
       <c r="Q101" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R101" s="19" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -9704,7 +9703,7 @@
         <v>2018</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G102" s="15" t="s">
         <v>193</v>
@@ -9737,10 +9736,10 @@
         <v>78</v>
       </c>
       <c r="Q102" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R102" s="19" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -9760,7 +9759,7 @@
         <v>2018</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G103" s="15" t="s">
         <v>192</v>
@@ -9793,7 +9792,7 @@
         <v>78</v>
       </c>
       <c r="Q103" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R103" s="19" t="s">
         <v>80</v>
@@ -9816,10 +9815,10 @@
         <v>2018</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H104" t="s">
         <v>457</v>
@@ -9849,7 +9848,7 @@
         <v>78</v>
       </c>
       <c r="Q104" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R104" s="19" t="s">
         <v>311</v>
@@ -9872,7 +9871,7 @@
         <v>2018</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>191</v>
@@ -9905,10 +9904,10 @@
         <v>78</v>
       </c>
       <c r="Q105" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R105" s="19" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -9928,7 +9927,7 @@
         <v>2018</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G106" s="15" t="s">
         <v>190</v>
@@ -9951,7 +9950,7 @@
         <v>97</v>
       </c>
       <c r="M106" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N106" s="3"/>
       <c r="O106" t="s">
@@ -9961,7 +9960,7 @@
         <v>78</v>
       </c>
       <c r="Q106" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R106" s="19" t="s">
         <v>80</v>
@@ -9984,7 +9983,7 @@
         <v>2018</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G107" s="15" t="s">
         <v>189</v>
@@ -10017,7 +10016,7 @@
         <v>78</v>
       </c>
       <c r="Q107" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R107" s="19" t="s">
         <v>84</v>
@@ -10040,7 +10039,7 @@
         <v>2018</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G108" s="15" t="s">
         <v>187</v>
@@ -10073,7 +10072,7 @@
         <v>78</v>
       </c>
       <c r="Q108" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R108" s="19" t="s">
         <v>80</v>
@@ -10096,7 +10095,7 @@
         <v>2018</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G109" s="15" t="s">
         <v>188</v>
@@ -10129,7 +10128,7 @@
         <v>78</v>
       </c>
       <c r="Q109" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R109" s="19" t="s">
         <v>80</v>
@@ -10152,7 +10151,7 @@
         <v>2018</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G110" s="15" t="s">
         <v>186</v>
@@ -10185,7 +10184,7 @@
         <v>78</v>
       </c>
       <c r="Q110" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R110" s="19" t="s">
         <v>80</v>
@@ -10208,10 +10207,10 @@
         <v>2018</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H111" t="s">
         <v>470</v>
@@ -10241,7 +10240,7 @@
         <v>78</v>
       </c>
       <c r="Q111" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R111" s="19" t="s">
         <v>80</v>
@@ -10264,7 +10263,7 @@
         <v>2018</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G112" s="15" t="s">
         <v>185</v>
@@ -10297,7 +10296,7 @@
         <v>78</v>
       </c>
       <c r="Q112" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R112" s="19" t="s">
         <v>80</v>
@@ -10320,7 +10319,7 @@
         <v>2018</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G113" s="15" t="s">
         <v>184</v>
@@ -10353,7 +10352,7 @@
         <v>78</v>
       </c>
       <c r="Q113" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R113" s="19" t="s">
         <v>80</v>
@@ -10376,7 +10375,7 @@
         <v>2017</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G114" s="15" t="s">
         <v>183</v>
@@ -10409,7 +10408,7 @@
         <v>78</v>
       </c>
       <c r="Q114" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R114" s="19" t="s">
         <v>281</v>
@@ -10432,7 +10431,7 @@
         <v>2017</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G115" s="15" t="s">
         <v>182</v>
@@ -10465,7 +10464,7 @@
         <v>78</v>
       </c>
       <c r="Q115" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R115" s="19" t="s">
         <v>80</v>
@@ -10488,7 +10487,7 @@
         <v>2017</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G116" s="15" t="s">
         <v>181</v>
@@ -10521,7 +10520,7 @@
         <v>78</v>
       </c>
       <c r="Q116" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R116" s="19" t="s">
         <v>281</v>
@@ -10544,7 +10543,7 @@
         <v>2017</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G117" s="15" t="s">
         <v>481</v>
@@ -10577,7 +10576,7 @@
         <v>78</v>
       </c>
       <c r="Q117" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R117" s="19" t="s">
         <v>80</v>
@@ -10600,7 +10599,7 @@
         <v>2017</v>
       </c>
       <c r="F118" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G118" s="15" t="s">
         <v>482</v>
@@ -10633,7 +10632,7 @@
         <v>78</v>
       </c>
       <c r="Q118" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R118" s="19" t="s">
         <v>80</v>
@@ -10656,7 +10655,7 @@
         <v>2017</v>
       </c>
       <c r="F119" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G119" s="15" t="s">
         <v>180</v>
@@ -10689,7 +10688,7 @@
         <v>78</v>
       </c>
       <c r="Q119" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R119" s="19" t="s">
         <v>80</v>
@@ -10712,7 +10711,7 @@
         <v>2017</v>
       </c>
       <c r="F120" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G120" s="15" t="s">
         <v>179</v>
@@ -10735,7 +10734,7 @@
         <v>97</v>
       </c>
       <c r="M120" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N120" s="3"/>
       <c r="O120" t="s">
@@ -10745,7 +10744,7 @@
         <v>78</v>
       </c>
       <c r="Q120" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R120" s="19" t="s">
         <v>80</v>
@@ -10768,7 +10767,7 @@
         <v>2017</v>
       </c>
       <c r="F121" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G121" s="15" t="s">
         <v>177</v>
@@ -10791,7 +10790,7 @@
         <v>97</v>
       </c>
       <c r="M121" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N121" s="3"/>
       <c r="O121" t="s">
@@ -10801,10 +10800,10 @@
         <v>78</v>
       </c>
       <c r="Q121" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R121" s="19" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -10824,7 +10823,7 @@
         <v>2017</v>
       </c>
       <c r="F122" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G122" s="15" t="s">
         <v>178</v>
@@ -10857,7 +10856,7 @@
         <v>78</v>
       </c>
       <c r="Q122" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R122" s="19" t="s">
         <v>80</v>
@@ -10880,13 +10879,13 @@
         <v>2017</v>
       </c>
       <c r="F123" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G123" s="15" t="s">
         <v>493</v>
       </c>
       <c r="H123" s="15" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="I123" s="7" t="str">
         <f t="shared" si="5"/>
@@ -10897,13 +10896,13 @@
         <v>-0.31771080000000002</v>
       </c>
       <c r="K123" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="L123" t="s">
         <v>97</v>
       </c>
       <c r="M123" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N123" s="3"/>
       <c r="O123" t="s">
@@ -10913,7 +10912,7 @@
         <v>78</v>
       </c>
       <c r="Q123" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R123" s="19" t="s">
         <v>80</v>
@@ -10936,7 +10935,7 @@
         <v>2017</v>
       </c>
       <c r="F124" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G124" s="15" t="s">
         <v>492</v>
@@ -10969,7 +10968,7 @@
         <v>78</v>
       </c>
       <c r="Q124" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R124" s="19" t="s">
         <v>80</v>
@@ -10992,7 +10991,7 @@
         <v>2017</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G125" s="15" t="s">
         <v>170</v>
@@ -11025,7 +11024,7 @@
         <v>78</v>
       </c>
       <c r="Q125" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R125" s="19" t="s">
         <v>80</v>
@@ -11048,7 +11047,7 @@
         <v>2017</v>
       </c>
       <c r="F126" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G126" s="15" t="s">
         <v>176</v>
@@ -11081,7 +11080,7 @@
         <v>974</v>
       </c>
       <c r="Q126" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R126" s="19" t="s">
         <v>80</v>
@@ -11104,7 +11103,7 @@
         <v>2017</v>
       </c>
       <c r="F127" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G127" s="15" t="s">
         <v>175</v>
@@ -11137,7 +11136,7 @@
         <v>78</v>
       </c>
       <c r="Q127" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R127" s="19" t="s">
         <v>80</v>
@@ -11160,7 +11159,7 @@
         <v>2016</v>
       </c>
       <c r="F128" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G128" s="15" t="s">
         <v>174</v>
@@ -11193,7 +11192,7 @@
         <v>78</v>
       </c>
       <c r="Q128" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R128" s="19" t="s">
         <v>80</v>
@@ -11216,7 +11215,7 @@
         <v>2016</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G129" s="15" t="s">
         <v>173</v>
@@ -11249,10 +11248,10 @@
         <v>78</v>
       </c>
       <c r="Q129" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R129" s="19" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -11272,7 +11271,7 @@
         <v>2016</v>
       </c>
       <c r="F130" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G130" s="15" t="s">
         <v>172</v>
@@ -11305,7 +11304,7 @@
         <v>78</v>
       </c>
       <c r="Q130" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R130" s="19" t="s">
         <v>80</v>
@@ -11328,7 +11327,7 @@
         <v>2016</v>
       </c>
       <c r="F131" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G131" s="15" t="s">
         <v>508</v>
@@ -11351,7 +11350,7 @@
         <v>97</v>
       </c>
       <c r="M131" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N131" s="3"/>
       <c r="O131" t="s">
@@ -11361,7 +11360,7 @@
         <v>78</v>
       </c>
       <c r="Q131" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R131" s="19" t="s">
         <v>80</v>
@@ -11384,7 +11383,7 @@
         <v>2016</v>
       </c>
       <c r="F132" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G132" s="15" t="s">
         <v>506</v>
@@ -11417,7 +11416,7 @@
         <v>78</v>
       </c>
       <c r="Q132" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R132" s="19" t="s">
         <v>80</v>
@@ -11440,7 +11439,7 @@
         <v>2016</v>
       </c>
       <c r="F133" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G133" s="15" t="s">
         <v>171</v>
@@ -11463,7 +11462,7 @@
         <v>97</v>
       </c>
       <c r="M133" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N133" s="3"/>
       <c r="O133" t="s">
@@ -11473,7 +11472,7 @@
         <v>78</v>
       </c>
       <c r="Q133" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R133" s="19" t="s">
         <v>84</v>
@@ -11496,7 +11495,7 @@
         <v>2016</v>
       </c>
       <c r="F134" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G134" s="15" t="s">
         <v>512</v>
@@ -11529,7 +11528,7 @@
         <v>78</v>
       </c>
       <c r="Q134" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R134" s="19" t="s">
         <v>281</v>
@@ -11552,7 +11551,7 @@
         <v>2016</v>
       </c>
       <c r="F135" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G135" s="15" t="s">
         <v>514</v>
@@ -11585,7 +11584,7 @@
         <v>78</v>
       </c>
       <c r="Q135" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R135" s="19" t="s">
         <v>81</v>
@@ -11608,7 +11607,7 @@
         <v>2016</v>
       </c>
       <c r="F136" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G136" s="15" t="s">
         <v>170</v>
@@ -11641,7 +11640,7 @@
         <v>78</v>
       </c>
       <c r="Q136" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R136" s="19" t="s">
         <v>80</v>
@@ -11664,7 +11663,7 @@
         <v>2016</v>
       </c>
       <c r="F137" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G137" s="15" t="s">
         <v>169</v>
@@ -11687,7 +11686,7 @@
         <v>97</v>
       </c>
       <c r="M137" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N137" s="3"/>
       <c r="O137" t="s">
@@ -11697,7 +11696,7 @@
         <v>974</v>
       </c>
       <c r="Q137" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R137" s="19" t="s">
         <v>80</v>
@@ -11720,7 +11719,7 @@
         <v>2016</v>
       </c>
       <c r="F138" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G138" s="15" t="s">
         <v>168</v>
@@ -11753,7 +11752,7 @@
         <v>78</v>
       </c>
       <c r="Q138" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R138" s="19" t="s">
         <v>281</v>
@@ -11776,7 +11775,7 @@
         <v>2015</v>
       </c>
       <c r="F139" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G139" s="15" t="s">
         <v>167</v>
@@ -11809,7 +11808,7 @@
         <v>78</v>
       </c>
       <c r="Q139" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R139" s="19" t="s">
         <v>281</v>
@@ -11832,7 +11831,7 @@
         <v>2015</v>
       </c>
       <c r="F140" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G140" s="15" t="s">
         <v>166</v>
@@ -11865,7 +11864,7 @@
         <v>78</v>
       </c>
       <c r="Q140" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R140" s="19" t="s">
         <v>80</v>
@@ -11888,7 +11887,7 @@
         <v>2015</v>
       </c>
       <c r="F141" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G141" s="15" t="s">
         <v>525</v>
@@ -11921,7 +11920,7 @@
         <v>78</v>
       </c>
       <c r="Q141" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R141" s="19" t="s">
         <v>80</v>
@@ -11944,7 +11943,7 @@
         <v>2015</v>
       </c>
       <c r="F142" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G142" s="15" t="s">
         <v>526</v>
@@ -11977,7 +11976,7 @@
         <v>78</v>
       </c>
       <c r="Q142" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R142" s="19" t="s">
         <v>80</v>
@@ -12000,7 +11999,7 @@
         <v>2015</v>
       </c>
       <c r="F143" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G143" s="15" t="s">
         <v>528</v>
@@ -12033,7 +12032,7 @@
         <v>78</v>
       </c>
       <c r="Q143" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R143" s="19" t="s">
         <v>80</v>
@@ -12056,7 +12055,7 @@
         <v>2015</v>
       </c>
       <c r="F144" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G144" s="15" t="s">
         <v>530</v>
@@ -12089,7 +12088,7 @@
         <v>78</v>
       </c>
       <c r="Q144" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R144" s="19" t="s">
         <v>80</v>
@@ -12112,7 +12111,7 @@
         <v>2015</v>
       </c>
       <c r="F145" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G145" s="15" t="s">
         <v>533</v>
@@ -12135,7 +12134,7 @@
         <v>97</v>
       </c>
       <c r="M145" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N145" s="3"/>
       <c r="O145" t="s">
@@ -12145,7 +12144,7 @@
         <v>78</v>
       </c>
       <c r="Q145" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R145" s="19" t="s">
         <v>80</v>
@@ -12168,7 +12167,7 @@
         <v>2015</v>
       </c>
       <c r="F146" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G146" s="15" t="s">
         <v>535</v>
@@ -12201,7 +12200,7 @@
         <v>78</v>
       </c>
       <c r="Q146" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R146" s="19" t="s">
         <v>80</v>
@@ -12224,7 +12223,7 @@
         <v>2015</v>
       </c>
       <c r="F147" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G147" s="15" t="s">
         <v>537</v>
@@ -12257,7 +12256,7 @@
         <v>78</v>
       </c>
       <c r="Q147" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R147" s="19" t="s">
         <v>80</v>
@@ -12280,7 +12279,7 @@
         <v>2015</v>
       </c>
       <c r="F148" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G148" s="15" t="s">
         <v>223</v>
@@ -12313,7 +12312,7 @@
         <v>78</v>
       </c>
       <c r="Q148" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R148" s="19" t="s">
         <v>80</v>
@@ -12336,7 +12335,7 @@
         <v>2015</v>
       </c>
       <c r="F149" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G149" s="15" t="s">
         <v>541</v>
@@ -12369,7 +12368,7 @@
         <v>78</v>
       </c>
       <c r="Q149" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R149" s="19" t="s">
         <v>80</v>
@@ -12392,7 +12391,7 @@
         <v>2015</v>
       </c>
       <c r="F150" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G150" s="15" t="s">
         <v>543</v>
@@ -12425,7 +12424,7 @@
         <v>78</v>
       </c>
       <c r="Q150" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R150" s="19" t="s">
         <v>80</v>
@@ -12448,7 +12447,7 @@
         <v>2015</v>
       </c>
       <c r="F151" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G151" s="15" t="s">
         <v>545</v>
@@ -12481,7 +12480,7 @@
         <v>78</v>
       </c>
       <c r="Q151" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R151" s="19" t="s">
         <v>80</v>
@@ -12504,7 +12503,7 @@
         <v>2015</v>
       </c>
       <c r="F152" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G152" s="15" t="s">
         <v>547</v>
@@ -12537,7 +12536,7 @@
         <v>78</v>
       </c>
       <c r="Q152" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R152" s="19" t="s">
         <v>330</v>
@@ -12560,7 +12559,7 @@
         <v>2015</v>
       </c>
       <c r="F153" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G153" s="15" t="s">
         <v>165</v>
@@ -12593,7 +12592,7 @@
         <v>78</v>
       </c>
       <c r="Q153" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R153" s="19" t="s">
         <v>311</v>
@@ -12616,7 +12615,7 @@
         <v>2015</v>
       </c>
       <c r="F154" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G154" s="15" t="s">
         <v>163</v>
@@ -12649,7 +12648,7 @@
         <v>78</v>
       </c>
       <c r="Q154" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R154" s="19" t="s">
         <v>81</v>
@@ -12672,7 +12671,7 @@
         <v>2015</v>
       </c>
       <c r="F155" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G155" s="15" t="s">
         <v>164</v>
@@ -12705,7 +12704,7 @@
         <v>974</v>
       </c>
       <c r="Q155" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R155" s="19" t="s">
         <v>80</v>
@@ -12728,7 +12727,7 @@
         <v>2015</v>
       </c>
       <c r="F156" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G156" s="15" t="s">
         <v>555</v>
@@ -12761,7 +12760,7 @@
         <v>976</v>
       </c>
       <c r="Q156" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R156" s="19" t="s">
         <v>80</v>
@@ -12784,7 +12783,7 @@
         <v>2015</v>
       </c>
       <c r="F157" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G157" s="15" t="s">
         <v>557</v>
@@ -12817,7 +12816,7 @@
         <v>78</v>
       </c>
       <c r="Q157" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R157" s="19" t="s">
         <v>281</v>
@@ -12840,7 +12839,7 @@
         <v>2014</v>
       </c>
       <c r="F158" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G158" s="15" t="s">
         <v>162</v>
@@ -12873,7 +12872,7 @@
         <v>78</v>
       </c>
       <c r="Q158" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R158" s="19" t="s">
         <v>80</v>
@@ -12896,7 +12895,7 @@
         <v>2014</v>
       </c>
       <c r="F159" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G159" s="15" t="s">
         <v>562</v>
@@ -12929,7 +12928,7 @@
         <v>78</v>
       </c>
       <c r="Q159" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R159" s="19" t="s">
         <v>80</v>
@@ -12952,7 +12951,7 @@
         <v>2014</v>
       </c>
       <c r="F160" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G160" s="15" t="s">
         <v>564</v>
@@ -12985,7 +12984,7 @@
         <v>78</v>
       </c>
       <c r="Q160" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R160" s="19" t="s">
         <v>80</v>
@@ -13008,7 +13007,7 @@
         <v>2014</v>
       </c>
       <c r="F161" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G161" s="15" t="s">
         <v>161</v>
@@ -13041,7 +13040,7 @@
         <v>78</v>
       </c>
       <c r="Q161" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R161" s="19" t="s">
         <v>84</v>
@@ -13064,7 +13063,7 @@
         <v>2014</v>
       </c>
       <c r="F162" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G162" s="15" t="s">
         <v>568</v>
@@ -13097,7 +13096,7 @@
         <v>78</v>
       </c>
       <c r="Q162" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R162" s="19" t="s">
         <v>80</v>
@@ -13120,7 +13119,7 @@
         <v>2014</v>
       </c>
       <c r="F163" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G163" s="15" t="s">
         <v>570</v>
@@ -13153,7 +13152,7 @@
         <v>78</v>
       </c>
       <c r="Q163" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R163" s="19" t="s">
         <v>80</v>
@@ -13176,7 +13175,7 @@
         <v>2014</v>
       </c>
       <c r="F164" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G164" s="15" t="s">
         <v>160</v>
@@ -13209,7 +13208,7 @@
         <v>78</v>
       </c>
       <c r="Q164" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R164" s="19" t="s">
         <v>80</v>
@@ -13232,7 +13231,7 @@
         <v>2014</v>
       </c>
       <c r="F165" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G165" s="15" t="s">
         <v>159</v>
@@ -13265,7 +13264,7 @@
         <v>78</v>
       </c>
       <c r="Q165" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R165" s="19" t="s">
         <v>80</v>
@@ -13288,7 +13287,7 @@
         <v>2014</v>
       </c>
       <c r="F166" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G166" s="15" t="s">
         <v>158</v>
@@ -13321,7 +13320,7 @@
         <v>78</v>
       </c>
       <c r="Q166" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R166" s="19" t="s">
         <v>80</v>
@@ -13344,7 +13343,7 @@
         <v>2014</v>
       </c>
       <c r="F167" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G167" s="15" t="s">
         <v>576</v>
@@ -13377,7 +13376,7 @@
         <v>78</v>
       </c>
       <c r="Q167" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R167" s="19" t="s">
         <v>83</v>
@@ -13400,7 +13399,7 @@
         <v>2014</v>
       </c>
       <c r="F168" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G168" s="15" t="s">
         <v>578</v>
@@ -13433,7 +13432,7 @@
         <v>78</v>
       </c>
       <c r="Q168" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R168" s="19" t="s">
         <v>80</v>
@@ -13456,7 +13455,7 @@
         <v>2014</v>
       </c>
       <c r="F169" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G169" s="15" t="s">
         <v>580</v>
@@ -13489,7 +13488,7 @@
         <v>78</v>
       </c>
       <c r="Q169" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R169" s="19" t="s">
         <v>80</v>
@@ -13512,7 +13511,7 @@
         <v>2014</v>
       </c>
       <c r="F170" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G170" s="15" t="s">
         <v>582</v>
@@ -13545,7 +13544,7 @@
         <v>78</v>
       </c>
       <c r="Q170" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R170" s="19" t="s">
         <v>80</v>
@@ -13568,7 +13567,7 @@
         <v>2014</v>
       </c>
       <c r="F171" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G171" s="15" t="s">
         <v>157</v>
@@ -13601,7 +13600,7 @@
         <v>974</v>
       </c>
       <c r="Q171" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R171" s="19" t="s">
         <v>83</v>
@@ -13624,7 +13623,7 @@
         <v>2014</v>
       </c>
       <c r="F172" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G172" s="15" t="s">
         <v>156</v>
@@ -13657,7 +13656,7 @@
         <v>974</v>
       </c>
       <c r="Q172" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R172" s="19" t="s">
         <v>80</v>
@@ -13680,7 +13679,7 @@
         <v>2014</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G173" s="15" t="s">
         <v>155</v>
@@ -13713,7 +13712,7 @@
         <v>78</v>
       </c>
       <c r="Q173" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R173" s="19" t="s">
         <v>83</v>
@@ -13736,7 +13735,7 @@
         <v>2013</v>
       </c>
       <c r="F174" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G174" s="15" t="s">
         <v>154</v>
@@ -13769,7 +13768,7 @@
         <v>78</v>
       </c>
       <c r="Q174" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R174" s="19" t="s">
         <v>281</v>
@@ -13792,7 +13791,7 @@
         <v>2013</v>
       </c>
       <c r="F175" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G175" s="15" t="s">
         <v>153</v>
@@ -13825,7 +13824,7 @@
         <v>78</v>
       </c>
       <c r="Q175" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R175" s="19" t="s">
         <v>80</v>
@@ -13848,7 +13847,7 @@
         <v>2013</v>
       </c>
       <c r="F176" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G176" s="15" t="s">
         <v>152</v>
@@ -13881,7 +13880,7 @@
         <v>78</v>
       </c>
       <c r="Q176" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R176" s="19" t="s">
         <v>80</v>
@@ -13904,7 +13903,7 @@
         <v>2013</v>
       </c>
       <c r="F177" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G177" s="15" t="s">
         <v>594</v>
@@ -13937,7 +13936,7 @@
         <v>298</v>
       </c>
       <c r="Q177" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R177" s="19" t="s">
         <v>80</v>
@@ -13960,7 +13959,7 @@
         <v>2013</v>
       </c>
       <c r="F178" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G178" s="15" t="s">
         <v>151</v>
@@ -13993,7 +13992,7 @@
         <v>298</v>
       </c>
       <c r="Q178" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R178" s="19" t="s">
         <v>80</v>
@@ -14016,7 +14015,7 @@
         <v>2013</v>
       </c>
       <c r="F179" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G179" s="15" t="s">
         <v>597</v>
@@ -14049,7 +14048,7 @@
         <v>78</v>
       </c>
       <c r="Q179" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R179" s="19" t="s">
         <v>80</v>
@@ -14072,7 +14071,7 @@
         <v>2013</v>
       </c>
       <c r="F180" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G180" s="15" t="s">
         <v>599</v>
@@ -14105,7 +14104,7 @@
         <v>78</v>
       </c>
       <c r="Q180" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R180" s="19" t="s">
         <v>80</v>
@@ -14128,7 +14127,7 @@
         <v>2013</v>
       </c>
       <c r="F181" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G181" s="15" t="s">
         <v>601</v>
@@ -14161,7 +14160,7 @@
         <v>78</v>
       </c>
       <c r="Q181" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R181" s="19" t="s">
         <v>80</v>
@@ -14184,7 +14183,7 @@
         <v>2013</v>
       </c>
       <c r="F182" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G182" s="15" t="s">
         <v>150</v>
@@ -14217,7 +14216,7 @@
         <v>78</v>
       </c>
       <c r="Q182" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R182" s="19" t="s">
         <v>80</v>
@@ -14240,7 +14239,7 @@
         <v>2013</v>
       </c>
       <c r="F183" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G183" s="15" t="s">
         <v>605</v>
@@ -14273,7 +14272,7 @@
         <v>78</v>
       </c>
       <c r="Q183" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R183" s="19" t="s">
         <v>281</v>
@@ -14296,7 +14295,7 @@
         <v>2013</v>
       </c>
       <c r="F184" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G184" s="15" t="s">
         <v>607</v>
@@ -14329,7 +14328,7 @@
         <v>78</v>
       </c>
       <c r="Q184" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R184" s="19" t="s">
         <v>281</v>
@@ -14352,7 +14351,7 @@
         <v>2013</v>
       </c>
       <c r="F185" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G185" s="15" t="s">
         <v>609</v>
@@ -14385,7 +14384,7 @@
         <v>78</v>
       </c>
       <c r="Q185" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R185" s="19" t="s">
         <v>357</v>
@@ -14408,7 +14407,7 @@
         <v>2013</v>
       </c>
       <c r="F186" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G186" s="15" t="s">
         <v>610</v>
@@ -14441,7 +14440,7 @@
         <v>78</v>
       </c>
       <c r="Q186" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R186" s="19" t="s">
         <v>390</v>
@@ -14464,7 +14463,7 @@
         <v>2013</v>
       </c>
       <c r="F187" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G187" s="15" t="s">
         <v>149</v>
@@ -14497,7 +14496,7 @@
         <v>78</v>
       </c>
       <c r="Q187" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R187" s="19" t="s">
         <v>311</v>
@@ -14520,7 +14519,7 @@
         <v>2013</v>
       </c>
       <c r="F188" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G188" s="15" t="s">
         <v>148</v>
@@ -14553,7 +14552,7 @@
         <v>78</v>
       </c>
       <c r="Q188" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R188" s="19" t="s">
         <v>80</v>
@@ -14576,10 +14575,10 @@
         <v>2013</v>
       </c>
       <c r="F189" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G189" s="15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H189" s="15" t="s">
         <v>147</v>
@@ -14609,7 +14608,7 @@
         <v>78</v>
       </c>
       <c r="Q189" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R189" s="19" t="s">
         <v>80</v>
@@ -14632,7 +14631,7 @@
         <v>2012</v>
       </c>
       <c r="F190" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G190" s="15" t="s">
         <v>618</v>
@@ -14665,10 +14664,10 @@
         <v>78</v>
       </c>
       <c r="Q190" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R190" s="19" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="191" spans="1:18">
@@ -14688,7 +14687,7 @@
         <v>2012</v>
       </c>
       <c r="F191" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G191" s="15" t="s">
         <v>618</v>
@@ -14721,10 +14720,10 @@
         <v>78</v>
       </c>
       <c r="Q191" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R191" s="19" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="192" spans="1:18">
@@ -14744,7 +14743,7 @@
         <v>2012</v>
       </c>
       <c r="F192" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G192" s="15" t="s">
         <v>146</v>
@@ -14777,7 +14776,7 @@
         <v>78</v>
       </c>
       <c r="Q192" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R192" s="19" t="s">
         <v>80</v>
@@ -14800,7 +14799,7 @@
         <v>2012</v>
       </c>
       <c r="F193" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G193" s="15" t="s">
         <v>145</v>
@@ -14833,7 +14832,7 @@
         <v>78</v>
       </c>
       <c r="Q193" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R193" s="19" t="s">
         <v>80</v>
@@ -14856,7 +14855,7 @@
         <v>2012</v>
       </c>
       <c r="F194" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G194" s="15" t="s">
         <v>144</v>
@@ -14889,7 +14888,7 @@
         <v>78</v>
       </c>
       <c r="Q194" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R194" s="19" t="s">
         <v>80</v>
@@ -14912,7 +14911,7 @@
         <v>2012</v>
       </c>
       <c r="F195" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G195" s="15" t="s">
         <v>625</v>
@@ -14945,7 +14944,7 @@
         <v>78</v>
       </c>
       <c r="Q195" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R195" s="19" t="s">
         <v>80</v>
@@ -14968,7 +14967,7 @@
         <v>2012</v>
       </c>
       <c r="F196" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G196" s="15" t="s">
         <v>209</v>
@@ -15001,7 +15000,7 @@
         <v>78</v>
       </c>
       <c r="Q196" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R196" s="19" t="s">
         <v>80</v>
@@ -15024,7 +15023,7 @@
         <v>2012</v>
       </c>
       <c r="F197" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G197" s="15" t="s">
         <v>143</v>
@@ -15057,7 +15056,7 @@
         <v>78</v>
       </c>
       <c r="Q197" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R197" s="19" t="s">
         <v>281</v>
@@ -15080,7 +15079,7 @@
         <v>2012</v>
       </c>
       <c r="F198" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G198" s="15" t="s">
         <v>142</v>
@@ -15113,7 +15112,7 @@
         <v>78</v>
       </c>
       <c r="Q198" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R198" s="19" t="s">
         <v>80</v>
@@ -15136,7 +15135,7 @@
         <v>2012</v>
       </c>
       <c r="F199" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G199" s="15" t="s">
         <v>141</v>
@@ -15169,7 +15168,7 @@
         <v>78</v>
       </c>
       <c r="Q199" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R199" s="19" t="s">
         <v>80</v>
@@ -15192,7 +15191,7 @@
         <v>2012</v>
       </c>
       <c r="F200" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G200" s="15" t="s">
         <v>141</v>
@@ -15225,7 +15224,7 @@
         <v>78</v>
       </c>
       <c r="Q200" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R200" s="19" t="s">
         <v>80</v>
@@ -15248,7 +15247,7 @@
         <v>2012</v>
       </c>
       <c r="F201" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G201" s="15" t="s">
         <v>140</v>
@@ -15281,7 +15280,7 @@
         <v>78</v>
       </c>
       <c r="Q201" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R201" s="19" t="s">
         <v>281</v>
@@ -15304,7 +15303,7 @@
         <v>2012</v>
       </c>
       <c r="F202" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G202" s="15" t="s">
         <v>139</v>
@@ -15337,7 +15336,7 @@
         <v>78</v>
       </c>
       <c r="Q202" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R202" s="19" t="s">
         <v>83</v>
@@ -15360,7 +15359,7 @@
         <v>2011</v>
       </c>
       <c r="F203" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G203" s="15" t="s">
         <v>138</v>
@@ -15393,7 +15392,7 @@
         <v>78</v>
       </c>
       <c r="Q203" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R203" s="19" t="s">
         <v>83</v>
@@ -15416,7 +15415,7 @@
         <v>2011</v>
       </c>
       <c r="F204" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G204" s="15" t="s">
         <v>137</v>
@@ -15449,7 +15448,7 @@
         <v>78</v>
       </c>
       <c r="Q204" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R204" s="19" t="s">
         <v>80</v>
@@ -15472,7 +15471,7 @@
         <v>2011</v>
       </c>
       <c r="F205" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G205" s="15" t="s">
         <v>136</v>
@@ -15505,7 +15504,7 @@
         <v>78</v>
       </c>
       <c r="Q205" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R205" s="19" t="s">
         <v>80</v>
@@ -15528,7 +15527,7 @@
         <v>2011</v>
       </c>
       <c r="F206" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G206" s="15" t="s">
         <v>641</v>
@@ -15561,7 +15560,7 @@
         <v>78</v>
       </c>
       <c r="Q206" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R206" s="19" t="s">
         <v>311</v>
@@ -15584,10 +15583,10 @@
         <v>2011</v>
       </c>
       <c r="F207" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G207" s="15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H207" s="15" t="s">
         <v>643</v>
@@ -15617,7 +15616,7 @@
         <v>78</v>
       </c>
       <c r="Q207" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R207" s="19" t="s">
         <v>311</v>
@@ -15640,7 +15639,7 @@
         <v>2011</v>
       </c>
       <c r="F208" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G208" s="15" t="s">
         <v>135</v>
@@ -15673,7 +15672,7 @@
         <v>298</v>
       </c>
       <c r="Q208" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R208" s="19" t="s">
         <v>80</v>
@@ -15696,7 +15695,7 @@
         <v>2011</v>
       </c>
       <c r="F209" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G209" s="15" t="s">
         <v>646</v>
@@ -15729,7 +15728,7 @@
         <v>298</v>
       </c>
       <c r="Q209" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R209" s="19" t="s">
         <v>80</v>
@@ -15752,7 +15751,7 @@
         <v>2011</v>
       </c>
       <c r="F210" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G210" s="15" t="s">
         <v>647</v>
@@ -15785,7 +15784,7 @@
         <v>298</v>
       </c>
       <c r="Q210" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R210" s="19" t="s">
         <v>80</v>
@@ -15808,7 +15807,7 @@
         <v>2011</v>
       </c>
       <c r="F211" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G211" s="15" t="s">
         <v>648</v>
@@ -15841,7 +15840,7 @@
         <v>298</v>
       </c>
       <c r="Q211" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R211" s="19" t="s">
         <v>80</v>
@@ -15864,7 +15863,7 @@
         <v>2011</v>
       </c>
       <c r="F212" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G212" s="15" t="s">
         <v>134</v>
@@ -15897,7 +15896,7 @@
         <v>78</v>
       </c>
       <c r="Q212" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R212" s="19" t="s">
         <v>80</v>
@@ -15920,7 +15919,7 @@
         <v>2011</v>
       </c>
       <c r="F213" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G213" s="15" t="s">
         <v>651</v>
@@ -15953,7 +15952,7 @@
         <v>78</v>
       </c>
       <c r="Q213" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R213" s="19" t="s">
         <v>81</v>
@@ -15976,7 +15975,7 @@
         <v>2011</v>
       </c>
       <c r="F214" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G214" s="15" t="s">
         <v>653</v>
@@ -16009,7 +16008,7 @@
         <v>78</v>
       </c>
       <c r="Q214" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R214" s="19" t="s">
         <v>81</v>
@@ -16032,7 +16031,7 @@
         <v>2011</v>
       </c>
       <c r="F215" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G215" s="15" t="s">
         <v>133</v>
@@ -16065,7 +16064,7 @@
         <v>78</v>
       </c>
       <c r="Q215" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R215" s="19" t="s">
         <v>80</v>
@@ -16088,7 +16087,7 @@
         <v>2011</v>
       </c>
       <c r="F216" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G216" s="15" t="s">
         <v>132</v>
@@ -16111,7 +16110,7 @@
         <v>97</v>
       </c>
       <c r="M216" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N216" s="3"/>
       <c r="O216" t="s">
@@ -16121,7 +16120,7 @@
         <v>78</v>
       </c>
       <c r="Q216" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R216" s="19" t="s">
         <v>80</v>
@@ -16144,7 +16143,7 @@
         <v>2011</v>
       </c>
       <c r="F217" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G217" s="15" t="s">
         <v>105</v>
@@ -16177,7 +16176,7 @@
         <v>78</v>
       </c>
       <c r="Q217" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R217" s="19" t="s">
         <v>80</v>
@@ -16200,10 +16199,10 @@
         <v>2011</v>
       </c>
       <c r="F218" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H218" s="15" t="s">
         <v>131</v>
@@ -16233,7 +16232,7 @@
         <v>78</v>
       </c>
       <c r="Q218" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R218" s="19" t="s">
         <v>83</v>
@@ -16256,7 +16255,7 @@
         <v>2010</v>
       </c>
       <c r="F219" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G219" s="15" t="s">
         <v>130</v>
@@ -16289,7 +16288,7 @@
         <v>78</v>
       </c>
       <c r="Q219" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R219" s="19" t="s">
         <v>83</v>
@@ -16312,7 +16311,7 @@
         <v>2010</v>
       </c>
       <c r="F220" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G220" s="15" t="s">
         <v>129</v>
@@ -16345,7 +16344,7 @@
         <v>78</v>
       </c>
       <c r="Q220" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R220" s="19" t="s">
         <v>83</v>
@@ -16368,7 +16367,7 @@
         <v>2010</v>
       </c>
       <c r="F221" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G221" s="15" t="s">
         <v>665</v>
@@ -16391,7 +16390,7 @@
         <v>97</v>
       </c>
       <c r="M221" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N221" s="3"/>
       <c r="O221" t="s">
@@ -16401,7 +16400,7 @@
         <v>78</v>
       </c>
       <c r="Q221" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R221" s="19" t="s">
         <v>80</v>
@@ -16424,7 +16423,7 @@
         <v>2010</v>
       </c>
       <c r="F222" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G222" s="15" t="s">
         <v>664</v>
@@ -16457,7 +16456,7 @@
         <v>78</v>
       </c>
       <c r="Q222" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R222" s="19" t="s">
         <v>80</v>
@@ -16480,7 +16479,7 @@
         <v>2010</v>
       </c>
       <c r="F223" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G223" s="15" t="s">
         <v>128</v>
@@ -16513,7 +16512,7 @@
         <v>78</v>
       </c>
       <c r="Q223" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R223" s="19" t="s">
         <v>80</v>
@@ -16536,7 +16535,7 @@
         <v>2010</v>
       </c>
       <c r="F224" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G224" s="15" t="s">
         <v>126</v>
@@ -16569,7 +16568,7 @@
         <v>78</v>
       </c>
       <c r="Q224" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R224" s="19" t="s">
         <v>80</v>
@@ -16592,7 +16591,7 @@
         <v>2010</v>
       </c>
       <c r="F225" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G225" s="15" t="s">
         <v>125</v>
@@ -16615,7 +16614,7 @@
         <v>97</v>
       </c>
       <c r="M225" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N225" s="3"/>
       <c r="O225" t="s">
@@ -16625,7 +16624,7 @@
         <v>78</v>
       </c>
       <c r="Q225" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R225" s="19" t="s">
         <v>281</v>
@@ -16648,7 +16647,7 @@
         <v>2010</v>
       </c>
       <c r="F226" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G226" s="15" t="s">
         <v>124</v>
@@ -16681,7 +16680,7 @@
         <v>78</v>
       </c>
       <c r="Q226" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R226" s="19" t="s">
         <v>80</v>
@@ -16704,7 +16703,7 @@
         <v>2010</v>
       </c>
       <c r="F227" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G227" s="15" t="s">
         <v>123</v>
@@ -16737,7 +16736,7 @@
         <v>78</v>
       </c>
       <c r="Q227" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R227" s="19" t="s">
         <v>80</v>
@@ -16760,7 +16759,7 @@
         <v>2010</v>
       </c>
       <c r="F228" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G228" s="15" t="s">
         <v>122</v>
@@ -16793,7 +16792,7 @@
         <v>78</v>
       </c>
       <c r="Q228" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R228" s="19" t="s">
         <v>83</v>
@@ -16816,7 +16815,7 @@
         <v>2010</v>
       </c>
       <c r="F229" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G229" s="15" t="s">
         <v>121</v>
@@ -16839,7 +16838,7 @@
         <v>97</v>
       </c>
       <c r="M229" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N229" s="3"/>
       <c r="O229" t="s">
@@ -16849,7 +16848,7 @@
         <v>78</v>
       </c>
       <c r="Q229" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R229" s="19" t="s">
         <v>80</v>
@@ -16872,7 +16871,7 @@
         <v>2009</v>
       </c>
       <c r="F230" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G230" s="15" t="s">
         <v>120</v>
@@ -16889,13 +16888,13 @@
         <v>-0.67069840000000003</v>
       </c>
       <c r="K230" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="L230" t="s">
         <v>97</v>
       </c>
       <c r="M230" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N230" s="3"/>
       <c r="O230" t="s">
@@ -16905,7 +16904,7 @@
         <v>78</v>
       </c>
       <c r="Q230" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R230" s="19" t="s">
         <v>80</v>
@@ -16928,7 +16927,7 @@
         <v>2009</v>
       </c>
       <c r="F231" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G231" s="15" t="s">
         <v>118</v>
@@ -16951,7 +16950,7 @@
         <v>97</v>
       </c>
       <c r="M231" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N231" s="3"/>
       <c r="O231" t="s">
@@ -16961,7 +16960,7 @@
         <v>78</v>
       </c>
       <c r="Q231" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R231" s="19" t="s">
         <v>80</v>
@@ -16984,7 +16983,7 @@
         <v>2009</v>
       </c>
       <c r="F232" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G232" s="15" t="s">
         <v>679</v>
@@ -17007,7 +17006,7 @@
         <v>97</v>
       </c>
       <c r="M232" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N232" s="3"/>
       <c r="O232" t="s">
@@ -17017,7 +17016,7 @@
         <v>78</v>
       </c>
       <c r="Q232" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R232" s="19" t="s">
         <v>80</v>
@@ -17040,7 +17039,7 @@
         <v>2009</v>
       </c>
       <c r="F233" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G233" s="15" t="s">
         <v>680</v>
@@ -17063,7 +17062,7 @@
         <v>97</v>
       </c>
       <c r="M233" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N233" s="3"/>
       <c r="O233" t="s">
@@ -17073,7 +17072,7 @@
         <v>78</v>
       </c>
       <c r="Q233" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R233" s="19" t="s">
         <v>80</v>
@@ -17096,7 +17095,7 @@
         <v>2009</v>
       </c>
       <c r="F234" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G234" s="15" t="s">
         <v>117</v>
@@ -17129,7 +17128,7 @@
         <v>78</v>
       </c>
       <c r="Q234" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R234" s="19" t="s">
         <v>83</v>
@@ -17152,7 +17151,7 @@
         <v>2009</v>
       </c>
       <c r="F235" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G235" s="15" t="s">
         <v>116</v>
@@ -17175,7 +17174,7 @@
         <v>97</v>
       </c>
       <c r="M235" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N235" s="3"/>
       <c r="O235" t="s">
@@ -17185,7 +17184,7 @@
         <v>78</v>
       </c>
       <c r="Q235" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R235" s="19" t="s">
         <v>80</v>
@@ -17208,7 +17207,7 @@
         <v>2009</v>
       </c>
       <c r="F236" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G236" s="15" t="s">
         <v>115</v>
@@ -17231,7 +17230,7 @@
         <v>97</v>
       </c>
       <c r="M236" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N236" s="3"/>
       <c r="O236" t="s">
@@ -17241,7 +17240,7 @@
         <v>78</v>
       </c>
       <c r="Q236" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R236" s="19" t="s">
         <v>281</v>
@@ -17264,7 +17263,7 @@
         <v>2009</v>
       </c>
       <c r="F237" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G237" s="15" t="s">
         <v>114</v>
@@ -17287,7 +17286,7 @@
         <v>97</v>
       </c>
       <c r="M237" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N237" s="3"/>
       <c r="O237" t="s">
@@ -17297,7 +17296,7 @@
         <v>78</v>
       </c>
       <c r="Q237" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R237" s="19" t="s">
         <v>80</v>
@@ -17320,7 +17319,7 @@
         <v>2009</v>
       </c>
       <c r="F238" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G238" s="15" t="s">
         <v>113</v>
@@ -17353,7 +17352,7 @@
         <v>78</v>
       </c>
       <c r="Q238" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R238" s="19" t="s">
         <v>80</v>
@@ -17376,7 +17375,7 @@
         <v>2009</v>
       </c>
       <c r="F239" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G239" s="15" t="s">
         <v>112</v>
@@ -17399,7 +17398,7 @@
         <v>97</v>
       </c>
       <c r="M239" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N239" s="3"/>
       <c r="O239" t="s">
@@ -17409,7 +17408,7 @@
         <v>78</v>
       </c>
       <c r="Q239" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R239" s="19" t="s">
         <v>83</v>
@@ -17432,13 +17431,13 @@
         <v>2008</v>
       </c>
       <c r="F240" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G240" s="15" t="s">
         <v>111</v>
       </c>
       <c r="H240" s="15" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I240" s="7" t="str">
         <f t="shared" si="9"/>
@@ -17449,13 +17448,13 @@
         <v>-1.3857569999999999</v>
       </c>
       <c r="K240" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="L240" t="s">
         <v>97</v>
       </c>
       <c r="M240" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N240" s="3"/>
       <c r="O240" t="s">
@@ -17465,7 +17464,7 @@
         <v>78</v>
       </c>
       <c r="Q240" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R240" s="19" t="s">
         <v>83</v>
@@ -17488,7 +17487,7 @@
         <v>2008</v>
       </c>
       <c r="F241" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G241" s="15" t="s">
         <v>110</v>
@@ -17505,13 +17504,13 @@
         <v>-0.33615020000000001</v>
       </c>
       <c r="K241" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="L241" t="s">
         <v>97</v>
       </c>
       <c r="M241" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N241" s="3"/>
       <c r="O241" t="s">
@@ -17521,7 +17520,7 @@
         <v>78</v>
       </c>
       <c r="Q241" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R241" s="19" t="s">
         <v>80</v>
@@ -17544,7 +17543,7 @@
         <v>2008</v>
       </c>
       <c r="F242" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G242" s="15" t="s">
         <v>109</v>
@@ -17567,7 +17566,7 @@
         <v>97</v>
       </c>
       <c r="M242" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N242" s="3"/>
       <c r="O242" t="s">
@@ -17577,7 +17576,7 @@
         <v>78</v>
       </c>
       <c r="Q242" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R242" s="19" t="s">
         <v>80</v>
@@ -17600,7 +17599,7 @@
         <v>2008</v>
       </c>
       <c r="F243" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G243" s="15" t="s">
         <v>108</v>
@@ -17623,7 +17622,7 @@
         <v>97</v>
       </c>
       <c r="M243" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N243" s="3"/>
       <c r="O243" t="s">
@@ -17633,7 +17632,7 @@
         <v>78</v>
       </c>
       <c r="Q243" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R243" s="19" t="s">
         <v>80</v>
@@ -17656,7 +17655,7 @@
         <v>2008</v>
       </c>
       <c r="F244" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G244" s="15" t="s">
         <v>107</v>
@@ -17679,7 +17678,7 @@
         <v>97</v>
       </c>
       <c r="M244" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N244" s="3"/>
       <c r="O244" t="s">
@@ -17689,7 +17688,7 @@
         <v>78</v>
       </c>
       <c r="Q244" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R244" s="19" t="s">
         <v>80</v>
@@ -17712,7 +17711,7 @@
         <v>2008</v>
       </c>
       <c r="F245" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G245" s="15" t="s">
         <v>106</v>
@@ -17745,7 +17744,7 @@
         <v>78</v>
       </c>
       <c r="Q245" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R245" s="19" t="s">
         <v>80</v>
@@ -17768,7 +17767,7 @@
         <v>2008</v>
       </c>
       <c r="F246" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G246" s="15" t="s">
         <v>105</v>
@@ -17801,7 +17800,7 @@
         <v>78</v>
       </c>
       <c r="Q246" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R246" s="19" t="s">
         <v>80</v>
@@ -17824,7 +17823,7 @@
         <v>2008</v>
       </c>
       <c r="F247" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G247" s="15" t="s">
         <v>104</v>
@@ -17847,7 +17846,7 @@
         <v>97</v>
       </c>
       <c r="M247" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N247" s="3"/>
       <c r="O247" t="s">
@@ -17857,7 +17856,7 @@
         <v>78</v>
       </c>
       <c r="Q247" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R247" s="19" t="s">
         <v>80</v>
@@ -17880,7 +17879,7 @@
         <v>2008</v>
       </c>
       <c r="F248" s="14" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G248" s="15" t="s">
         <v>103</v>
@@ -17903,7 +17902,7 @@
         <v>97</v>
       </c>
       <c r="M248" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="N248" s="3"/>
       <c r="O248" t="s">
@@ -17913,7 +17912,7 @@
         <v>78</v>
       </c>
       <c r="Q248" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R248" s="19" t="s">
         <v>80</v>
@@ -17936,7 +17935,7 @@
         <v>2007</v>
       </c>
       <c r="F249" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G249" s="15" t="s">
         <v>977</v>
@@ -17959,7 +17958,7 @@
         <v>97</v>
       </c>
       <c r="M249" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="O249" t="s">
         <v>86</v>
@@ -17968,7 +17967,7 @@
         <v>78</v>
       </c>
       <c r="Q249" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R249" s="19" t="s">
         <v>83</v>
@@ -17991,7 +17990,7 @@
         <v>2006</v>
       </c>
       <c r="F250" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G250" s="15" t="s">
         <v>977</v>
@@ -18014,7 +18013,7 @@
         <v>97</v>
       </c>
       <c r="M250" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="O250" t="s">
         <v>86</v>
@@ -18023,7 +18022,7 @@
         <v>78</v>
       </c>
       <c r="Q250" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R250" s="19" t="s">
         <v>83</v>

--- a/datos/excursiones.xlsx
+++ b/datos/excursiones.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josel\Documents\elaios_mapa\proyecto_mapa_excursiones\mapa_elaios\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67259905-77D8-4289-9548-48AB3CD52313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2445AF-EE84-4D8F-A0E5-9C98EE1C39C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3071397-29EF-4FE4-BFF9-584C2604D779}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$R$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$R$249</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3002" uniqueCount="1058">
   <si>
     <t>mes_numerico</t>
   </si>
@@ -2150,9 +2150,6 @@
     <t>2008_01_01</t>
   </si>
   <si>
-    <t>2007_01_01</t>
-  </si>
-  <si>
     <t>2006_01_01</t>
   </si>
   <si>
@@ -3177,13 +3174,58 @@
   </si>
   <si>
     <t>Circular Piracés (RGP)</t>
+  </si>
+  <si>
+    <t>San Martin de Val d'onsera</t>
+  </si>
+  <si>
+    <t>2007_02_18</t>
+  </si>
+  <si>
+    <t>2007_05_13</t>
+  </si>
+  <si>
+    <t>2007_05_26</t>
+  </si>
+  <si>
+    <t>2007_07_14</t>
+  </si>
+  <si>
+    <t>Hoces del Rio Piedra</t>
+  </si>
+  <si>
+    <t>Valle de Tena</t>
+  </si>
+  <si>
+    <t>Pico Anayet</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aparcamiento+San+Mart%C3%ADn+de+la+Bal+d'Onsera/@42.2387223,-0.3489316,805m/data=!3m2!1e3!4b1!4m6!3m5!1s0xd583f7cd23dd333:0x238a2f790bd3e23f!8m2!3d42.2387184!4d-0.3463567!16s%2Fg%2F11gfn5gdml?entry=ttu&amp;g_ep=EgoyMDI2MTAwNi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Loporzano</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/50374+Torralba+de+los+Frailes,+Zaragoza/@41.0368836,-1.6627352,820m/data=!3m2!1e3!4b1!4m6!3m5!1s0xd5c6f4897998e25:0x2c8cb2897b40bab7!8m2!3d41.0369306!4d-1.6608876!16s%2Fm%2F02z9vrt?entry=ttu&amp;g_ep=EgoyMDI2MTAwNi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Valle+de+Tena/@42.6666815,-0.3269664,3197m/data=!3m2!1e3!4b1!4m6!3m5!1s0xd578cdfbcd9157d:0x8907dc58399f1308!8m2!3d42.6666667!4d-0.3166667!16s%2Fm%2F026l8c_?entry=ttu&amp;g_ep=EgoyMDI2MTAwNi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/search/parking+portalet/@42.7996859,-0.4165246,797m/data=!3m1!1e3?entry=ttu&amp;g_ep=EgoyMDI2MTAwNi4wIKXMDSoASAFQAw%3D%3D</t>
+  </si>
+  <si>
+    <t>Portalet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3329,6 +3371,12 @@
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3458,7 +3506,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3501,6 +3549,13 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="19" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="Accent" xfId="4" xr:uid="{1F55EB33-E00A-4941-9C5C-0A7BC0917C5B}"/>
@@ -3854,7 +3909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F92D137-B0F7-489C-BBD5-87D14D584D75}">
-  <dimension ref="A1:R250"/>
+  <dimension ref="A1:R253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -3888,7 +3943,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -3942,7 +3997,7 @@
         <v>2025</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>93</v>
@@ -3998,10 +4053,10 @@
         <v>2025</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H3" t="s">
         <v>58</v>
@@ -4021,7 +4076,7 @@
         <v>97</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="8" t="s">
@@ -4055,7 +4110,7 @@
         <v>2025</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G4" t="s">
         <v>57</v>
@@ -4112,7 +4167,7 @@
         <v>2025</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G5" t="s">
         <v>53</v>
@@ -4169,7 +4224,7 @@
         <v>2025</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G6" t="s">
         <v>50</v>
@@ -4226,7 +4281,7 @@
         <v>2025</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G7" t="s">
         <v>47</v>
@@ -4283,7 +4338,7 @@
         <v>2025</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G8" t="s">
         <v>44</v>
@@ -4340,7 +4395,7 @@
         <v>2025</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G9" t="s">
         <v>42</v>
@@ -4397,7 +4452,7 @@
         <v>2025</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -4454,7 +4509,7 @@
         <v>2025</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G11" t="s">
         <v>37</v>
@@ -4477,7 +4532,7 @@
         <v>97</v>
       </c>
       <c r="M11" s="18" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>97</v>
@@ -4513,7 +4568,7 @@
         <v>2025</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G12" t="s">
         <v>33</v>
@@ -4570,7 +4625,7 @@
         <v>2025</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>28</v>
@@ -4629,7 +4684,7 @@
         <v>2025</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -4686,7 +4741,7 @@
         <v>2025</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
@@ -4743,7 +4798,7 @@
         <v>2025</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
@@ -4800,7 +4855,7 @@
         <v>2025</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G17" t="s">
         <v>16</v>
@@ -4857,7 +4912,7 @@
         <v>2025</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>11</v>
@@ -4916,7 +4971,7 @@
         <v>2025</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G19" t="s">
         <v>7</v>
@@ -4973,7 +5028,7 @@
         <v>2024</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G20" t="s">
         <v>273</v>
@@ -5032,7 +5087,7 @@
         <v>2024</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G21" t="s">
         <v>271</v>
@@ -5091,7 +5146,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G22" t="s">
         <v>289</v>
@@ -5148,7 +5203,7 @@
         <v>2024</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G23" t="s">
         <v>284</v>
@@ -5207,7 +5262,7 @@
         <v>2024</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G24" t="s">
         <v>292</v>
@@ -5227,7 +5282,7 @@
         <v>297</v>
       </c>
       <c r="M24" s="20" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" t="s">
@@ -5261,7 +5316,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G25" t="s">
         <v>291</v>
@@ -5320,7 +5375,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G26" t="s">
         <v>267</v>
@@ -5343,7 +5398,7 @@
         <v>97</v>
       </c>
       <c r="M26" s="18" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>268</v>
@@ -5379,7 +5434,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G27" t="s">
         <v>265</v>
@@ -5438,7 +5493,7 @@
         <v>2024</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G28" t="s">
         <v>301</v>
@@ -5497,7 +5552,7 @@
         <v>2024</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G29" t="s">
         <v>314</v>
@@ -5554,7 +5609,7 @@
         <v>2024</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G30" t="s">
         <v>307</v>
@@ -5613,7 +5668,7 @@
         <v>2024</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G31" t="s">
         <v>261</v>
@@ -5672,7 +5727,7 @@
         <v>2024</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G32" t="s">
         <v>321</v>
@@ -5695,7 +5750,7 @@
         <v>97</v>
       </c>
       <c r="M32" s="20" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" t="s">
@@ -5729,7 +5784,7 @@
         <v>2024</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G33" s="12" t="s">
         <v>319</v>
@@ -5752,7 +5807,7 @@
         <v>97</v>
       </c>
       <c r="M33" s="20" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>260</v>
@@ -5788,7 +5843,7 @@
         <v>2024</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G34" t="s">
         <v>258</v>
@@ -5811,7 +5866,7 @@
         <v>97</v>
       </c>
       <c r="M34" s="20" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="N34" s="3" t="s">
         <v>259</v>
@@ -5847,7 +5902,7 @@
         <v>2024</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G35" t="s">
         <v>256</v>
@@ -5870,7 +5925,7 @@
         <v>97</v>
       </c>
       <c r="M35" s="20" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>257</v>
@@ -5906,7 +5961,7 @@
         <v>2024</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G36" t="s">
         <v>254</v>
@@ -5929,7 +5984,7 @@
         <v>97</v>
       </c>
       <c r="M36" s="20" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="N36" s="3" t="s">
         <v>255</v>
@@ -5965,7 +6020,7 @@
         <v>2023</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G37" t="s">
         <v>328</v>
@@ -5988,7 +6043,7 @@
         <v>97</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="N37" s="3" t="s">
         <v>253</v>
@@ -6024,7 +6079,7 @@
         <v>2023</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G38" t="s">
         <v>250</v>
@@ -6047,7 +6102,7 @@
         <v>97</v>
       </c>
       <c r="M38" s="21" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>251</v>
@@ -6083,7 +6138,7 @@
         <v>2023</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G39" t="s">
         <v>248</v>
@@ -6142,7 +6197,7 @@
         <v>2023</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G40" t="s">
         <v>246</v>
@@ -6165,7 +6220,7 @@
         <v>97</v>
       </c>
       <c r="M40" s="20" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>247</v>
@@ -6201,7 +6256,7 @@
         <v>2023</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G41" t="s">
         <v>244</v>
@@ -6218,13 +6273,13 @@
         <v>-0.23676420000000001</v>
       </c>
       <c r="K41" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L41" t="s">
         <v>97</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>245</v>
@@ -6260,7 +6315,7 @@
         <v>2023</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G42" t="s">
         <v>341</v>
@@ -6277,13 +6332,13 @@
         <v>-0.23676420000000001</v>
       </c>
       <c r="K42" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L42" t="s">
         <v>97</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>243</v>
@@ -6319,7 +6374,7 @@
         <v>2023</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G43" t="s">
         <v>338</v>
@@ -6342,7 +6397,7 @@
         <v>97</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>242</v>
@@ -6378,7 +6433,7 @@
         <v>2023</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G44" t="s">
         <v>344</v>
@@ -6401,7 +6456,7 @@
         <v>97</v>
       </c>
       <c r="M44" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" t="s">
@@ -6435,7 +6490,7 @@
         <v>2023</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>345</v>
@@ -6458,7 +6513,7 @@
         <v>97</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>241</v>
@@ -6494,13 +6549,13 @@
         <v>2023</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G46" t="s">
         <v>347</v>
       </c>
       <c r="H46" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="I46" s="7" t="str">
         <f t="shared" si="1"/>
@@ -6511,13 +6566,13 @@
         <v>-0.16970170000000001</v>
       </c>
       <c r="K46" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="L46" t="s">
         <v>97</v>
       </c>
       <c r="M46" s="20" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" t="s">
@@ -6551,13 +6606,13 @@
         <v>2023</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H47" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="I47" s="7" t="str">
         <f t="shared" si="1"/>
@@ -6568,13 +6623,13 @@
         <v>-0.32057790000000003</v>
       </c>
       <c r="K47" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="L47" t="s">
         <v>97</v>
       </c>
       <c r="M47" s="20" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>240</v>
@@ -6610,7 +6665,7 @@
         <v>2023</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G48" t="s">
         <v>349</v>
@@ -6633,7 +6688,7 @@
         <v>97</v>
       </c>
       <c r="M48" s="20" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" t="s">
@@ -6667,7 +6722,7 @@
         <v>2023</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G49" t="s">
         <v>348</v>
@@ -6690,7 +6745,7 @@
         <v>97</v>
       </c>
       <c r="M49" s="20" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>239</v>
@@ -6726,7 +6781,7 @@
         <v>2023</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G50" t="s">
         <v>358</v>
@@ -6783,7 +6838,7 @@
         <v>2023</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G51" t="s">
         <v>359</v>
@@ -6842,13 +6897,13 @@
         <v>2023</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G52" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H52" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="I52" s="7" t="str">
         <f t="shared" si="1"/>
@@ -6859,13 +6914,13 @@
         <v>-0.8052433</v>
       </c>
       <c r="K52" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="L52" t="s">
         <v>97</v>
       </c>
       <c r="M52" s="20" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>237</v>
@@ -6901,7 +6956,7 @@
         <v>2022</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G53" t="s">
         <v>235</v>
@@ -6924,7 +6979,7 @@
         <v>97</v>
       </c>
       <c r="M53" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>236</v>
@@ -6960,7 +7015,7 @@
         <v>2022</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G54" t="s">
         <v>233</v>
@@ -7019,7 +7074,7 @@
         <v>2022</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G55" t="s">
         <v>231</v>
@@ -7042,7 +7097,7 @@
         <v>97</v>
       </c>
       <c r="M55" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" t="s">
@@ -7076,7 +7131,7 @@
         <v>2022</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G56" t="s">
         <v>231</v>
@@ -7099,7 +7154,7 @@
         <v>97</v>
       </c>
       <c r="M56" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N56" s="3" t="s">
         <v>232</v>
@@ -7135,7 +7190,7 @@
         <v>2022</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G57" t="s">
         <v>229</v>
@@ -7158,7 +7213,7 @@
         <v>97</v>
       </c>
       <c r="M57" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N57" s="3"/>
       <c r="O57" t="s">
@@ -7192,7 +7247,7 @@
         <v>2022</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G58" t="s">
         <v>229</v>
@@ -7215,7 +7270,7 @@
         <v>97</v>
       </c>
       <c r="M58" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>230</v>
@@ -7251,7 +7306,7 @@
         <v>2022</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G59" t="s">
         <v>227</v>
@@ -7274,7 +7329,7 @@
         <v>97</v>
       </c>
       <c r="M59" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>228</v>
@@ -7310,7 +7365,7 @@
         <v>2022</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G60" t="s">
         <v>374</v>
@@ -7333,7 +7388,7 @@
         <v>97</v>
       </c>
       <c r="M60" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N60" s="3"/>
       <c r="O60" t="s">
@@ -7367,7 +7422,7 @@
         <v>2022</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>373</v>
@@ -7390,7 +7445,7 @@
         <v>97</v>
       </c>
       <c r="M61" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>226</v>
@@ -7426,7 +7481,7 @@
         <v>2022</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G62" t="s">
         <v>378</v>
@@ -7449,7 +7504,7 @@
         <v>97</v>
       </c>
       <c r="M62" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N62" s="3"/>
       <c r="O62" t="s">
@@ -7483,7 +7538,7 @@
         <v>2022</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>377</v>
@@ -7506,7 +7561,7 @@
         <v>97</v>
       </c>
       <c r="M63" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>225</v>
@@ -7542,7 +7597,7 @@
         <v>2022</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G64" t="s">
         <v>223</v>
@@ -7565,7 +7620,7 @@
         <v>97</v>
       </c>
       <c r="M64" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>224</v>
@@ -7601,7 +7656,7 @@
         <v>2022</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G65" t="s">
         <v>383</v>
@@ -7624,7 +7679,7 @@
         <v>97</v>
       </c>
       <c r="M65" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N65" s="3"/>
       <c r="O65" t="s">
@@ -7658,7 +7713,7 @@
         <v>2022</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G66" t="s">
         <v>221</v>
@@ -7681,7 +7736,7 @@
         <v>97</v>
       </c>
       <c r="M66" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>222</v>
@@ -7717,7 +7772,7 @@
         <v>2022</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G67" t="s">
         <v>391</v>
@@ -7740,7 +7795,7 @@
         <v>97</v>
       </c>
       <c r="M67" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" t="s">
@@ -7753,7 +7808,7 @@
         <v>79</v>
       </c>
       <c r="R67" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -7774,7 +7829,7 @@
         <v>2022</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G68" t="s">
         <v>219</v>
@@ -7797,7 +7852,7 @@
         <v>97</v>
       </c>
       <c r="M68" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>220</v>
@@ -7833,7 +7888,7 @@
         <v>2022</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G69" t="s">
         <v>217</v>
@@ -7856,7 +7911,7 @@
         <v>97</v>
       </c>
       <c r="M69" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>218</v>
@@ -7892,7 +7947,7 @@
         <v>2022</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G70" t="s">
         <v>215</v>
@@ -7915,7 +7970,7 @@
         <v>97</v>
       </c>
       <c r="M70" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>216</v>
@@ -7951,7 +8006,7 @@
         <v>2021</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G71" t="s">
         <v>213</v>
@@ -7974,7 +8029,7 @@
         <v>97</v>
       </c>
       <c r="M71" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>214</v>
@@ -8010,7 +8065,7 @@
         <v>2021</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G72" t="s">
         <v>211</v>
@@ -8033,7 +8088,7 @@
         <v>97</v>
       </c>
       <c r="M72" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>212</v>
@@ -8069,7 +8124,7 @@
         <v>2021</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G73" t="s">
         <v>209</v>
@@ -8092,7 +8147,7 @@
         <v>97</v>
       </c>
       <c r="M73" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N73" s="3" t="s">
         <v>210</v>
@@ -8128,7 +8183,7 @@
         <v>2021</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G74" t="s">
         <v>205</v>
@@ -8151,7 +8206,7 @@
         <v>97</v>
       </c>
       <c r="M74" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N74" s="3" t="s">
         <v>206</v>
@@ -8187,7 +8242,7 @@
         <v>2021</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G75" t="s">
         <v>405</v>
@@ -8210,7 +8265,7 @@
         <v>97</v>
       </c>
       <c r="M75" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N75" s="3"/>
       <c r="O75" t="s">
@@ -8244,7 +8299,7 @@
         <v>2021</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G76" t="s">
         <v>103</v>
@@ -8267,7 +8322,7 @@
         <v>97</v>
       </c>
       <c r="M76" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N76" s="3"/>
       <c r="O76" t="s">
@@ -8301,7 +8356,7 @@
         <v>2021</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>404</v>
@@ -8324,7 +8379,7 @@
         <v>97</v>
       </c>
       <c r="M77" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>208</v>
@@ -8359,7 +8414,7 @@
         <v>2021</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G78" s="15" t="s">
         <v>207</v>
@@ -8376,13 +8431,13 @@
         <v>-0.17384520000000001</v>
       </c>
       <c r="K78" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L78" t="s">
         <v>97</v>
       </c>
       <c r="M78" s="17" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="N78" s="3"/>
       <c r="O78" t="s">
@@ -8392,7 +8447,7 @@
         <v>78</v>
       </c>
       <c r="Q78" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R78" s="19" t="s">
         <v>80</v>
@@ -8415,7 +8470,7 @@
         <v>2021</v>
       </c>
       <c r="F79" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G79" s="15" t="s">
         <v>205</v>
@@ -8432,13 +8487,13 @@
         <v>-0.93618029999999997</v>
       </c>
       <c r="K79" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L79" t="s">
         <v>97</v>
       </c>
       <c r="M79" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N79" s="3"/>
       <c r="O79" t="s">
@@ -8448,7 +8503,7 @@
         <v>78</v>
       </c>
       <c r="Q79" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R79" s="19" t="s">
         <v>83</v>
@@ -8471,7 +8526,7 @@
         <v>2020</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G80" s="15" t="s">
         <v>204</v>
@@ -8488,13 +8543,13 @@
         <v>-1.9144475000000001</v>
       </c>
       <c r="K80" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L80" t="s">
         <v>97</v>
       </c>
       <c r="M80" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="N80" s="3"/>
       <c r="O80" t="s">
@@ -8504,7 +8559,7 @@
         <v>78</v>
       </c>
       <c r="Q80" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R80" s="19" t="s">
         <v>83</v>
@@ -8527,7 +8582,7 @@
         <v>2020</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G81" s="15" t="s">
         <v>117</v>
@@ -8544,13 +8599,13 @@
         <v>-1.8201556999999999</v>
       </c>
       <c r="K81" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L81" t="s">
         <v>97</v>
       </c>
       <c r="M81" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N81" s="3"/>
       <c r="O81" t="s">
@@ -8560,7 +8615,7 @@
         <v>78</v>
       </c>
       <c r="Q81" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R81" s="19" t="s">
         <v>83</v>
@@ -8583,7 +8638,7 @@
         <v>2020</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G82" s="15" t="s">
         <v>203</v>
@@ -8600,23 +8655,23 @@
         <v>-0.42896970000000001</v>
       </c>
       <c r="K82" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L82" t="s">
         <v>97</v>
       </c>
       <c r="M82" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N82" s="3"/>
       <c r="O82" t="s">
         <v>86</v>
       </c>
       <c r="P82" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="Q82" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R82" s="19" t="s">
         <v>80</v>
@@ -8639,7 +8694,7 @@
         <v>2020</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G83" s="15" t="s">
         <v>202</v>
@@ -8656,13 +8711,13 @@
         <v>0.1245092</v>
       </c>
       <c r="K83" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L83" t="s">
         <v>97</v>
       </c>
       <c r="M83" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="N83" s="3"/>
       <c r="O83" t="s">
@@ -8672,7 +8727,7 @@
         <v>78</v>
       </c>
       <c r="Q83" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R83" s="19" t="s">
         <v>80</v>
@@ -8695,7 +8750,7 @@
         <v>2019</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G84" s="15" t="s">
         <v>106</v>
@@ -8712,13 +8767,13 @@
         <v>-0.43927529999999998</v>
       </c>
       <c r="K84" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L84" t="s">
         <v>97</v>
       </c>
       <c r="M84" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="N84" s="3"/>
       <c r="O84" t="s">
@@ -8728,7 +8783,7 @@
         <v>78</v>
       </c>
       <c r="Q84" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R84" s="19" t="s">
         <v>80</v>
@@ -8751,7 +8806,7 @@
         <v>2019</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G85" s="15" t="s">
         <v>425</v>
@@ -8768,13 +8823,13 @@
         <v>-0.40943079999999998</v>
       </c>
       <c r="K85" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="L85" t="s">
         <v>97</v>
       </c>
       <c r="M85" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="N85" s="3"/>
       <c r="O85" t="s">
@@ -8784,7 +8839,7 @@
         <v>78</v>
       </c>
       <c r="Q85" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R85" s="19" t="s">
         <v>80</v>
@@ -8807,7 +8862,7 @@
         <v>2019</v>
       </c>
       <c r="F86" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G86" s="15" t="s">
         <v>201</v>
@@ -8824,13 +8879,13 @@
         <v>-6.2200900000000003E-2</v>
       </c>
       <c r="K86" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="L86" t="s">
         <v>97</v>
       </c>
       <c r="M86" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="N86" s="3"/>
       <c r="O86" t="s">
@@ -8840,7 +8895,7 @@
         <v>78</v>
       </c>
       <c r="Q86" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R86" s="19" t="s">
         <v>80</v>
@@ -8863,7 +8918,7 @@
         <v>2019</v>
       </c>
       <c r="F87" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G87" s="15" t="s">
         <v>429</v>
@@ -8880,13 +8935,13 @@
         <v>0.91948110000000005</v>
       </c>
       <c r="K87" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L87" t="s">
         <v>97</v>
       </c>
       <c r="M87" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="N87" s="3"/>
       <c r="O87" t="s">
@@ -8896,7 +8951,7 @@
         <v>78</v>
       </c>
       <c r="Q87" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R87" s="19" t="s">
         <v>288</v>
@@ -8919,7 +8974,7 @@
         <v>2019</v>
       </c>
       <c r="F88" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G88" s="15" t="s">
         <v>431</v>
@@ -8936,13 +8991,13 @@
         <v>-0.1129619</v>
       </c>
       <c r="K88" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="L88" t="s">
         <v>97</v>
       </c>
       <c r="M88" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="N88" s="3"/>
       <c r="O88" t="s">
@@ -8952,7 +9007,7 @@
         <v>78</v>
       </c>
       <c r="Q88" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R88" s="19" t="s">
         <v>80</v>
@@ -8975,13 +9030,13 @@
         <v>2019</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G89" s="15" t="s">
         <v>200</v>
       </c>
       <c r="H89" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="I89" s="7" t="str">
         <f t="shared" si="5"/>
@@ -8992,13 +9047,13 @@
         <v>-9.1917266000000009</v>
       </c>
       <c r="K89" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="L89" t="s">
         <v>97</v>
       </c>
       <c r="M89" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="N89" s="3"/>
       <c r="O89" t="s">
@@ -9008,10 +9063,10 @@
         <v>78</v>
       </c>
       <c r="Q89" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R89" s="19" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -9031,7 +9086,7 @@
         <v>2019</v>
       </c>
       <c r="F90" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G90" s="15" t="s">
         <v>434</v>
@@ -9048,13 +9103,13 @@
         <v>-0.1129619</v>
       </c>
       <c r="K90" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="L90" t="s">
         <v>97</v>
       </c>
       <c r="M90" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="N90" s="3"/>
       <c r="O90" t="s">
@@ -9064,7 +9119,7 @@
         <v>298</v>
       </c>
       <c r="Q90" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R90" s="19" t="s">
         <v>80</v>
@@ -9087,7 +9142,7 @@
         <v>2019</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G91" s="15" t="s">
         <v>435</v>
@@ -9104,13 +9159,13 @@
         <v>-0.1013479</v>
       </c>
       <c r="K91" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="L91" t="s">
         <v>97</v>
       </c>
       <c r="M91" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="N91" s="3"/>
       <c r="O91" t="s">
@@ -9120,7 +9175,7 @@
         <v>298</v>
       </c>
       <c r="Q91" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R91" s="19" t="s">
         <v>311</v>
@@ -9143,7 +9198,7 @@
         <v>2019</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G92" s="15" t="s">
         <v>199</v>
@@ -9160,13 +9215,13 @@
         <v>0.19423489999999999</v>
       </c>
       <c r="K92" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="L92" t="s">
         <v>97</v>
       </c>
       <c r="M92" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="N92" s="3"/>
       <c r="O92" t="s">
@@ -9176,7 +9231,7 @@
         <v>78</v>
       </c>
       <c r="Q92" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R92" s="19" t="s">
         <v>80</v>
@@ -9199,13 +9254,13 @@
         <v>2019</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G93" s="15" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H93" t="s">
         <v>1026</v>
-      </c>
-      <c r="H93" t="s">
-        <v>1027</v>
       </c>
       <c r="I93" s="7" t="str">
         <f t="shared" si="5"/>
@@ -9216,13 +9271,13 @@
         <v>0.39274419999999999</v>
       </c>
       <c r="K93" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L93" t="s">
         <v>97</v>
       </c>
       <c r="M93" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="N93" s="3"/>
       <c r="O93" t="s">
@@ -9232,7 +9287,7 @@
         <v>78</v>
       </c>
       <c r="Q93" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R93" s="19" t="s">
         <v>80</v>
@@ -9255,7 +9310,7 @@
         <v>2019</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G94" s="15" t="s">
         <v>440</v>
@@ -9272,13 +9327,13 @@
         <v>0.59178759999999997</v>
       </c>
       <c r="K94" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="L94" t="s">
         <v>97</v>
       </c>
       <c r="M94" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="N94" s="3"/>
       <c r="O94" t="s">
@@ -9288,7 +9343,7 @@
         <v>78</v>
       </c>
       <c r="Q94" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R94" s="19" t="s">
         <v>80</v>
@@ -9311,7 +9366,7 @@
         <v>2019</v>
       </c>
       <c r="F95" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G95" s="15" t="s">
         <v>198</v>
@@ -9328,13 +9383,13 @@
         <v>-1.6534180999999999</v>
       </c>
       <c r="K95" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="L95" t="s">
         <v>97</v>
       </c>
       <c r="M95" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" t="s">
@@ -9344,7 +9399,7 @@
         <v>78</v>
       </c>
       <c r="Q95" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R95" s="19" t="s">
         <v>83</v>
@@ -9367,7 +9422,7 @@
         <v>2019</v>
       </c>
       <c r="F96" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G96" s="15" t="s">
         <v>197</v>
@@ -9384,13 +9439,13 @@
         <v>-0.53164290000000003</v>
       </c>
       <c r="K96" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="L96" t="s">
         <v>97</v>
       </c>
       <c r="M96" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" t="s">
@@ -9400,7 +9455,7 @@
         <v>78</v>
       </c>
       <c r="Q96" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R96" s="19" t="s">
         <v>281</v>
@@ -9423,7 +9478,7 @@
         <v>2019</v>
       </c>
       <c r="F97" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G97" s="15" t="s">
         <v>195</v>
@@ -9440,13 +9495,13 @@
         <v>1.8350496999999999</v>
       </c>
       <c r="K97" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="L97" t="s">
         <v>97</v>
       </c>
       <c r="M97" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" t="s">
@@ -9456,10 +9511,10 @@
         <v>78</v>
       </c>
       <c r="Q97" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R97" s="19" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -9479,7 +9534,7 @@
         <v>2019</v>
       </c>
       <c r="F98" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G98" s="15" t="s">
         <v>196</v>
@@ -9496,23 +9551,23 @@
         <v>-0.63656729999999995</v>
       </c>
       <c r="K98" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L98" t="s">
         <v>97</v>
       </c>
       <c r="M98" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N98" s="3"/>
       <c r="O98" t="s">
         <v>87</v>
       </c>
       <c r="P98" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="Q98" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R98" s="19" t="s">
         <v>80</v>
@@ -9535,7 +9590,7 @@
         <v>2019</v>
       </c>
       <c r="F99" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G99" s="15" t="s">
         <v>114</v>
@@ -9552,13 +9607,13 @@
         <v>-0.62996949999999996</v>
       </c>
       <c r="K99" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="L99" t="s">
         <v>97</v>
       </c>
       <c r="M99" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N99" s="3"/>
       <c r="O99" t="s">
@@ -9568,7 +9623,7 @@
         <v>78</v>
       </c>
       <c r="Q99" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R99" s="19" t="s">
         <v>80</v>
@@ -9591,7 +9646,7 @@
         <v>2018</v>
       </c>
       <c r="F100" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G100" s="15" t="s">
         <v>194</v>
@@ -9608,13 +9663,13 @@
         <v>-1.6627352</v>
       </c>
       <c r="K100" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L100" t="s">
         <v>97</v>
       </c>
       <c r="M100" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N100" s="3"/>
       <c r="O100" t="s">
@@ -9624,7 +9679,7 @@
         <v>78</v>
       </c>
       <c r="Q100" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R100" s="19" t="s">
         <v>83</v>
@@ -9647,13 +9702,13 @@
         <v>2018</v>
       </c>
       <c r="F101" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G101" s="15" t="s">
         <v>193</v>
       </c>
       <c r="H101" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="I101" s="7" t="str">
         <f t="shared" si="5"/>
@@ -9664,13 +9719,13 @@
         <v>-3.3156636000000002</v>
       </c>
       <c r="K101" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="L101" t="s">
         <v>97</v>
       </c>
       <c r="M101" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N101" s="3"/>
       <c r="O101" t="s">
@@ -9680,10 +9735,10 @@
         <v>78</v>
       </c>
       <c r="Q101" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R101" s="19" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -9703,7 +9758,7 @@
         <v>2018</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G102" s="15" t="s">
         <v>193</v>
@@ -9720,13 +9775,13 @@
         <v>-3.3028339</v>
       </c>
       <c r="K102" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="L102" t="s">
         <v>97</v>
       </c>
       <c r="M102" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N102" s="3"/>
       <c r="O102" t="s">
@@ -9736,10 +9791,10 @@
         <v>78</v>
       </c>
       <c r="Q102" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R102" s="19" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -9759,7 +9814,7 @@
         <v>2018</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G103" s="15" t="s">
         <v>192</v>
@@ -9776,13 +9831,13 @@
         <v>-0.7282594</v>
       </c>
       <c r="K103" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L103" t="s">
         <v>97</v>
       </c>
       <c r="M103" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N103" s="3"/>
       <c r="O103" t="s">
@@ -9792,7 +9847,7 @@
         <v>78</v>
       </c>
       <c r="Q103" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R103" s="19" t="s">
         <v>80</v>
@@ -9815,10 +9870,10 @@
         <v>2018</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H104" t="s">
         <v>457</v>
@@ -9832,13 +9887,13 @@
         <v>0.64494929999999995</v>
       </c>
       <c r="K104" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L104" t="s">
         <v>97</v>
       </c>
       <c r="M104" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N104" s="3"/>
       <c r="O104" t="s">
@@ -9848,7 +9903,7 @@
         <v>78</v>
       </c>
       <c r="Q104" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R104" s="19" t="s">
         <v>311</v>
@@ -9871,7 +9926,7 @@
         <v>2018</v>
       </c>
       <c r="F105" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G105" s="15" t="s">
         <v>191</v>
@@ -9888,13 +9943,13 @@
         <v>-7.2681152999999998</v>
       </c>
       <c r="K105" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="L105" t="s">
         <v>97</v>
       </c>
       <c r="M105" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="N105" s="3"/>
       <c r="O105" t="s">
@@ -9904,10 +9959,10 @@
         <v>78</v>
       </c>
       <c r="Q105" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R105" s="19" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -9927,7 +9982,7 @@
         <v>2018</v>
       </c>
       <c r="F106" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G106" s="15" t="s">
         <v>190</v>
@@ -9944,13 +9999,13 @@
         <v>-0.81536249999999999</v>
       </c>
       <c r="K106" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="L106" t="s">
         <v>97</v>
       </c>
       <c r="M106" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N106" s="3"/>
       <c r="O106" t="s">
@@ -9960,7 +10015,7 @@
         <v>78</v>
       </c>
       <c r="Q106" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R106" s="19" t="s">
         <v>80</v>
@@ -9983,7 +10038,7 @@
         <v>2018</v>
       </c>
       <c r="F107" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G107" s="15" t="s">
         <v>189</v>
@@ -10000,13 +10055,13 @@
         <v>-1.5426099</v>
       </c>
       <c r="K107" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L107" t="s">
         <v>97</v>
       </c>
       <c r="M107" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N107" s="3"/>
       <c r="O107" t="s">
@@ -10016,7 +10071,7 @@
         <v>78</v>
       </c>
       <c r="Q107" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R107" s="19" t="s">
         <v>84</v>
@@ -10039,7 +10094,7 @@
         <v>2018</v>
       </c>
       <c r="F108" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G108" s="15" t="s">
         <v>187</v>
@@ -10056,13 +10111,13 @@
         <v>0.19718959999999999</v>
       </c>
       <c r="K108" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="L108" t="s">
         <v>97</v>
       </c>
       <c r="M108" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N108" s="3"/>
       <c r="O108" t="s">
@@ -10072,7 +10127,7 @@
         <v>78</v>
       </c>
       <c r="Q108" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R108" s="19" t="s">
         <v>80</v>
@@ -10095,7 +10150,7 @@
         <v>2018</v>
       </c>
       <c r="F109" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G109" s="15" t="s">
         <v>188</v>
@@ -10112,13 +10167,13 @@
         <v>5.9412E-2</v>
       </c>
       <c r="K109" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L109" t="s">
         <v>97</v>
       </c>
       <c r="M109" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="N109" s="3"/>
       <c r="O109" t="s">
@@ -10128,7 +10183,7 @@
         <v>78</v>
       </c>
       <c r="Q109" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R109" s="19" t="s">
         <v>80</v>
@@ -10151,7 +10206,7 @@
         <v>2018</v>
       </c>
       <c r="F110" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G110" s="15" t="s">
         <v>186</v>
@@ -10168,13 +10223,13 @@
         <v>2.2811700000000001E-2</v>
       </c>
       <c r="K110" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="L110" t="s">
         <v>97</v>
       </c>
       <c r="M110" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="N110" s="3"/>
       <c r="O110" t="s">
@@ -10184,7 +10239,7 @@
         <v>78</v>
       </c>
       <c r="Q110" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R110" s="19" t="s">
         <v>80</v>
@@ -10207,10 +10262,10 @@
         <v>2018</v>
       </c>
       <c r="F111" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="H111" t="s">
         <v>470</v>
@@ -10224,13 +10279,13 @@
         <v>-0.38027699999999998</v>
       </c>
       <c r="K111" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="L111" t="s">
         <v>97</v>
       </c>
       <c r="M111" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="N111" s="3"/>
       <c r="O111" t="s">
@@ -10240,7 +10295,7 @@
         <v>78</v>
       </c>
       <c r="Q111" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R111" s="19" t="s">
         <v>80</v>
@@ -10263,7 +10318,7 @@
         <v>2018</v>
       </c>
       <c r="F112" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G112" s="15" t="s">
         <v>185</v>
@@ -10280,13 +10335,13 @@
         <v>1.5633500000000002E-2</v>
       </c>
       <c r="K112" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="L112" t="s">
         <v>97</v>
       </c>
       <c r="M112" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="N112" s="3"/>
       <c r="O112" t="s">
@@ -10296,7 +10351,7 @@
         <v>78</v>
       </c>
       <c r="Q112" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R112" s="19" t="s">
         <v>80</v>
@@ -10319,7 +10374,7 @@
         <v>2018</v>
       </c>
       <c r="F113" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G113" s="15" t="s">
         <v>184</v>
@@ -10336,13 +10391,13 @@
         <v>-0.43927529999999998</v>
       </c>
       <c r="K113" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="L113" t="s">
         <v>97</v>
       </c>
       <c r="M113" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="N113" s="3"/>
       <c r="O113" t="s">
@@ -10352,7 +10407,7 @@
         <v>78</v>
       </c>
       <c r="Q113" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R113" s="19" t="s">
         <v>80</v>
@@ -10375,7 +10430,7 @@
         <v>2017</v>
       </c>
       <c r="F114" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G114" s="15" t="s">
         <v>183</v>
@@ -10392,13 +10447,13 @@
         <v>-0.70656609999999997</v>
       </c>
       <c r="K114" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="L114" t="s">
         <v>97</v>
       </c>
       <c r="M114" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="N114" s="3"/>
       <c r="O114" t="s">
@@ -10408,7 +10463,7 @@
         <v>78</v>
       </c>
       <c r="Q114" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R114" s="19" t="s">
         <v>281</v>
@@ -10431,7 +10486,7 @@
         <v>2017</v>
       </c>
       <c r="F115" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G115" s="15" t="s">
         <v>182</v>
@@ -10448,13 +10503,13 @@
         <v>-0.53366979999999997</v>
       </c>
       <c r="K115" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="L115" t="s">
         <v>97</v>
       </c>
       <c r="M115" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="N115" s="3"/>
       <c r="O115" t="s">
@@ -10464,7 +10519,7 @@
         <v>78</v>
       </c>
       <c r="Q115" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R115" s="19" t="s">
         <v>80</v>
@@ -10487,7 +10542,7 @@
         <v>2017</v>
       </c>
       <c r="F116" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G116" s="15" t="s">
         <v>181</v>
@@ -10504,13 +10559,13 @@
         <v>-3.5937200000000002E-2</v>
       </c>
       <c r="K116" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L116" t="s">
         <v>97</v>
       </c>
       <c r="M116" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="N116" s="3"/>
       <c r="O116" t="s">
@@ -10520,7 +10575,7 @@
         <v>78</v>
       </c>
       <c r="Q116" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R116" s="19" t="s">
         <v>281</v>
@@ -10543,7 +10598,7 @@
         <v>2017</v>
       </c>
       <c r="F117" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G117" s="15" t="s">
         <v>481</v>
@@ -10560,13 +10615,13 @@
         <v>0.15132409999999999</v>
       </c>
       <c r="K117" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="L117" t="s">
         <v>97</v>
       </c>
       <c r="M117" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="N117" s="3"/>
       <c r="O117" t="s">
@@ -10576,7 +10631,7 @@
         <v>78</v>
       </c>
       <c r="Q117" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R117" s="19" t="s">
         <v>80</v>
@@ -10599,7 +10654,7 @@
         <v>2017</v>
       </c>
       <c r="F118" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G118" s="15" t="s">
         <v>482</v>
@@ -10616,13 +10671,13 @@
         <v>0.14296210000000001</v>
       </c>
       <c r="K118" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L118" t="s">
         <v>97</v>
       </c>
       <c r="M118" s="10" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="N118" s="3"/>
       <c r="O118" t="s">
@@ -10632,7 +10687,7 @@
         <v>78</v>
       </c>
       <c r="Q118" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R118" s="19" t="s">
         <v>80</v>
@@ -10655,7 +10710,7 @@
         <v>2017</v>
       </c>
       <c r="F119" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G119" s="15" t="s">
         <v>180</v>
@@ -10672,13 +10727,13 @@
         <v>-0.59192719999999999</v>
       </c>
       <c r="K119" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="L119" t="s">
         <v>97</v>
       </c>
       <c r="M119" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="N119" s="3"/>
       <c r="O119" t="s">
@@ -10688,7 +10743,7 @@
         <v>78</v>
       </c>
       <c r="Q119" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R119" s="19" t="s">
         <v>80</v>
@@ -10711,7 +10766,7 @@
         <v>2017</v>
       </c>
       <c r="F120" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G120" s="15" t="s">
         <v>179</v>
@@ -10728,13 +10783,13 @@
         <v>-0.80211480000000002</v>
       </c>
       <c r="K120" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L120" t="s">
         <v>97</v>
       </c>
       <c r="M120" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N120" s="3"/>
       <c r="O120" t="s">
@@ -10744,7 +10799,7 @@
         <v>78</v>
       </c>
       <c r="Q120" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R120" s="19" t="s">
         <v>80</v>
@@ -10767,7 +10822,7 @@
         <v>2017</v>
       </c>
       <c r="F121" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G121" s="15" t="s">
         <v>177</v>
@@ -10784,13 +10839,13 @@
         <v>-5.7569756999999999</v>
       </c>
       <c r="K121" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="L121" t="s">
         <v>97</v>
       </c>
       <c r="M121" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N121" s="3"/>
       <c r="O121" t="s">
@@ -10800,10 +10855,10 @@
         <v>78</v>
       </c>
       <c r="Q121" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R121" s="19" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -10823,7 +10878,7 @@
         <v>2017</v>
       </c>
       <c r="F122" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G122" s="15" t="s">
         <v>178</v>
@@ -10840,13 +10895,13 @@
         <v>-0.51671279999999997</v>
       </c>
       <c r="K122" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="L122" t="s">
         <v>97</v>
       </c>
       <c r="M122" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="N122" s="3"/>
       <c r="O122" t="s">
@@ -10856,7 +10911,7 @@
         <v>78</v>
       </c>
       <c r="Q122" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R122" s="19" t="s">
         <v>80</v>
@@ -10879,13 +10934,13 @@
         <v>2017</v>
       </c>
       <c r="F123" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G123" s="15" t="s">
         <v>493</v>
       </c>
       <c r="H123" s="15" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="I123" s="7" t="str">
         <f t="shared" si="5"/>
@@ -10896,13 +10951,13 @@
         <v>-0.31771080000000002</v>
       </c>
       <c r="K123" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="L123" t="s">
         <v>97</v>
       </c>
       <c r="M123" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N123" s="3"/>
       <c r="O123" t="s">
@@ -10912,7 +10967,7 @@
         <v>78</v>
       </c>
       <c r="Q123" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R123" s="19" t="s">
         <v>80</v>
@@ -10935,7 +10990,7 @@
         <v>2017</v>
       </c>
       <c r="F124" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G124" s="15" t="s">
         <v>492</v>
@@ -10952,13 +11007,13 @@
         <v>-0.1197907</v>
       </c>
       <c r="K124" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="L124" t="s">
         <v>97</v>
       </c>
       <c r="M124" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="N124" s="3"/>
       <c r="O124" t="s">
@@ -10968,7 +11023,7 @@
         <v>78</v>
       </c>
       <c r="Q124" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R124" s="19" t="s">
         <v>80</v>
@@ -10991,7 +11046,7 @@
         <v>2017</v>
       </c>
       <c r="F125" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G125" s="15" t="s">
         <v>170</v>
@@ -11008,13 +11063,13 @@
         <v>-7.98846E-2</v>
       </c>
       <c r="K125" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L125" t="s">
         <v>97</v>
       </c>
       <c r="M125" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="N125" s="3"/>
       <c r="O125" t="s">
@@ -11024,7 +11079,7 @@
         <v>78</v>
       </c>
       <c r="Q125" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R125" s="19" t="s">
         <v>80</v>
@@ -11047,7 +11102,7 @@
         <v>2017</v>
       </c>
       <c r="F126" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G126" s="15" t="s">
         <v>176</v>
@@ -11064,23 +11119,23 @@
         <v>-0.62325059999999999</v>
       </c>
       <c r="K126" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L126" t="s">
         <v>97</v>
       </c>
       <c r="M126" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="N126" s="3"/>
       <c r="O126" t="s">
         <v>86</v>
       </c>
       <c r="P126" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="Q126" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R126" s="19" t="s">
         <v>80</v>
@@ -11103,7 +11158,7 @@
         <v>2017</v>
       </c>
       <c r="F127" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G127" s="15" t="s">
         <v>175</v>
@@ -11120,13 +11175,13 @@
         <v>-0.1197308</v>
       </c>
       <c r="K127" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="L127" t="s">
         <v>97</v>
       </c>
       <c r="M127" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="N127" s="3"/>
       <c r="O127" t="s">
@@ -11136,7 +11191,7 @@
         <v>78</v>
       </c>
       <c r="Q127" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R127" s="19" t="s">
         <v>80</v>
@@ -11159,7 +11214,7 @@
         <v>2016</v>
       </c>
       <c r="F128" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G128" s="15" t="s">
         <v>174</v>
@@ -11176,13 +11231,13 @@
         <v>-0.28213009999999999</v>
       </c>
       <c r="K128" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="L128" t="s">
         <v>97</v>
       </c>
       <c r="M128" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="N128" s="3"/>
       <c r="O128" t="s">
@@ -11192,7 +11247,7 @@
         <v>78</v>
       </c>
       <c r="Q128" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R128" s="19" t="s">
         <v>80</v>
@@ -11215,7 +11270,7 @@
         <v>2016</v>
       </c>
       <c r="F129" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G129" s="15" t="s">
         <v>173</v>
@@ -11232,13 +11287,13 @@
         <v>-1.9804782000000001</v>
       </c>
       <c r="K129" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="L129" t="s">
         <v>97</v>
       </c>
       <c r="M129" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="N129" s="3"/>
       <c r="O129" t="s">
@@ -11248,10 +11303,10 @@
         <v>78</v>
       </c>
       <c r="Q129" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R129" s="19" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -11271,7 +11326,7 @@
         <v>2016</v>
       </c>
       <c r="F130" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G130" s="15" t="s">
         <v>172</v>
@@ -11288,13 +11343,13 @@
         <v>-0.63656729999999995</v>
       </c>
       <c r="K130" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L130" t="s">
         <v>97</v>
       </c>
       <c r="M130" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="N130" s="3"/>
       <c r="O130" t="s">
@@ -11304,7 +11359,7 @@
         <v>78</v>
       </c>
       <c r="Q130" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R130" s="19" t="s">
         <v>80</v>
@@ -11327,7 +11382,7 @@
         <v>2016</v>
       </c>
       <c r="F131" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G131" s="15" t="s">
         <v>508</v>
@@ -11344,13 +11399,13 @@
         <v>0.37464500000000001</v>
       </c>
       <c r="K131" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="L131" t="s">
         <v>97</v>
       </c>
       <c r="M131" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N131" s="3"/>
       <c r="O131" t="s">
@@ -11360,7 +11415,7 @@
         <v>78</v>
       </c>
       <c r="Q131" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R131" s="19" t="s">
         <v>80</v>
@@ -11383,7 +11438,7 @@
         <v>2016</v>
       </c>
       <c r="F132" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G132" s="15" t="s">
         <v>506</v>
@@ -11400,13 +11455,13 @@
         <v>0.37464500000000001</v>
       </c>
       <c r="K132" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="L132" t="s">
         <v>97</v>
       </c>
       <c r="M132" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="N132" s="3"/>
       <c r="O132" t="s">
@@ -11416,7 +11471,7 @@
         <v>78</v>
       </c>
       <c r="Q132" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R132" s="19" t="s">
         <v>80</v>
@@ -11439,7 +11494,7 @@
         <v>2016</v>
       </c>
       <c r="F133" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G133" s="15" t="s">
         <v>171</v>
@@ -11456,13 +11511,13 @@
         <v>-2.0977996999999999</v>
       </c>
       <c r="K133" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="L133" t="s">
         <v>97</v>
       </c>
       <c r="M133" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N133" s="3"/>
       <c r="O133" t="s">
@@ -11472,7 +11527,7 @@
         <v>78</v>
       </c>
       <c r="Q133" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R133" s="19" t="s">
         <v>84</v>
@@ -11495,7 +11550,7 @@
         <v>2016</v>
       </c>
       <c r="F134" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G134" s="15" t="s">
         <v>512</v>
@@ -11512,13 +11567,13 @@
         <v>0.17912230000000001</v>
       </c>
       <c r="K134" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="L134" t="s">
         <v>97</v>
       </c>
       <c r="M134" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="N134" s="3"/>
       <c r="O134" t="s">
@@ -11528,7 +11583,7 @@
         <v>78</v>
       </c>
       <c r="Q134" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R134" s="19" t="s">
         <v>281</v>
@@ -11551,7 +11606,7 @@
         <v>2016</v>
       </c>
       <c r="F135" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G135" s="15" t="s">
         <v>514</v>
@@ -11568,13 +11623,13 @@
         <v>0.25824150000000001</v>
       </c>
       <c r="K135" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="L135" t="s">
         <v>97</v>
       </c>
       <c r="M135" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="N135" s="3"/>
       <c r="O135" t="s">
@@ -11584,7 +11639,7 @@
         <v>78</v>
       </c>
       <c r="Q135" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R135" s="19" t="s">
         <v>81</v>
@@ -11607,7 +11662,7 @@
         <v>2016</v>
       </c>
       <c r="F136" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G136" s="15" t="s">
         <v>170</v>
@@ -11624,13 +11679,13 @@
         <v>-7.98846E-2</v>
       </c>
       <c r="K136" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="L136" t="s">
         <v>97</v>
       </c>
       <c r="M136" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="N136" s="3"/>
       <c r="O136" t="s">
@@ -11640,7 +11695,7 @@
         <v>78</v>
       </c>
       <c r="Q136" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R136" s="19" t="s">
         <v>80</v>
@@ -11663,7 +11718,7 @@
         <v>2016</v>
       </c>
       <c r="F137" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G137" s="15" t="s">
         <v>169</v>
@@ -11680,23 +11735,23 @@
         <v>-0.5202871</v>
       </c>
       <c r="K137" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="L137" t="s">
         <v>97</v>
       </c>
       <c r="M137" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N137" s="3"/>
       <c r="O137" t="s">
         <v>86</v>
       </c>
       <c r="P137" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="Q137" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R137" s="19" t="s">
         <v>80</v>
@@ -11719,7 +11774,7 @@
         <v>2016</v>
       </c>
       <c r="F138" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G138" s="15" t="s">
         <v>168</v>
@@ -11736,13 +11791,13 @@
         <v>-1.4719616</v>
       </c>
       <c r="K138" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="L138" t="s">
         <v>97</v>
       </c>
       <c r="M138" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="N138" s="3"/>
       <c r="O138" t="s">
@@ -11752,7 +11807,7 @@
         <v>78</v>
       </c>
       <c r="Q138" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R138" s="19" t="s">
         <v>281</v>
@@ -11775,7 +11830,7 @@
         <v>2015</v>
       </c>
       <c r="F139" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G139" s="15" t="s">
         <v>167</v>
@@ -11792,13 +11847,13 @@
         <v>-0.80277620000000005</v>
       </c>
       <c r="K139" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="L139" t="s">
         <v>97</v>
       </c>
       <c r="M139" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N139" s="3"/>
       <c r="O139" t="s">
@@ -11808,7 +11863,7 @@
         <v>78</v>
       </c>
       <c r="Q139" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R139" s="19" t="s">
         <v>281</v>
@@ -11831,7 +11886,7 @@
         <v>2015</v>
       </c>
       <c r="F140" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G140" s="15" t="s">
         <v>166</v>
@@ -11848,13 +11903,13 @@
         <v>-2.1610500000000001E-2</v>
       </c>
       <c r="K140" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="L140" t="s">
         <v>97</v>
       </c>
       <c r="M140" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="N140" s="3"/>
       <c r="O140" t="s">
@@ -11864,7 +11919,7 @@
         <v>78</v>
       </c>
       <c r="Q140" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R140" s="19" t="s">
         <v>80</v>
@@ -11887,7 +11942,7 @@
         <v>2015</v>
       </c>
       <c r="F141" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G141" s="15" t="s">
         <v>525</v>
@@ -11904,13 +11959,13 @@
         <v>-0.80211480000000002</v>
       </c>
       <c r="K141" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L141" t="s">
         <v>97</v>
       </c>
       <c r="M141" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="N141" s="3"/>
       <c r="O141" t="s">
@@ -11920,7 +11975,7 @@
         <v>78</v>
       </c>
       <c r="Q141" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R141" s="19" t="s">
         <v>80</v>
@@ -11943,7 +11998,7 @@
         <v>2015</v>
       </c>
       <c r="F142" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G142" s="15" t="s">
         <v>526</v>
@@ -11960,13 +12015,13 @@
         <v>-0.80211480000000002</v>
       </c>
       <c r="K142" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="L142" t="s">
         <v>97</v>
       </c>
       <c r="M142" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="N142" s="3"/>
       <c r="O142" t="s">
@@ -11976,7 +12031,7 @@
         <v>78</v>
       </c>
       <c r="Q142" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R142" s="19" t="s">
         <v>80</v>
@@ -11999,7 +12054,7 @@
         <v>2015</v>
       </c>
       <c r="F143" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G143" s="15" t="s">
         <v>528</v>
@@ -12016,13 +12071,13 @@
         <v>0.19492380000000001</v>
       </c>
       <c r="K143" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L143" t="s">
         <v>97</v>
       </c>
       <c r="M143" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="N143" s="3"/>
       <c r="O143" t="s">
@@ -12032,7 +12087,7 @@
         <v>78</v>
       </c>
       <c r="Q143" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R143" s="19" t="s">
         <v>80</v>
@@ -12055,7 +12110,7 @@
         <v>2015</v>
       </c>
       <c r="F144" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G144" s="15" t="s">
         <v>530</v>
@@ -12072,13 +12127,13 @@
         <v>0.33613019999999999</v>
       </c>
       <c r="K144" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L144" t="s">
         <v>97</v>
       </c>
       <c r="M144" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N144" s="3"/>
       <c r="O144" t="s">
@@ -12088,7 +12143,7 @@
         <v>78</v>
       </c>
       <c r="Q144" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R144" s="19" t="s">
         <v>80</v>
@@ -12111,7 +12166,7 @@
         <v>2015</v>
       </c>
       <c r="F145" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G145" s="15" t="s">
         <v>533</v>
@@ -12128,13 +12183,13 @@
         <v>-0.23676420000000001</v>
       </c>
       <c r="K145" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L145" t="s">
         <v>97</v>
       </c>
       <c r="M145" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N145" s="3"/>
       <c r="O145" t="s">
@@ -12144,7 +12199,7 @@
         <v>78</v>
       </c>
       <c r="Q145" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R145" s="19" t="s">
         <v>80</v>
@@ -12167,7 +12222,7 @@
         <v>2015</v>
       </c>
       <c r="F146" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G146" s="15" t="s">
         <v>535</v>
@@ -12184,13 +12239,13 @@
         <v>-0.23676420000000001</v>
       </c>
       <c r="K146" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L146" t="s">
         <v>97</v>
       </c>
       <c r="M146" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="N146" s="3"/>
       <c r="O146" t="s">
@@ -12200,7 +12255,7 @@
         <v>78</v>
       </c>
       <c r="Q146" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R146" s="19" t="s">
         <v>80</v>
@@ -12223,7 +12278,7 @@
         <v>2015</v>
       </c>
       <c r="F147" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G147" s="15" t="s">
         <v>537</v>
@@ -12240,13 +12295,13 @@
         <v>0.1947237</v>
       </c>
       <c r="K147" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L147" t="s">
         <v>97</v>
       </c>
       <c r="M147" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="N147" s="3"/>
       <c r="O147" t="s">
@@ -12256,7 +12311,7 @@
         <v>78</v>
       </c>
       <c r="Q147" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R147" s="19" t="s">
         <v>80</v>
@@ -12279,7 +12334,7 @@
         <v>2015</v>
       </c>
       <c r="F148" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G148" s="15" t="s">
         <v>223</v>
@@ -12296,13 +12351,13 @@
         <v>0.13082460000000001</v>
       </c>
       <c r="K148" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L148" t="s">
         <v>97</v>
       </c>
       <c r="M148" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N148" s="3"/>
       <c r="O148" t="s">
@@ -12312,7 +12367,7 @@
         <v>78</v>
       </c>
       <c r="Q148" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R148" s="19" t="s">
         <v>80</v>
@@ -12335,7 +12390,7 @@
         <v>2015</v>
       </c>
       <c r="F149" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G149" s="15" t="s">
         <v>541</v>
@@ -12352,13 +12407,13 @@
         <v>-0.29727290000000001</v>
       </c>
       <c r="K149" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L149" t="s">
         <v>97</v>
       </c>
       <c r="M149" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="N149" s="3"/>
       <c r="O149" t="s">
@@ -12368,7 +12423,7 @@
         <v>78</v>
       </c>
       <c r="Q149" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R149" s="19" t="s">
         <v>80</v>
@@ -12391,7 +12446,7 @@
         <v>2015</v>
       </c>
       <c r="F150" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G150" s="15" t="s">
         <v>543</v>
@@ -12408,23 +12463,23 @@
         <v>-0.28213009999999999</v>
       </c>
       <c r="K150" s="16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L150" t="s">
         <v>97</v>
       </c>
       <c r="M150" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="N150" s="3"/>
       <c r="O150" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="P150" t="s">
         <v>78</v>
       </c>
       <c r="Q150" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R150" s="19" t="s">
         <v>80</v>
@@ -12447,7 +12502,7 @@
         <v>2015</v>
       </c>
       <c r="F151" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G151" s="15" t="s">
         <v>545</v>
@@ -12464,23 +12519,23 @@
         <v>-0.35085169999999999</v>
       </c>
       <c r="K151" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L151" t="s">
         <v>97</v>
       </c>
       <c r="M151" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N151" s="3"/>
       <c r="O151" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="P151" t="s">
         <v>78</v>
       </c>
       <c r="Q151" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R151" s="19" t="s">
         <v>80</v>
@@ -12503,7 +12558,7 @@
         <v>2015</v>
       </c>
       <c r="F152" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G152" s="15" t="s">
         <v>547</v>
@@ -12520,13 +12575,13 @@
         <v>-2.4000925</v>
       </c>
       <c r="K152" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L152" t="s">
         <v>97</v>
       </c>
       <c r="M152" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N152" s="3"/>
       <c r="O152" t="s">
@@ -12536,7 +12591,7 @@
         <v>78</v>
       </c>
       <c r="Q152" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R152" s="19" t="s">
         <v>330</v>
@@ -12559,7 +12614,7 @@
         <v>2015</v>
       </c>
       <c r="F153" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G153" s="15" t="s">
         <v>165</v>
@@ -12576,13 +12631,13 @@
         <v>-0.43769469999999999</v>
       </c>
       <c r="K153" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L153" t="s">
         <v>97</v>
       </c>
       <c r="M153" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="N153" s="3"/>
       <c r="O153" t="s">
@@ -12592,7 +12647,7 @@
         <v>78</v>
       </c>
       <c r="Q153" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R153" s="19" t="s">
         <v>311</v>
@@ -12615,7 +12670,7 @@
         <v>2015</v>
       </c>
       <c r="F154" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G154" s="15" t="s">
         <v>163</v>
@@ -12632,13 +12687,13 @@
         <v>0.90206229999999998</v>
       </c>
       <c r="K154" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L154" t="s">
         <v>97</v>
       </c>
       <c r="M154" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="N154" s="3"/>
       <c r="O154" t="s">
@@ -12648,7 +12703,7 @@
         <v>78</v>
       </c>
       <c r="Q154" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R154" s="19" t="s">
         <v>81</v>
@@ -12671,7 +12726,7 @@
         <v>2015</v>
       </c>
       <c r="F155" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G155" s="15" t="s">
         <v>164</v>
@@ -12688,23 +12743,23 @@
         <v>-0.20173279999999999</v>
       </c>
       <c r="K155" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L155" t="s">
         <v>97</v>
       </c>
       <c r="M155" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="N155" s="3"/>
       <c r="O155" t="s">
         <v>86</v>
       </c>
       <c r="P155" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="Q155" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R155" s="19" t="s">
         <v>80</v>
@@ -12727,7 +12782,7 @@
         <v>2015</v>
       </c>
       <c r="F156" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G156" s="15" t="s">
         <v>555</v>
@@ -12744,23 +12799,23 @@
         <v>-0.53521790000000002</v>
       </c>
       <c r="K156" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L156" t="s">
         <v>97</v>
       </c>
       <c r="M156" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="N156" s="3"/>
       <c r="O156" t="s">
         <v>86</v>
       </c>
       <c r="P156" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="Q156" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R156" s="19" t="s">
         <v>80</v>
@@ -12783,7 +12838,7 @@
         <v>2015</v>
       </c>
       <c r="F157" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G157" s="15" t="s">
         <v>557</v>
@@ -12800,13 +12855,13 @@
         <v>-0.56035999999999997</v>
       </c>
       <c r="K157" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L157" t="s">
         <v>97</v>
       </c>
       <c r="M157" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N157" s="3"/>
       <c r="O157" t="s">
@@ -12816,7 +12871,7 @@
         <v>78</v>
       </c>
       <c r="Q157" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R157" s="19" t="s">
         <v>281</v>
@@ -12839,7 +12894,7 @@
         <v>2014</v>
       </c>
       <c r="F158" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G158" s="15" t="s">
         <v>162</v>
@@ -12856,13 +12911,13 @@
         <v>6.2604499999999993E-2</v>
       </c>
       <c r="K158" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L158" t="s">
         <v>97</v>
       </c>
       <c r="M158" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="N158" s="3"/>
       <c r="O158" t="s">
@@ -12872,7 +12927,7 @@
         <v>78</v>
       </c>
       <c r="Q158" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R158" s="19" t="s">
         <v>80</v>
@@ -12895,7 +12950,7 @@
         <v>2014</v>
       </c>
       <c r="F159" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G159" s="15" t="s">
         <v>562</v>
@@ -12912,13 +12967,13 @@
         <v>6.9404099999999996E-2</v>
       </c>
       <c r="K159" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L159" t="s">
         <v>97</v>
       </c>
       <c r="M159" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N159" s="3"/>
       <c r="O159" t="s">
@@ -12928,7 +12983,7 @@
         <v>78</v>
       </c>
       <c r="Q159" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R159" s="19" t="s">
         <v>80</v>
@@ -12951,7 +13006,7 @@
         <v>2014</v>
       </c>
       <c r="F160" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G160" s="15" t="s">
         <v>564</v>
@@ -12968,13 +13023,13 @@
         <v>-0.1197907</v>
       </c>
       <c r="K160" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="L160" t="s">
         <v>97</v>
       </c>
       <c r="M160" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="N160" s="3"/>
       <c r="O160" t="s">
@@ -12984,7 +13039,7 @@
         <v>78</v>
       </c>
       <c r="Q160" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R160" s="19" t="s">
         <v>80</v>
@@ -13007,7 +13062,7 @@
         <v>2014</v>
       </c>
       <c r="F161" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G161" s="15" t="s">
         <v>161</v>
@@ -13024,13 +13079,13 @@
         <v>-1.1760128999999999</v>
       </c>
       <c r="K161" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L161" t="s">
         <v>97</v>
       </c>
       <c r="M161" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="N161" s="3"/>
       <c r="O161" t="s">
@@ -13040,7 +13095,7 @@
         <v>78</v>
       </c>
       <c r="Q161" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R161" s="19" t="s">
         <v>84</v>
@@ -13063,7 +13118,7 @@
         <v>2014</v>
       </c>
       <c r="F162" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G162" s="15" t="s">
         <v>568</v>
@@ -13080,13 +13135,13 @@
         <v>8.2242499999999996E-2</v>
       </c>
       <c r="K162" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L162" t="s">
         <v>97</v>
       </c>
       <c r="M162" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="N162" s="3"/>
       <c r="O162" t="s">
@@ -13096,7 +13151,7 @@
         <v>78</v>
       </c>
       <c r="Q162" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R162" s="19" t="s">
         <v>80</v>
@@ -13119,7 +13174,7 @@
         <v>2014</v>
       </c>
       <c r="F163" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G163" s="15" t="s">
         <v>570</v>
@@ -13136,13 +13191,13 @@
         <v>8.2242499999999996E-2</v>
       </c>
       <c r="K163" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L163" t="s">
         <v>97</v>
       </c>
       <c r="M163" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="N163" s="3"/>
       <c r="O163" t="s">
@@ -13152,7 +13207,7 @@
         <v>78</v>
       </c>
       <c r="Q163" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R163" s="19" t="s">
         <v>80</v>
@@ -13175,7 +13230,7 @@
         <v>2014</v>
       </c>
       <c r="F164" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G164" s="15" t="s">
         <v>160</v>
@@ -13192,13 +13247,13 @@
         <v>-0.23676420000000001</v>
       </c>
       <c r="K164" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L164" t="s">
         <v>97</v>
       </c>
       <c r="M164" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N164" s="3"/>
       <c r="O164" t="s">
@@ -13208,7 +13263,7 @@
         <v>78</v>
       </c>
       <c r="Q164" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R164" s="19" t="s">
         <v>80</v>
@@ -13231,7 +13286,7 @@
         <v>2014</v>
       </c>
       <c r="F165" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G165" s="15" t="s">
         <v>159</v>
@@ -13248,13 +13303,13 @@
         <v>0.21614739999999999</v>
       </c>
       <c r="K165" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L165" t="s">
         <v>97</v>
       </c>
       <c r="M165" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="N165" s="3"/>
       <c r="O165" t="s">
@@ -13264,7 +13319,7 @@
         <v>78</v>
       </c>
       <c r="Q165" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R165" s="19" t="s">
         <v>80</v>
@@ -13287,7 +13342,7 @@
         <v>2014</v>
       </c>
       <c r="F166" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G166" s="15" t="s">
         <v>158</v>
@@ -13304,13 +13359,13 @@
         <v>-0.25697730000000002</v>
       </c>
       <c r="K166" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="L166" t="s">
         <v>97</v>
       </c>
       <c r="M166" s="10" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="N166" s="3"/>
       <c r="O166" t="s">
@@ -13320,7 +13375,7 @@
         <v>78</v>
       </c>
       <c r="Q166" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R166" s="19" t="s">
         <v>80</v>
@@ -13343,7 +13398,7 @@
         <v>2014</v>
       </c>
       <c r="F167" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G167" s="15" t="s">
         <v>576</v>
@@ -13360,13 +13415,13 @@
         <v>-0.6173497</v>
       </c>
       <c r="K167" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="L167" t="s">
         <v>97</v>
       </c>
       <c r="M167" s="10" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="N167" s="3"/>
       <c r="O167" t="s">
@@ -13376,7 +13431,7 @@
         <v>78</v>
       </c>
       <c r="Q167" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R167" s="19" t="s">
         <v>83</v>
@@ -13399,7 +13454,7 @@
         <v>2014</v>
       </c>
       <c r="F168" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G168" s="15" t="s">
         <v>578</v>
@@ -13416,13 +13471,13 @@
         <v>-0.4062867</v>
       </c>
       <c r="K168" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="L168" t="s">
         <v>97</v>
       </c>
       <c r="M168" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="N168" s="3"/>
       <c r="O168" t="s">
@@ -13432,7 +13487,7 @@
         <v>78</v>
       </c>
       <c r="Q168" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R168" s="19" t="s">
         <v>80</v>
@@ -13455,7 +13510,7 @@
         <v>2014</v>
       </c>
       <c r="F169" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G169" s="15" t="s">
         <v>580</v>
@@ -13472,13 +13527,13 @@
         <v>0.62387959999999998</v>
       </c>
       <c r="K169" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L169" t="s">
         <v>97</v>
       </c>
       <c r="M169" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="N169" s="3"/>
       <c r="O169" t="s">
@@ -13488,7 +13543,7 @@
         <v>78</v>
       </c>
       <c r="Q169" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R169" s="19" t="s">
         <v>80</v>
@@ -13511,7 +13566,7 @@
         <v>2014</v>
       </c>
       <c r="F170" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G170" s="15" t="s">
         <v>582</v>
@@ -13528,13 +13583,13 @@
         <v>0.65281750000000005</v>
       </c>
       <c r="K170" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L170" t="s">
         <v>97</v>
       </c>
       <c r="M170" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="N170" s="3"/>
       <c r="O170" t="s">
@@ -13544,7 +13599,7 @@
         <v>78</v>
       </c>
       <c r="Q170" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R170" s="19" t="s">
         <v>80</v>
@@ -13567,7 +13622,7 @@
         <v>2014</v>
       </c>
       <c r="F171" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G171" s="15" t="s">
         <v>157</v>
@@ -13584,23 +13639,23 @@
         <v>-1.8201556999999999</v>
       </c>
       <c r="K171" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L171" t="s">
         <v>97</v>
       </c>
       <c r="M171" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="N171" s="3"/>
       <c r="O171" t="s">
         <v>86</v>
       </c>
       <c r="P171" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="Q171" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R171" s="19" t="s">
         <v>83</v>
@@ -13623,7 +13678,7 @@
         <v>2014</v>
       </c>
       <c r="F172" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G172" s="15" t="s">
         <v>156</v>
@@ -13640,23 +13695,23 @@
         <v>-0.1054061</v>
       </c>
       <c r="K172" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="L172" t="s">
         <v>97</v>
       </c>
       <c r="M172" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="N172" s="3"/>
       <c r="O172" t="s">
         <v>86</v>
       </c>
       <c r="P172" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="Q172" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R172" s="19" t="s">
         <v>80</v>
@@ -13679,7 +13734,7 @@
         <v>2014</v>
       </c>
       <c r="F173" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G173" s="15" t="s">
         <v>155</v>
@@ -13696,13 +13751,13 @@
         <v>-0.93820729999999997</v>
       </c>
       <c r="K173" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L173" t="s">
         <v>97</v>
       </c>
       <c r="M173" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="N173" s="3"/>
       <c r="O173" t="s">
@@ -13712,7 +13767,7 @@
         <v>78</v>
       </c>
       <c r="Q173" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R173" s="19" t="s">
         <v>83</v>
@@ -13735,7 +13790,7 @@
         <v>2013</v>
       </c>
       <c r="F174" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G174" s="15" t="s">
         <v>154</v>
@@ -13752,13 +13807,13 @@
         <v>-1.2172527</v>
       </c>
       <c r="K174" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L174" t="s">
         <v>97</v>
       </c>
       <c r="M174" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N174" s="3"/>
       <c r="O174" t="s">
@@ -13768,7 +13823,7 @@
         <v>78</v>
       </c>
       <c r="Q174" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R174" s="19" t="s">
         <v>281</v>
@@ -13791,7 +13846,7 @@
         <v>2013</v>
       </c>
       <c r="F175" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G175" s="15" t="s">
         <v>153</v>
@@ -13808,13 +13863,13 @@
         <v>-0.80211480000000002</v>
       </c>
       <c r="K175" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="L175" t="s">
         <v>97</v>
       </c>
       <c r="M175" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="N175" s="3"/>
       <c r="O175" t="s">
@@ -13824,7 +13879,7 @@
         <v>78</v>
       </c>
       <c r="Q175" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R175" s="19" t="s">
         <v>80</v>
@@ -13847,7 +13902,7 @@
         <v>2013</v>
       </c>
       <c r="F176" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G176" s="15" t="s">
         <v>152</v>
@@ -13864,13 +13919,13 @@
         <v>2.2766399999999999E-2</v>
       </c>
       <c r="K176" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L176" t="s">
         <v>97</v>
       </c>
       <c r="M176" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="N176" s="3"/>
       <c r="O176" t="s">
@@ -13880,7 +13935,7 @@
         <v>78</v>
       </c>
       <c r="Q176" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R176" s="19" t="s">
         <v>80</v>
@@ -13903,7 +13958,7 @@
         <v>2013</v>
       </c>
       <c r="F177" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G177" s="15" t="s">
         <v>594</v>
@@ -13920,13 +13975,13 @@
         <v>0.60203200000000001</v>
       </c>
       <c r="K177" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L177" t="s">
         <v>97</v>
       </c>
       <c r="M177" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="N177" s="3"/>
       <c r="O177" t="s">
@@ -13936,7 +13991,7 @@
         <v>298</v>
       </c>
       <c r="Q177" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R177" s="19" t="s">
         <v>80</v>
@@ -13959,7 +14014,7 @@
         <v>2013</v>
       </c>
       <c r="F178" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G178" s="15" t="s">
         <v>151</v>
@@ -13976,13 +14031,13 @@
         <v>0.60203200000000001</v>
       </c>
       <c r="K178" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L178" t="s">
         <v>97</v>
       </c>
       <c r="M178" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="N178" s="3"/>
       <c r="O178" t="s">
@@ -13992,7 +14047,7 @@
         <v>298</v>
       </c>
       <c r="Q178" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R178" s="19" t="s">
         <v>80</v>
@@ -14015,7 +14070,7 @@
         <v>2013</v>
       </c>
       <c r="F179" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G179" s="15" t="s">
         <v>597</v>
@@ -14032,13 +14087,13 @@
         <v>-0.23010449999999999</v>
       </c>
       <c r="K179" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L179" t="s">
         <v>97</v>
       </c>
       <c r="M179" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="N179" s="3"/>
       <c r="O179" t="s">
@@ -14048,7 +14103,7 @@
         <v>78</v>
       </c>
       <c r="Q179" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R179" s="19" t="s">
         <v>80</v>
@@ -14071,7 +14126,7 @@
         <v>2013</v>
       </c>
       <c r="F180" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G180" s="15" t="s">
         <v>599</v>
@@ -14088,13 +14143,13 @@
         <v>-0.23010449999999999</v>
       </c>
       <c r="K180" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L180" t="s">
         <v>97</v>
       </c>
       <c r="M180" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="N180" s="3"/>
       <c r="O180" t="s">
@@ -14104,7 +14159,7 @@
         <v>78</v>
       </c>
       <c r="Q180" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R180" s="19" t="s">
         <v>80</v>
@@ -14127,7 +14182,7 @@
         <v>2013</v>
       </c>
       <c r="F181" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G181" s="15" t="s">
         <v>601</v>
@@ -14144,13 +14199,13 @@
         <v>-0.23010449999999999</v>
       </c>
       <c r="K181" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L181" t="s">
         <v>97</v>
       </c>
       <c r="M181" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="N181" s="3"/>
       <c r="O181" t="s">
@@ -14160,7 +14215,7 @@
         <v>78</v>
       </c>
       <c r="Q181" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R181" s="19" t="s">
         <v>80</v>
@@ -14183,7 +14238,7 @@
         <v>2013</v>
       </c>
       <c r="F182" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G182" s="15" t="s">
         <v>150</v>
@@ -14200,13 +14255,13 @@
         <v>0.21528269999999999</v>
       </c>
       <c r="K182" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L182" t="s">
         <v>97</v>
       </c>
       <c r="M182" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="N182" s="3"/>
       <c r="O182" t="s">
@@ -14216,7 +14271,7 @@
         <v>78</v>
       </c>
       <c r="Q182" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R182" s="19" t="s">
         <v>80</v>
@@ -14239,7 +14294,7 @@
         <v>2013</v>
       </c>
       <c r="F183" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G183" s="15" t="s">
         <v>605</v>
@@ -14256,13 +14311,13 @@
         <v>3.7993300000000001E-2</v>
       </c>
       <c r="K183" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L183" t="s">
         <v>97</v>
       </c>
       <c r="M183" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="N183" s="3"/>
       <c r="O183" t="s">
@@ -14272,7 +14327,7 @@
         <v>78</v>
       </c>
       <c r="Q183" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R183" s="19" t="s">
         <v>281</v>
@@ -14295,7 +14350,7 @@
         <v>2013</v>
       </c>
       <c r="F184" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G184" s="15" t="s">
         <v>607</v>
@@ -14312,13 +14367,13 @@
         <v>0.17911869999999999</v>
       </c>
       <c r="K184" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L184" t="s">
         <v>97</v>
       </c>
       <c r="M184" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="N184" s="3"/>
       <c r="O184" t="s">
@@ -14328,7 +14383,7 @@
         <v>78</v>
       </c>
       <c r="Q184" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R184" s="19" t="s">
         <v>281</v>
@@ -14351,7 +14406,7 @@
         <v>2013</v>
       </c>
       <c r="F185" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G185" s="15" t="s">
         <v>609</v>
@@ -14368,13 +14423,13 @@
         <v>-2.5899448</v>
       </c>
       <c r="K185" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L185" t="s">
         <v>97</v>
       </c>
       <c r="M185" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="N185" s="3"/>
       <c r="O185" t="s">
@@ -14384,7 +14439,7 @@
         <v>78</v>
       </c>
       <c r="Q185" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R185" s="19" t="s">
         <v>357</v>
@@ -14407,7 +14462,7 @@
         <v>2013</v>
       </c>
       <c r="F186" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G186" s="15" t="s">
         <v>610</v>
@@ -14424,13 +14479,13 @@
         <v>-2.5173668</v>
       </c>
       <c r="K186" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L186" t="s">
         <v>97</v>
       </c>
       <c r="M186" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="N186" s="3"/>
       <c r="O186" t="s">
@@ -14440,7 +14495,7 @@
         <v>78</v>
       </c>
       <c r="Q186" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R186" s="19" t="s">
         <v>390</v>
@@ -14463,7 +14518,7 @@
         <v>2013</v>
       </c>
       <c r="F187" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G187" s="15" t="s">
         <v>149</v>
@@ -14480,13 +14535,13 @@
         <v>-0.49950689999999998</v>
       </c>
       <c r="K187" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L187" t="s">
         <v>97</v>
       </c>
       <c r="M187" s="10" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="N187" s="3"/>
       <c r="O187" t="s">
@@ -14496,7 +14551,7 @@
         <v>78</v>
       </c>
       <c r="Q187" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R187" s="19" t="s">
         <v>311</v>
@@ -14519,7 +14574,7 @@
         <v>2013</v>
       </c>
       <c r="F188" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G188" s="15" t="s">
         <v>148</v>
@@ -14536,13 +14591,13 @@
         <v>-0.79158209999999996</v>
       </c>
       <c r="K188" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L188" t="s">
         <v>97</v>
       </c>
       <c r="M188" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="N188" s="3"/>
       <c r="O188" t="s">
@@ -14552,7 +14607,7 @@
         <v>78</v>
       </c>
       <c r="Q188" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R188" s="19" t="s">
         <v>80</v>
@@ -14575,10 +14630,10 @@
         <v>2013</v>
       </c>
       <c r="F189" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G189" s="15" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H189" s="15" t="s">
         <v>147</v>
@@ -14592,13 +14647,13 @@
         <v>-8.1518199999999999E-2</v>
       </c>
       <c r="K189" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L189" t="s">
         <v>97</v>
       </c>
       <c r="M189" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="N189" s="3"/>
       <c r="O189" t="s">
@@ -14608,7 +14663,7 @@
         <v>78</v>
       </c>
       <c r="Q189" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R189" s="19" t="s">
         <v>80</v>
@@ -14631,7 +14686,7 @@
         <v>2012</v>
       </c>
       <c r="F190" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G190" s="15" t="s">
         <v>618</v>
@@ -14648,13 +14703,13 @@
         <v>-0.466146</v>
       </c>
       <c r="K190" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L190" t="s">
         <v>97</v>
       </c>
       <c r="M190" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="N190" s="3"/>
       <c r="O190" t="s">
@@ -14664,10 +14719,10 @@
         <v>78</v>
       </c>
       <c r="Q190" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R190" s="19" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="191" spans="1:18">
@@ -14687,7 +14742,7 @@
         <v>2012</v>
       </c>
       <c r="F191" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G191" s="15" t="s">
         <v>618</v>
@@ -14704,13 +14759,13 @@
         <v>-0.30641659999999998</v>
       </c>
       <c r="K191" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="L191" t="s">
         <v>97</v>
       </c>
       <c r="M191" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="N191" s="3"/>
       <c r="O191" t="s">
@@ -14720,10 +14775,10 @@
         <v>78</v>
       </c>
       <c r="Q191" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R191" s="19" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="192" spans="1:18">
@@ -14743,7 +14798,7 @@
         <v>2012</v>
       </c>
       <c r="F192" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G192" s="15" t="s">
         <v>146</v>
@@ -14760,13 +14815,13 @@
         <v>-2.1610500000000001E-2</v>
       </c>
       <c r="K192" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="L192" t="s">
         <v>97</v>
       </c>
       <c r="M192" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="N192" s="3"/>
       <c r="O192" t="s">
@@ -14776,7 +14831,7 @@
         <v>78</v>
       </c>
       <c r="Q192" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R192" s="19" t="s">
         <v>80</v>
@@ -14799,7 +14854,7 @@
         <v>2012</v>
       </c>
       <c r="F193" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G193" s="15" t="s">
         <v>145</v>
@@ -14816,13 +14871,13 @@
         <v>-0.32664290000000001</v>
       </c>
       <c r="K193" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L193" t="s">
         <v>97</v>
       </c>
       <c r="M193" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="N193" s="3"/>
       <c r="O193" t="s">
@@ -14832,7 +14887,7 @@
         <v>78</v>
       </c>
       <c r="Q193" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R193" s="19" t="s">
         <v>80</v>
@@ -14855,7 +14910,7 @@
         <v>2012</v>
       </c>
       <c r="F194" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G194" s="15" t="s">
         <v>144</v>
@@ -14864,21 +14919,21 @@
         <v>534</v>
       </c>
       <c r="I194" s="7" t="str">
-        <f t="shared" ref="I194:I250" si="9">MID(K194,FIND("@",K194)+1,FIND(",",K194,FIND("@",K194))-FIND("@",K194)-1)</f>
+        <f t="shared" ref="I194:I249" si="9">MID(K194,FIND("@",K194)+1,FIND(",",K194,FIND("@",K194))-FIND("@",K194)-1)</f>
         <v>42.7610304</v>
       </c>
       <c r="J194" s="7">
-        <f t="shared" ref="J194:J250" si="10">VALUE(SUBSTITUTE(MID(K194,FIND(",",K194,FIND("@",K194))+1,FIND(",",K194,FIND(",",K194,FIND("@",K194))+1)-FIND(",",K194,FIND("@",K194))-1),".",","))</f>
+        <f t="shared" ref="J194:J249" si="10">VALUE(SUBSTITUTE(MID(K194,FIND(",",K194,FIND("@",K194))+1,FIND(",",K194,FIND(",",K194,FIND("@",K194))+1)-FIND(",",K194,FIND("@",K194))-1),".",","))</f>
         <v>-0.23676420000000001</v>
       </c>
       <c r="K194" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L194" t="s">
         <v>97</v>
       </c>
       <c r="M194" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="N194" s="3"/>
       <c r="O194" t="s">
@@ -14888,7 +14943,7 @@
         <v>78</v>
       </c>
       <c r="Q194" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R194" s="19" t="s">
         <v>80</v>
@@ -14911,7 +14966,7 @@
         <v>2012</v>
       </c>
       <c r="F195" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G195" s="15" t="s">
         <v>625</v>
@@ -14928,13 +14983,13 @@
         <v>-0.65815349999999995</v>
       </c>
       <c r="K195" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L195" t="s">
         <v>97</v>
       </c>
       <c r="M195" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="N195" s="3"/>
       <c r="O195" t="s">
@@ -14944,7 +14999,7 @@
         <v>78</v>
       </c>
       <c r="Q195" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R195" s="19" t="s">
         <v>80</v>
@@ -14967,7 +15022,7 @@
         <v>2012</v>
       </c>
       <c r="F196" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G196" s="15" t="s">
         <v>209</v>
@@ -14984,13 +15039,13 @@
         <v>-0.76221879999999997</v>
       </c>
       <c r="K196" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L196" t="s">
         <v>97</v>
       </c>
       <c r="M196" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="N196" s="3"/>
       <c r="O196" t="s">
@@ -15000,7 +15055,7 @@
         <v>78</v>
       </c>
       <c r="Q196" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R196" s="19" t="s">
         <v>80</v>
@@ -15023,7 +15078,7 @@
         <v>2012</v>
       </c>
       <c r="F197" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G197" s="15" t="s">
         <v>143</v>
@@ -15040,13 +15095,13 @@
         <v>0.17911869999999999</v>
       </c>
       <c r="K197" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L197" t="s">
         <v>97</v>
       </c>
       <c r="M197" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="N197" s="3"/>
       <c r="O197" t="s">
@@ -15056,7 +15111,7 @@
         <v>78</v>
       </c>
       <c r="Q197" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R197" s="19" t="s">
         <v>281</v>
@@ -15079,7 +15134,7 @@
         <v>2012</v>
       </c>
       <c r="F198" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G198" s="15" t="s">
         <v>142</v>
@@ -15096,13 +15151,13 @@
         <v>0.18948789999999999</v>
       </c>
       <c r="K198" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L198" t="s">
         <v>97</v>
       </c>
       <c r="M198" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="N198" s="3"/>
       <c r="O198" t="s">
@@ -15112,7 +15167,7 @@
         <v>78</v>
       </c>
       <c r="Q198" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R198" s="19" t="s">
         <v>80</v>
@@ -15135,7 +15190,7 @@
         <v>2012</v>
       </c>
       <c r="F199" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G199" s="15" t="s">
         <v>141</v>
@@ -15152,13 +15207,13 @@
         <v>0.14296210000000001</v>
       </c>
       <c r="K199" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="L199" t="s">
         <v>97</v>
       </c>
       <c r="M199" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="N199" s="3"/>
       <c r="O199" t="s">
@@ -15168,7 +15223,7 @@
         <v>78</v>
       </c>
       <c r="Q199" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R199" s="19" t="s">
         <v>80</v>
@@ -15191,7 +15246,7 @@
         <v>2012</v>
       </c>
       <c r="F200" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G200" s="15" t="s">
         <v>141</v>
@@ -15208,13 +15263,13 @@
         <v>1.5633500000000002E-2</v>
       </c>
       <c r="K200" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="L200" t="s">
         <v>97</v>
       </c>
       <c r="M200" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="N200" s="3"/>
       <c r="O200" t="s">
@@ -15224,7 +15279,7 @@
         <v>78</v>
       </c>
       <c r="Q200" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R200" s="19" t="s">
         <v>80</v>
@@ -15247,7 +15302,7 @@
         <v>2012</v>
       </c>
       <c r="F201" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G201" s="15" t="s">
         <v>140</v>
@@ -15264,13 +15319,13 @@
         <v>-0.72897630000000002</v>
       </c>
       <c r="K201" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="L201" t="s">
         <v>97</v>
       </c>
       <c r="M201" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="N201" s="3"/>
       <c r="O201" t="s">
@@ -15280,7 +15335,7 @@
         <v>78</v>
       </c>
       <c r="Q201" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R201" s="19" t="s">
         <v>281</v>
@@ -15303,7 +15358,7 @@
         <v>2012</v>
       </c>
       <c r="F202" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G202" s="15" t="s">
         <v>139</v>
@@ -15320,13 +15375,13 @@
         <v>-1.3351447000000001</v>
       </c>
       <c r="K202" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="L202" t="s">
         <v>97</v>
       </c>
       <c r="M202" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="N202" s="3"/>
       <c r="O202" t="s">
@@ -15336,7 +15391,7 @@
         <v>78</v>
       </c>
       <c r="Q202" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R202" s="19" t="s">
         <v>83</v>
@@ -15359,7 +15414,7 @@
         <v>2011</v>
       </c>
       <c r="F203" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G203" s="15" t="s">
         <v>138</v>
@@ -15376,13 +15431,13 @@
         <v>-0.51267479999999999</v>
       </c>
       <c r="K203" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L203" t="s">
         <v>97</v>
       </c>
       <c r="M203" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="N203" s="3"/>
       <c r="O203" t="s">
@@ -15392,7 +15447,7 @@
         <v>78</v>
       </c>
       <c r="Q203" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R203" s="19" t="s">
         <v>83</v>
@@ -15415,7 +15470,7 @@
         <v>2011</v>
       </c>
       <c r="F204" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G204" s="15" t="s">
         <v>137</v>
@@ -15432,13 +15487,13 @@
         <v>-0.30449759999999998</v>
       </c>
       <c r="K204" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="L204" t="s">
         <v>97</v>
       </c>
       <c r="M204" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="N204" s="3"/>
       <c r="O204" t="s">
@@ -15448,7 +15503,7 @@
         <v>78</v>
       </c>
       <c r="Q204" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R204" s="19" t="s">
         <v>80</v>
@@ -15471,7 +15526,7 @@
         <v>2011</v>
       </c>
       <c r="F205" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G205" s="15" t="s">
         <v>136</v>
@@ -15488,13 +15543,13 @@
         <v>0.2154124</v>
       </c>
       <c r="K205" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="L205" t="s">
         <v>97</v>
       </c>
       <c r="M205" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="N205" s="3"/>
       <c r="O205" t="s">
@@ -15504,7 +15559,7 @@
         <v>78</v>
       </c>
       <c r="Q205" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R205" s="19" t="s">
         <v>80</v>
@@ -15527,7 +15582,7 @@
         <v>2011</v>
       </c>
       <c r="F206" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G206" s="15" t="s">
         <v>641</v>
@@ -15544,13 +15599,13 @@
         <v>-0.45867639999999998</v>
       </c>
       <c r="K206" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="L206" t="s">
         <v>97</v>
       </c>
       <c r="M206" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="N206" s="3"/>
       <c r="O206" t="s">
@@ -15560,7 +15615,7 @@
         <v>78</v>
       </c>
       <c r="Q206" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R206" s="19" t="s">
         <v>311</v>
@@ -15583,10 +15638,10 @@
         <v>2011</v>
       </c>
       <c r="F207" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G207" s="15" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="H207" s="15" t="s">
         <v>643</v>
@@ -15600,13 +15655,13 @@
         <v>-0.49376930000000002</v>
       </c>
       <c r="K207" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="L207" t="s">
         <v>97</v>
       </c>
       <c r="M207" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="N207" s="3"/>
       <c r="O207" t="s">
@@ -15616,7 +15671,7 @@
         <v>78</v>
       </c>
       <c r="Q207" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R207" s="19" t="s">
         <v>311</v>
@@ -15639,7 +15694,7 @@
         <v>2011</v>
       </c>
       <c r="F208" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G208" s="15" t="s">
         <v>135</v>
@@ -15656,13 +15711,13 @@
         <v>-0.33615020000000001</v>
       </c>
       <c r="K208" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="L208" t="s">
         <v>97</v>
       </c>
       <c r="M208" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="N208" s="3"/>
       <c r="O208" t="s">
@@ -15672,7 +15727,7 @@
         <v>298</v>
       </c>
       <c r="Q208" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R208" s="19" t="s">
         <v>80</v>
@@ -15695,7 +15750,7 @@
         <v>2011</v>
       </c>
       <c r="F209" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G209" s="15" t="s">
         <v>646</v>
@@ -15712,13 +15767,13 @@
         <v>-0.53366979999999997</v>
       </c>
       <c r="K209" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L209" t="s">
         <v>97</v>
       </c>
       <c r="M209" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="N209" s="3"/>
       <c r="O209" t="s">
@@ -15728,7 +15783,7 @@
         <v>298</v>
       </c>
       <c r="Q209" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R209" s="19" t="s">
         <v>80</v>
@@ -15751,7 +15806,7 @@
         <v>2011</v>
       </c>
       <c r="F210" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G210" s="15" t="s">
         <v>647</v>
@@ -15768,13 +15823,13 @@
         <v>-0.63656729999999995</v>
       </c>
       <c r="K210" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="L210" t="s">
         <v>97</v>
       </c>
       <c r="M210" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="N210" s="3"/>
       <c r="O210" t="s">
@@ -15784,7 +15839,7 @@
         <v>298</v>
       </c>
       <c r="Q210" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R210" s="19" t="s">
         <v>80</v>
@@ -15807,7 +15862,7 @@
         <v>2011</v>
       </c>
       <c r="F211" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G211" s="15" t="s">
         <v>648</v>
@@ -15824,13 +15879,13 @@
         <v>-0.63656729999999995</v>
       </c>
       <c r="K211" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="L211" t="s">
         <v>97</v>
       </c>
       <c r="M211" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="N211" s="3"/>
       <c r="O211" t="s">
@@ -15840,7 +15895,7 @@
         <v>298</v>
       </c>
       <c r="Q211" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R211" s="19" t="s">
         <v>80</v>
@@ -15863,7 +15918,7 @@
         <v>2011</v>
       </c>
       <c r="F212" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G212" s="15" t="s">
         <v>134</v>
@@ -15880,13 +15935,13 @@
         <v>-7.98846E-2</v>
       </c>
       <c r="K212" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="L212" t="s">
         <v>97</v>
       </c>
       <c r="M212" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="N212" s="3"/>
       <c r="O212" t="s">
@@ -15896,7 +15951,7 @@
         <v>78</v>
       </c>
       <c r="Q212" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R212" s="19" t="s">
         <v>80</v>
@@ -15919,7 +15974,7 @@
         <v>2011</v>
       </c>
       <c r="F213" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G213" s="15" t="s">
         <v>651</v>
@@ -15936,13 +15991,13 @@
         <v>0.69295439999999997</v>
       </c>
       <c r="K213" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="L213" t="s">
         <v>97</v>
       </c>
       <c r="M213" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="N213" s="3"/>
       <c r="O213" t="s">
@@ -15952,7 +16007,7 @@
         <v>78</v>
       </c>
       <c r="Q213" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R213" s="19" t="s">
         <v>81</v>
@@ -15975,7 +16030,7 @@
         <v>2011</v>
       </c>
       <c r="F214" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G214" s="15" t="s">
         <v>653</v>
@@ -15992,13 +16047,13 @@
         <v>0.79681880000000005</v>
       </c>
       <c r="K214" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="L214" t="s">
         <v>97</v>
       </c>
       <c r="M214" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="N214" s="3"/>
       <c r="O214" t="s">
@@ -16008,7 +16063,7 @@
         <v>78</v>
       </c>
       <c r="Q214" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R214" s="19" t="s">
         <v>81</v>
@@ -16031,7 +16086,7 @@
         <v>2011</v>
       </c>
       <c r="F215" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G215" s="15" t="s">
         <v>133</v>
@@ -16048,13 +16103,13 @@
         <v>-0.28213009999999999</v>
       </c>
       <c r="K215" s="16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L215" t="s">
         <v>97</v>
       </c>
       <c r="M215" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="N215" s="3"/>
       <c r="O215" t="s">
@@ -16064,7 +16119,7 @@
         <v>78</v>
       </c>
       <c r="Q215" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R215" s="19" t="s">
         <v>80</v>
@@ -16087,7 +16142,7 @@
         <v>2011</v>
       </c>
       <c r="F216" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G216" s="15" t="s">
         <v>132</v>
@@ -16104,13 +16159,13 @@
         <v>-0.53366979999999997</v>
       </c>
       <c r="K216" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L216" t="s">
         <v>97</v>
       </c>
       <c r="M216" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N216" s="3"/>
       <c r="O216" t="s">
@@ -16120,7 +16175,7 @@
         <v>78</v>
       </c>
       <c r="Q216" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R216" s="19" t="s">
         <v>80</v>
@@ -16143,7 +16198,7 @@
         <v>2011</v>
       </c>
       <c r="F217" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G217" s="15" t="s">
         <v>105</v>
@@ -16160,13 +16215,13 @@
         <v>-0.28305079999999999</v>
       </c>
       <c r="K217" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="L217" t="s">
         <v>97</v>
       </c>
       <c r="M217" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="N217" s="3"/>
       <c r="O217" t="s">
@@ -16176,7 +16231,7 @@
         <v>78</v>
       </c>
       <c r="Q217" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R217" s="19" t="s">
         <v>80</v>
@@ -16199,10 +16254,10 @@
         <v>2011</v>
       </c>
       <c r="F218" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H218" s="15" t="s">
         <v>131</v>
@@ -16216,13 +16271,13 @@
         <v>-1.2160280000000001</v>
       </c>
       <c r="K218" s="10" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="L218" t="s">
         <v>97</v>
       </c>
       <c r="M218" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="N218" s="3"/>
       <c r="O218" t="s">
@@ -16232,7 +16287,7 @@
         <v>78</v>
       </c>
       <c r="Q218" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R218" s="19" t="s">
         <v>83</v>
@@ -16255,7 +16310,7 @@
         <v>2010</v>
       </c>
       <c r="F219" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G219" s="15" t="s">
         <v>130</v>
@@ -16272,13 +16327,13 @@
         <v>-1.9144475000000001</v>
       </c>
       <c r="K219" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L219" t="s">
         <v>97</v>
       </c>
       <c r="M219" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="N219" s="3"/>
       <c r="O219" t="s">
@@ -16288,7 +16343,7 @@
         <v>78</v>
       </c>
       <c r="Q219" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R219" s="19" t="s">
         <v>83</v>
@@ -16311,7 +16366,7 @@
         <v>2010</v>
       </c>
       <c r="F220" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G220" s="15" t="s">
         <v>129</v>
@@ -16328,13 +16383,13 @@
         <v>-1.6796218000000001</v>
       </c>
       <c r="K220" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="L220" t="s">
         <v>97</v>
       </c>
       <c r="M220" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="N220" s="3"/>
       <c r="O220" t="s">
@@ -16344,7 +16399,7 @@
         <v>78</v>
       </c>
       <c r="Q220" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R220" s="19" t="s">
         <v>83</v>
@@ -16367,7 +16422,7 @@
         <v>2010</v>
       </c>
       <c r="F221" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G221" s="15" t="s">
         <v>665</v>
@@ -16384,13 +16439,13 @@
         <v>-0.75527650000000002</v>
       </c>
       <c r="K221" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="L221" t="s">
         <v>97</v>
       </c>
       <c r="M221" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N221" s="3"/>
       <c r="O221" t="s">
@@ -16400,7 +16455,7 @@
         <v>78</v>
       </c>
       <c r="Q221" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R221" s="19" t="s">
         <v>80</v>
@@ -16423,7 +16478,7 @@
         <v>2010</v>
       </c>
       <c r="F222" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G222" s="15" t="s">
         <v>664</v>
@@ -16440,13 +16495,13 @@
         <v>-0.80441079999999998</v>
       </c>
       <c r="K222" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="L222" t="s">
         <v>97</v>
       </c>
       <c r="M222" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="N222" s="3"/>
       <c r="O222" t="s">
@@ -16456,7 +16511,7 @@
         <v>78</v>
       </c>
       <c r="Q222" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R222" s="19" t="s">
         <v>80</v>
@@ -16479,7 +16534,7 @@
         <v>2010</v>
       </c>
       <c r="F223" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G223" s="15" t="s">
         <v>128</v>
@@ -16496,13 +16551,13 @@
         <v>-4.9033899999999998E-2</v>
       </c>
       <c r="K223" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="L223" t="s">
         <v>97</v>
       </c>
       <c r="M223" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="N223" s="3"/>
       <c r="O223" t="s">
@@ -16512,7 +16567,7 @@
         <v>78</v>
       </c>
       <c r="Q223" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R223" s="19" t="s">
         <v>80</v>
@@ -16535,7 +16590,7 @@
         <v>2010</v>
       </c>
       <c r="F224" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G224" s="15" t="s">
         <v>126</v>
@@ -16552,13 +16607,13 @@
         <v>-0.5202871</v>
       </c>
       <c r="K224" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="L224" t="s">
         <v>97</v>
       </c>
       <c r="M224" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="N224" s="3"/>
       <c r="O224" t="s">
@@ -16568,7 +16623,7 @@
         <v>78</v>
       </c>
       <c r="Q224" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R224" s="19" t="s">
         <v>80</v>
@@ -16591,7 +16646,7 @@
         <v>2010</v>
       </c>
       <c r="F225" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G225" s="15" t="s">
         <v>125</v>
@@ -16608,13 +16663,13 @@
         <v>-1.5773185999999999</v>
       </c>
       <c r="K225" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="L225" t="s">
         <v>97</v>
       </c>
       <c r="M225" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N225" s="3"/>
       <c r="O225" t="s">
@@ -16624,7 +16679,7 @@
         <v>78</v>
       </c>
       <c r="Q225" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R225" s="19" t="s">
         <v>281</v>
@@ -16647,7 +16702,7 @@
         <v>2010</v>
       </c>
       <c r="F226" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G226" s="15" t="s">
         <v>124</v>
@@ -16664,13 +16719,13 @@
         <v>-0.7282594</v>
       </c>
       <c r="K226" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L226" t="s">
         <v>97</v>
       </c>
       <c r="M226" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N226" s="3"/>
       <c r="O226" t="s">
@@ -16680,7 +16735,7 @@
         <v>78</v>
       </c>
       <c r="Q226" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R226" s="19" t="s">
         <v>80</v>
@@ -16703,7 +16758,7 @@
         <v>2010</v>
       </c>
       <c r="F227" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G227" s="15" t="s">
         <v>123</v>
@@ -16720,13 +16775,13 @@
         <v>-0.32003280000000001</v>
       </c>
       <c r="K227" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="L227" t="s">
         <v>97</v>
       </c>
       <c r="M227" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="N227" s="3"/>
       <c r="O227" t="s">
@@ -16736,7 +16791,7 @@
         <v>78</v>
       </c>
       <c r="Q227" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R227" s="19" t="s">
         <v>80</v>
@@ -16759,7 +16814,7 @@
         <v>2010</v>
       </c>
       <c r="F228" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G228" s="15" t="s">
         <v>122</v>
@@ -16776,13 +16831,13 @@
         <v>-1.6796218000000001</v>
       </c>
       <c r="K228" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="L228" t="s">
         <v>97</v>
       </c>
       <c r="M228" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="N228" s="3"/>
       <c r="O228" t="s">
@@ -16792,7 +16847,7 @@
         <v>78</v>
       </c>
       <c r="Q228" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R228" s="19" t="s">
         <v>83</v>
@@ -16815,7 +16870,7 @@
         <v>2010</v>
       </c>
       <c r="F229" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G229" s="15" t="s">
         <v>121</v>
@@ -16832,13 +16887,13 @@
         <v>-0.43927529999999998</v>
       </c>
       <c r="K229" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="L229" t="s">
         <v>97</v>
       </c>
       <c r="M229" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N229" s="3"/>
       <c r="O229" t="s">
@@ -16848,7 +16903,7 @@
         <v>78</v>
       </c>
       <c r="Q229" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R229" s="19" t="s">
         <v>80</v>
@@ -16871,7 +16926,7 @@
         <v>2009</v>
       </c>
       <c r="F230" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G230" s="15" t="s">
         <v>120</v>
@@ -16888,13 +16943,13 @@
         <v>-0.67069840000000003</v>
       </c>
       <c r="K230" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="L230" t="s">
         <v>97</v>
       </c>
       <c r="M230" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N230" s="3"/>
       <c r="O230" t="s">
@@ -16904,7 +16959,7 @@
         <v>78</v>
       </c>
       <c r="Q230" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R230" s="19" t="s">
         <v>80</v>
@@ -16927,7 +16982,7 @@
         <v>2009</v>
       </c>
       <c r="F231" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G231" s="15" t="s">
         <v>118</v>
@@ -16944,13 +16999,13 @@
         <v>-0.5202871</v>
       </c>
       <c r="K231" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="L231" t="s">
         <v>97</v>
       </c>
       <c r="M231" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N231" s="3"/>
       <c r="O231" t="s">
@@ -16960,7 +17015,7 @@
         <v>78</v>
       </c>
       <c r="Q231" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R231" s="19" t="s">
         <v>80</v>
@@ -16983,7 +17038,7 @@
         <v>2009</v>
       </c>
       <c r="F232" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G232" s="15" t="s">
         <v>679</v>
@@ -17000,13 +17055,13 @@
         <v>-0.63656729999999995</v>
       </c>
       <c r="K232" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="L232" t="s">
         <v>97</v>
       </c>
       <c r="M232" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N232" s="3"/>
       <c r="O232" t="s">
@@ -17016,7 +17071,7 @@
         <v>78</v>
       </c>
       <c r="Q232" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R232" s="19" t="s">
         <v>80</v>
@@ -17039,7 +17094,7 @@
         <v>2009</v>
       </c>
       <c r="F233" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G233" s="15" t="s">
         <v>680</v>
@@ -17056,13 +17111,13 @@
         <v>-0.63656729999999995</v>
       </c>
       <c r="K233" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="L233" t="s">
         <v>97</v>
       </c>
       <c r="M233" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N233" s="3"/>
       <c r="O233" t="s">
@@ -17072,7 +17127,7 @@
         <v>78</v>
       </c>
       <c r="Q233" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R233" s="19" t="s">
         <v>80</v>
@@ -17095,7 +17150,7 @@
         <v>2009</v>
       </c>
       <c r="F234" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G234" s="15" t="s">
         <v>117</v>
@@ -17112,13 +17167,13 @@
         <v>-1.8201556999999999</v>
       </c>
       <c r="K234" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L234" t="s">
         <v>97</v>
       </c>
       <c r="M234" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="N234" s="3"/>
       <c r="O234" t="s">
@@ -17128,7 +17183,7 @@
         <v>78</v>
       </c>
       <c r="Q234" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R234" s="19" t="s">
         <v>83</v>
@@ -17151,7 +17206,7 @@
         <v>2009</v>
       </c>
       <c r="F235" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G235" s="15" t="s">
         <v>116</v>
@@ -17168,13 +17223,13 @@
         <v>-0.10937529999999999</v>
       </c>
       <c r="K235" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L235" t="s">
         <v>97</v>
       </c>
       <c r="M235" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N235" s="3"/>
       <c r="O235" t="s">
@@ -17184,7 +17239,7 @@
         <v>78</v>
       </c>
       <c r="Q235" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R235" s="19" t="s">
         <v>80</v>
@@ -17207,7 +17262,7 @@
         <v>2009</v>
       </c>
       <c r="F236" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G236" s="15" t="s">
         <v>115</v>
@@ -17224,13 +17279,13 @@
         <v>-0.59473030000000005</v>
       </c>
       <c r="K236" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="L236" t="s">
         <v>97</v>
       </c>
       <c r="M236" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N236" s="3"/>
       <c r="O236" t="s">
@@ -17240,7 +17295,7 @@
         <v>78</v>
       </c>
       <c r="Q236" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R236" s="19" t="s">
         <v>281</v>
@@ -17263,7 +17318,7 @@
         <v>2009</v>
       </c>
       <c r="F237" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G237" s="15" t="s">
         <v>114</v>
@@ -17280,13 +17335,13 @@
         <v>-0.61496090000000003</v>
       </c>
       <c r="K237" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="L237" t="s">
         <v>97</v>
       </c>
       <c r="M237" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N237" s="3"/>
       <c r="O237" t="s">
@@ -17296,7 +17351,7 @@
         <v>78</v>
       </c>
       <c r="Q237" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R237" s="19" t="s">
         <v>80</v>
@@ -17319,7 +17374,7 @@
         <v>2009</v>
       </c>
       <c r="F238" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G238" s="15" t="s">
         <v>113</v>
@@ -17336,13 +17391,13 @@
         <v>-0.32664290000000001</v>
       </c>
       <c r="K238" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="L238" t="s">
         <v>97</v>
       </c>
       <c r="M238" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="N238" s="3"/>
       <c r="O238" t="s">
@@ -17352,7 +17407,7 @@
         <v>78</v>
       </c>
       <c r="Q238" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R238" s="19" t="s">
         <v>80</v>
@@ -17375,7 +17430,7 @@
         <v>2009</v>
       </c>
       <c r="F239" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G239" s="15" t="s">
         <v>112</v>
@@ -17392,13 +17447,13 @@
         <v>-0.75635940000000002</v>
       </c>
       <c r="K239" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="L239" t="s">
         <v>97</v>
       </c>
       <c r="M239" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N239" s="3"/>
       <c r="O239" t="s">
@@ -17408,7 +17463,7 @@
         <v>78</v>
       </c>
       <c r="Q239" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R239" s="19" t="s">
         <v>83</v>
@@ -17431,13 +17486,13 @@
         <v>2008</v>
       </c>
       <c r="F240" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G240" s="15" t="s">
         <v>111</v>
       </c>
       <c r="H240" s="15" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="I240" s="7" t="str">
         <f t="shared" si="9"/>
@@ -17448,13 +17503,13 @@
         <v>-1.3857569999999999</v>
       </c>
       <c r="K240" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="L240" t="s">
         <v>97</v>
       </c>
       <c r="M240" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N240" s="3"/>
       <c r="O240" t="s">
@@ -17464,7 +17519,7 @@
         <v>78</v>
       </c>
       <c r="Q240" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R240" s="19" t="s">
         <v>83</v>
@@ -17487,7 +17542,7 @@
         <v>2008</v>
       </c>
       <c r="F241" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G241" s="15" t="s">
         <v>110</v>
@@ -17504,13 +17559,13 @@
         <v>-0.33615020000000001</v>
       </c>
       <c r="K241" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="L241" t="s">
         <v>97</v>
       </c>
       <c r="M241" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N241" s="3"/>
       <c r="O241" t="s">
@@ -17520,7 +17575,7 @@
         <v>78</v>
       </c>
       <c r="Q241" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R241" s="19" t="s">
         <v>80</v>
@@ -17543,7 +17598,7 @@
         <v>2008</v>
       </c>
       <c r="F242" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G242" s="15" t="s">
         <v>109</v>
@@ -17560,13 +17615,13 @@
         <v>0.64747520000000003</v>
       </c>
       <c r="K242" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="L242" t="s">
         <v>97</v>
       </c>
       <c r="M242" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N242" s="3"/>
       <c r="O242" t="s">
@@ -17576,7 +17631,7 @@
         <v>78</v>
       </c>
       <c r="Q242" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R242" s="19" t="s">
         <v>80</v>
@@ -17599,7 +17654,7 @@
         <v>2008</v>
       </c>
       <c r="F243" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G243" s="15" t="s">
         <v>108</v>
@@ -17616,13 +17671,13 @@
         <v>-0.5385392</v>
       </c>
       <c r="K243" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="L243" t="s">
         <v>97</v>
       </c>
       <c r="M243" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N243" s="3"/>
       <c r="O243" t="s">
@@ -17632,7 +17687,7 @@
         <v>78</v>
       </c>
       <c r="Q243" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R243" s="19" t="s">
         <v>80</v>
@@ -17655,7 +17710,7 @@
         <v>2008</v>
       </c>
       <c r="F244" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G244" s="15" t="s">
         <v>107</v>
@@ -17672,13 +17727,13 @@
         <v>-4.9033899999999998E-2</v>
       </c>
       <c r="K244" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="L244" t="s">
         <v>97</v>
       </c>
       <c r="M244" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N244" s="3"/>
       <c r="O244" t="s">
@@ -17688,7 +17743,7 @@
         <v>78</v>
       </c>
       <c r="Q244" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R244" s="19" t="s">
         <v>80</v>
@@ -17711,7 +17766,7 @@
         <v>2008</v>
       </c>
       <c r="F245" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G245" s="15" t="s">
         <v>106</v>
@@ -17728,13 +17783,13 @@
         <v>-0.43927529999999998</v>
       </c>
       <c r="K245" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="L245" t="s">
         <v>97</v>
       </c>
       <c r="M245" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="N245" s="3"/>
       <c r="O245" t="s">
@@ -17744,7 +17799,7 @@
         <v>78</v>
       </c>
       <c r="Q245" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R245" s="19" t="s">
         <v>80</v>
@@ -17767,7 +17822,7 @@
         <v>2008</v>
       </c>
       <c r="F246" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G246" s="15" t="s">
         <v>105</v>
@@ -17784,13 +17839,13 @@
         <v>-0.28305079999999999</v>
       </c>
       <c r="K246" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="L246" t="s">
         <v>97</v>
       </c>
       <c r="M246" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="N246" s="3"/>
       <c r="O246" t="s">
@@ -17800,7 +17855,7 @@
         <v>78</v>
       </c>
       <c r="Q246" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R246" s="19" t="s">
         <v>80</v>
@@ -17823,7 +17878,7 @@
         <v>2008</v>
       </c>
       <c r="F247" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G247" s="15" t="s">
         <v>104</v>
@@ -17840,13 +17895,13 @@
         <v>-0.57880589999999998</v>
       </c>
       <c r="K247" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="L247" t="s">
         <v>97</v>
       </c>
       <c r="M247" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N247" s="3"/>
       <c r="O247" t="s">
@@ -17856,7 +17911,7 @@
         <v>78</v>
       </c>
       <c r="Q247" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R247" s="19" t="s">
         <v>80</v>
@@ -17879,7 +17934,7 @@
         <v>2008</v>
       </c>
       <c r="F248" s="14" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="G248" s="15" t="s">
         <v>103</v>
@@ -17896,13 +17951,13 @@
         <v>-0.55839329999999998</v>
       </c>
       <c r="K248" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L248" t="s">
         <v>97</v>
       </c>
       <c r="M248" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="N248" s="3"/>
       <c r="O248" t="s">
@@ -17912,7 +17967,7 @@
         <v>78</v>
       </c>
       <c r="Q248" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R248" s="19" t="s">
         <v>80</v>
@@ -17932,16 +17987,16 @@
         <v>6</v>
       </c>
       <c r="E249" s="14">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F249" s="14" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G249" s="15" t="s">
+        <v>976</v>
+      </c>
+      <c r="H249" t="s">
         <v>977</v>
-      </c>
-      <c r="H249" t="s">
-        <v>978</v>
       </c>
       <c r="I249" s="7" t="str">
         <f t="shared" si="9"/>
@@ -17952,13 +18007,13 @@
         <v>-0.87778060000000002</v>
       </c>
       <c r="K249" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="L249" t="s">
         <v>97</v>
       </c>
       <c r="M249" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="O249" t="s">
         <v>86</v>
@@ -17967,7 +18022,7 @@
         <v>78</v>
       </c>
       <c r="Q249" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="R249" s="19" t="s">
         <v>83</v>
@@ -17975,45 +18030,42 @@
     </row>
     <row r="250" spans="1:18">
       <c r="A250" s="13" t="s">
-        <v>702</v>
+        <v>1044</v>
       </c>
       <c r="B250" s="14">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C250" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D250" s="15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E250" s="14">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F250" s="14" t="s">
-        <v>986</v>
-      </c>
-      <c r="G250" s="15" t="s">
-        <v>977</v>
-      </c>
-      <c r="H250" t="s">
-        <v>978</v>
+        <v>1053</v>
+      </c>
+      <c r="G250" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H250" s="15" t="s">
+        <v>1052</v>
       </c>
       <c r="I250" s="7" t="str">
-        <f t="shared" si="9"/>
-        <v>41.6529037</v>
+        <f t="shared" ref="I250:I253" si="11">MID(K250,FIND("@",K250)+1,FIND(",",K250,FIND("@",K250))-FIND("@",K250)-1)</f>
+        <v>42.2387223</v>
       </c>
       <c r="J250" s="7">
-        <f t="shared" si="10"/>
-        <v>-0.87778060000000002</v>
+        <f t="shared" ref="J250:J253" si="12">VALUE(SUBSTITUTE(MID(K250,FIND(",",K250,FIND("@",K250))+1,FIND(",",K250,FIND(",",K250,FIND("@",K250))+1)-FIND(",",K250,FIND("@",K250))-1),".",","))</f>
+        <v>-0.34893160000000001</v>
       </c>
       <c r="K250" t="s">
-        <v>979</v>
-      </c>
-      <c r="L250" t="s">
-        <v>97</v>
+        <v>1051</v>
       </c>
       <c r="M250" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="O250" t="s">
         <v>86</v>
@@ -18022,16 +18074,163 @@
         <v>78</v>
       </c>
       <c r="Q250" t="s">
-        <v>1014</v>
-      </c>
-      <c r="R250" s="19" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R250" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18">
+      <c r="A251" s="13" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B251" s="14">
+        <v>13</v>
+      </c>
+      <c r="C251" s="14">
+        <v>5</v>
+      </c>
+      <c r="D251" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E251" s="14">
+        <v>2007</v>
+      </c>
+      <c r="G251" s="15" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H251" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="I251" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>41.0368836</v>
+      </c>
+      <c r="J251" s="7">
+        <f t="shared" si="12"/>
+        <v>-1.6627352</v>
+      </c>
+      <c r="K251" t="s">
+        <v>1054</v>
+      </c>
+      <c r="M251" t="s">
+        <v>983</v>
+      </c>
+      <c r="O251" t="s">
+        <v>86</v>
+      </c>
+      <c r="P251" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R251" s="23" t="s">
         <v>83</v>
       </c>
     </row>
+    <row r="252" spans="1:18">
+      <c r="A252" s="22" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B252" s="14">
+        <v>26</v>
+      </c>
+      <c r="C252" s="14">
+        <v>5</v>
+      </c>
+      <c r="D252" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E252" s="14">
+        <v>2007</v>
+      </c>
+      <c r="G252" s="15" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H252" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I252" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>42.6666815</v>
+      </c>
+      <c r="J252" s="7">
+        <f t="shared" si="12"/>
+        <v>-0.32696639999999999</v>
+      </c>
+      <c r="K252" t="s">
+        <v>1055</v>
+      </c>
+      <c r="M252" t="s">
+        <v>983</v>
+      </c>
+      <c r="O252" t="s">
+        <v>86</v>
+      </c>
+      <c r="P252" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R252" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18">
+      <c r="A253" s="22" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B253" s="14">
+        <v>14</v>
+      </c>
+      <c r="C253" s="14">
+        <v>7</v>
+      </c>
+      <c r="D253" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E253" s="14">
+        <v>2007</v>
+      </c>
+      <c r="G253" s="15" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H253" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I253" s="7" t="str">
+        <f t="shared" si="11"/>
+        <v>42.7996859</v>
+      </c>
+      <c r="J253" s="7">
+        <f t="shared" si="12"/>
+        <v>-0.41652460000000002</v>
+      </c>
+      <c r="K253" t="s">
+        <v>1056</v>
+      </c>
+      <c r="M253" t="s">
+        <v>983</v>
+      </c>
+      <c r="O253" t="s">
+        <v>86</v>
+      </c>
+      <c r="P253" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R253" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R250" xr:uid="{0F92D137-B0F7-489C-BBD5-87D14D584D75}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R250">
-      <sortCondition descending="1" ref="A1:A250"/>
+  <autoFilter ref="A1:R249" xr:uid="{0F92D137-B0F7-489C-BBD5-87D14D584D75}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R249">
+      <sortCondition descending="1" ref="A1:A249"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
